--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -13,31 +13,23 @@
     <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" tabRatio="785"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="13" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="14" r:id="rId2"/>
-    <sheet name="Tags" sheetId="18" r:id="rId3"/>
-    <sheet name="Features" sheetId="16" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="11" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="3" r:id="rId2"/>
+    <sheet name="Tags" sheetId="4" r:id="rId3"/>
+    <sheet name="Features" sheetId="2" r:id="rId4"/>
+    <sheet name="Exceptions" sheetId="12" r:id="rId5"/>
     <sheet name="DB Data" sheetId="5" r:id="rId8" state="veryHidden"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="Chart1" localSheetId="3">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="1">Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="2">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1">#REF!</definedName>
-    <definedName name="Chart10">#REF!</definedName>
-    <definedName name="Chart30">#REF!</definedName>
-    <definedName name="Chart49">#REF!</definedName>
-    <definedName name="Chart51">#REF!</definedName>
+    <definedName name="Chart1">Scenarios!#REF!</definedName>
+    <definedName name="Chart51">Scenarios!#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="82">
   <si>
     <t>Duration</t>
   </si>
@@ -96,6 +88,9 @@
     <t>STATUS</t>
   </si>
   <si>
+    <t>FEATURE STATUS</t>
+  </si>
+  <si>
     <t>Features Total</t>
   </si>
   <si>
@@ -111,43 +106,109 @@
     <t>Excel Extent Report</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:16 PM</t>
+    <t>TAG</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:14 PM</t>
+    <t>Scenario Passed</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:15 PM</t>
+    <t>Scenario Failed</t>
   </si>
   <si>
-    <t>0.252 s</t>
+    <t>Scenario Skipped</t>
+  </si>
+  <si>
+    <t>Tag Name</t>
+  </si>
+  <si>
+    <t>Feature Name</t>
+  </si>
+  <si>
+    <t>Feature Status</t>
+  </si>
+  <si>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>Scenario Status</t>
+  </si>
+  <si>
+    <t>Step Passed</t>
+  </si>
+  <si>
+    <t>Step Failed</t>
+  </si>
+  <si>
+    <t>Step Skipped</t>
+  </si>
+  <si>
+    <t>FEATURE FAIL SKIP</t>
+  </si>
+  <si>
+    <t>SCENARIO FAIL SKIP</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>0.013 s</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>0.022 s</t>
+    <t>FAILED &amp; SKIPPED TAGS</t>
   </si>
   <si>
     <t>TAG NAME</t>
   </si>
   <si>
+    <t>FAILED &amp; SKIPPED SCENARIOS</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:11 PM</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:09 PM</t>
+  </si>
+  <si>
+    <t>0.253 s</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>0.015 s</t>
+  </si>
+  <si>
+    <t>0.023 s</t>
+  </si>
+  <si>
+    <t>tag1</t>
+  </si>
+  <si>
     <t>tag</t>
+  </si>
+  <si>
+    <t>STACKTRACE</t>
   </si>
   <si>
     <t>STEP / HOOK TEXT</t>
   </si>
   <si>
-    <t>STACKTRACE</t>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>STEPS</t>
+  </si>
+  <si>
+    <t>SCENARIOS</t>
+  </si>
+  <si>
+    <t>NAME</t>
   </si>
   <si>
     <t>SCENARIO</t>
@@ -156,67 +217,133 @@
     <t>FEATURE</t>
   </si>
   <si>
-    <t>STEPS</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>SCENARIOS</t>
-  </si>
-  <si>
     <t>PASS %</t>
   </si>
   <si>
     <t>AUTHOR NAME</t>
   </si>
   <si>
-    <t>author</t>
+    <t>device</t>
   </si>
   <si>
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>device</t>
+    <t>Feb 06, 2026 10:43:02 AM</t>
   </si>
   <si>
-    <t>Jan 27, 2026 11:45:22 am</t>
+    <t>Feb 06, 2026 10:41:44 AM</t>
   </si>
   <si>
-    <t>Jan 27, 2026 11:42:36 am</t>
+    <t>Feb 06, 2026 10:43:00 AM</t>
   </si>
   <si>
-    <t>Jan 27, 2026 11:45:21 am</t>
+    <t>1 m 16.602 s</t>
   </si>
   <si>
-    <t>2 m 44.991 s</t>
+    <t>0%</t>
   </si>
   <si>
-    <t>100%</t>
+    <t>50%</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_ATL_02 |Verify Try Along product added from Admin is displayed in application| "TD_UI_Zlaata_ATL_02"</t>
+    <t>@TC_UI_Admin_OEV_01</t>
   </si>
   <si>
-    <t>2 m 44.226 s</t>
+    <t>@Mail</t>
   </si>
   <si>
-    <t>Try along section</t>
+    <t>Verify Order Email Flow</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_ATL_02</t>
+    <t>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</t>
   </si>
   <si>
-    <t>2 m 44.230 s</t>
+    <t>1 m 15.719 s</t>
+  </si>
+  <si>
+    <t>1 m 15.728 s</t>
+  </si>
+  <si>
+    <t>When Order confirmation email should be received for order placed, order shipped, order delivered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.NoSuchWindowException: no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=144.0.7559.110)
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [6c2dd4389e88820d450c8ad7b752fcc2, findElements {value=//table//tr//span[@class='bog']/span, using=xpath}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.110, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62452}, goog:processID: 1168, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62452/devtoo..., se:cdpVersion: 144.0.7559.110, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 6c2dd4389e88820d450c8ad7b752fcc2
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.ElementLocation$ElementFinder$2.findElements(ElementLocation.java:182)
+	at org.openqa.selenium.remote.ElementLocation.findElements(ElementLocation.java:103)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElements(RemoteWebDriver.java:380)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElements(RemoteWebDriver.java:374)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke0(Native Method)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke(NativeMethodAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$sEA650lj.findElements(Unknown Source)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyOrderConfirmationMail(AdminEmailVerifyOrderFlowPage.java:430)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyOrderPlacedEmail(AdminEmailVerifyOrderFlowPage.java:2694)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.order_confirmation_email_should_be_received_for_order_placed_order_shipped_order_delivered(AdminEmailVerifyOrderFlowStepDef.java:26)
+	at ✽.Order confirmation email should be received for order placed, order shipped, order delivered.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever32/src/test/resources/features/AdminFeature/emailVerify.feature:7)
+</t>
+  </si>
+  <si>
+    <t>stepDef.Hooks.tearDown(io.cucumber.java.Scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.NoSuchWindowException: no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=144.0.7559.110)
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [6c2dd4389e88820d450c8ad7b752fcc2, screenshot {}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.110, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62452}, goog:processID: 1168, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62452/devtoo..., se:cdpVersion: 144.0.7559.110, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 6c2dd4389e88820d450c8ad7b752fcc2
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:617)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:621)
+	at org.openqa.selenium.remote.RemoteWebDriver.getScreenshotAs(RemoteWebDriver.java:333)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke0(Native Method)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke(NativeMethodAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$sEA650lj.getScreenshotAs(Unknown Source)
+	at utils.ExcelReportUtil.captureScreenshot(ExcelReportUtil.java:68)
+	at stepDef.Hooks.tearDown(Hooks.java:298)
+</t>
   </si>
 </sst>
 </file>
@@ -224,7 +351,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="0"/>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +362,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -284,9 +435,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FF51FF21"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,7 +461,7 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FF51FF21"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -317,7 +474,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
-      <color rgb="00FF00"/>
+      <color rgb="FF0000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color rgb="FF0000"/>
       <b val="true"/>
     </font>
     <font>
@@ -345,11 +507,6 @@
       <sz val="11.0"/>
       <b val="true"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="00FF00"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -359,7 +516,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -374,6 +531,43 @@
       <right style="hair">
         <color auto="1"/>
       </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -441,9 +635,7 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
@@ -471,173 +663,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,24 +853,30 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Features</a:t>
+              <a:t>Tags with</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> Failed &amp; Skipped Scenarios</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.1929905820595947E-3"/>
-          <c:y val="5.6284335775106678E-2"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -714,10 +886,719 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11780714910636171"/>
-          <c:y val="8.0818739637467149E-2"/>
-          <c:w val="0.76899981252343452"/>
-          <c:h val="0.87885598708448542"/>
+          <c:x val="2.9880212949228394E-2"/>
+          <c:y val="0.11750877449771498"/>
+          <c:w val="0.95813725490196078"/>
+          <c:h val="0.84734403472530151"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Mail</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$B$20:$B$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Mail</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$D$20:$D$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Mail</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$C$20:$C$21</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46151168"/>
+        <c:axId val="46117248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46151168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46117248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46117248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46151168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.3309046751669701E-2"/>
+          <c:y val="0.10919339164237124"/>
+          <c:w val="0.95333333333333337"/>
+          <c:h val="0.84804664723032075"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$F$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$H$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$H$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$G$22</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46512000"/>
+        <c:axId val="46513536"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46512000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46513536"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46513536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46512000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3310417416097107E-2"/>
+          <c:y val="0.17399131020088515"/>
+          <c:w val="0.93298799578986624"/>
+          <c:h val="0.80271606659122552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -759,7 +1640,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000001-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -784,7 +1665,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000003-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -809,7 +1690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000005-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -839,12 +1720,18 @@
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CEAE-4775-A1C6-116F718DC196}"/>
+              <c16:uniqueId val="{00000006-D2BC-4951-98B3-E41274AF2CA1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -880,7 +1767,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -906,15 +1793,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Devices</a:t>
+              <a:t>Authors</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -924,10 +1810,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -939,7 +1825,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$D$21</c:f>
+              <c:f>Authors!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -974,37 +1860,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$D$22</c:f>
+              <c:f>Authors!$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000000-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1013,7 +1898,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$F$21</c:f>
+              <c:f>Authors!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1048,25 +1933,24 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$F$22</c:f>
+              <c:f>Authors!$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1078,7 +1962,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000001-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1087,7 +1971,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$E$21</c:f>
+              <c:f>Authors!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1122,37 +2006,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$E$22</c:f>
+              <c:f>Authors!$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000002-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1166,11 +2049,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1180,7 +2063,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1188,7 +2071,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1206,7 +2089,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -1214,14 +2097,379 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Devices</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$E$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46589440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46590976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46590976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1275,12 +2523,750 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features with Failed &amp; Skipped</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> Scenarios</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.587826839649571E-2"/>
+          <c:y val="0.10654873856176561"/>
+          <c:w val="0.89369296921336749"/>
+          <c:h val="0.85018673119905308"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$J$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$J$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9F7-4BBB-94B0-AEDC4FA75EC0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$L$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$L$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$K$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46193280"/>
+        <c:axId val="46285184"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46193280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46285184"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46285184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46193280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Scenarios</a:t>
+              <a:t>Scenarios with Failed &amp; Skipped Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0031919744642044E-2"/>
+          <c:y val="0.10668158781898149"/>
+          <c:w val="0.92990424076607392"/>
+          <c:h val="0.8499999379835731"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$R$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$R$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$S$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$T$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$T$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$S$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46328448"/>
+        <c:axId val="46408064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46328448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46408064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46408064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Steps</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46328448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Features</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1289,8 +3275,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.9364481457108926E-3"/>
-          <c:y val="3.2123800120282653E-2"/>
+          <c:x val="5.9362468167315514E-3"/>
+          <c:y val="6.4713026203216312E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1302,10 +3288,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.6498186400440001E-2"/>
-          <c:y val="0.10118873685128098"/>
-          <c:w val="0.87710436725913243"/>
-          <c:h val="0.86336406553156542"/>
+          <c:x val="7.3672686824927558E-2"/>
+          <c:y val="0.11902669624860428"/>
+          <c:w val="0.92151704085316477"/>
+          <c:h val="0.85596714084772552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1347,7 +3333,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000001-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1372,7 +3358,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000003-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1397,42 +3383,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000005-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$E$2:$E$4</c:f>
+              <c:f>'DB Data'!$C$2:$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Scenarios Passed</c:v>
+                  <c:v>Features Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Scenarios Failed</c:v>
+                  <c:v>Features Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scenarios Skipped</c:v>
+                  <c:v>Features Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$F$2:$F$4</c:f>
+              <c:f>'DB Data'!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F52A-4A06-BA5F-6C71FCEF3775}"/>
+              <c16:uniqueId val="{00000006-C5E1-437A-A52D-DCB97CB8ED06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1468,7 +3491,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1488,16 +3511,16 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr algn="ctr">
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1800" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Steps</a:t>
+              <a:t>Scenarios</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1506,8 +3529,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.6171728533933258E-3"/>
-          <c:y val="5.4421749273573204E-2"/>
+          <c:x val="5.9107001159738751E-3"/>
+          <c:y val="3.7140215132502832E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1519,10 +3542,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11769966254218223"/>
-          <c:y val="8.4263722654767198E-2"/>
-          <c:w val="0.78142825896762902"/>
-          <c:h val="0.89306054848124394"/>
+          <c:x val="5.6571751205517912E-2"/>
+          <c:y val="8.4536101166436714E-2"/>
+          <c:w val="0.92725874381981321"/>
+          <c:h val="0.88851560210722469"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1564,7 +3587,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000001-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1589,7 +3612,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000003-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1614,42 +3637,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000005-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:f>'DB Data'!$E$2:$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Steps Passed</c:v>
+                  <c:v>Scenarios Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Steps Failed</c:v>
+                  <c:v>Scenarios Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Steps Skipped</c:v>
+                  <c:v>Scenarios Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:f>'DB Data'!$F$2:$F$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-33E3-412A-9233-ED47CE12E57E}"/>
+              <c16:uniqueId val="{00000006-86A0-4454-A31A-15C1830346B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1685,7 +3745,261 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.0163677357506801E-2"/>
+          <c:y val="5.5749128919860627E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.6917458262785006E-2"/>
+          <c:y val="0.10406650388213669"/>
+          <c:w val="0.93302459414795369"/>
+          <c:h val="0.87775832898936412"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d prstMaterial="matte"/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="51FF21"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Steps Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Steps Failed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Steps Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2833-4D5B-98DA-2F8086DE2D67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="40"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId1"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1728,9 +4042,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.3309046751669701E-2"/>
+          <c:x val="3.3278738246891114E-2"/>
           <c:y val="0.10500003204542271"/>
-          <c:w val="0.95333333333333337"/>
+          <c:w val="0.953375796178344"/>
           <c:h val="0.85236429602767994"/>
         </c:manualLayout>
       </c:layout>
@@ -1788,7 +4102,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_ATL_02 |Verify Try Along product added from Admin is displayed in application| "TD_UI_Zlaata_ATL_02"</c:v>
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1799,14 +4113,14 @@
               <c:numCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3.0</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000000-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1860,7 +4174,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_ATL_02 |Verify Try Along product added from Admin is displayed in application| "TD_UI_Zlaata_ATL_02"</c:v>
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1873,7 +4187,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000002-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1927,7 +4241,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_ATL_02 |Verify Try Along product added from Admin is displayed in application| "TD_UI_Zlaata_ATL_02"</c:v>
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1935,12 +4249,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$I$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000001-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1954,11 +4273,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97185152"/>
-        <c:axId val="97201536"/>
+        <c:axId val="89325952"/>
+        <c:axId val="44310528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97185152"/>
+        <c:axId val="89325952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1968,7 +4287,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97201536"/>
+        <c:crossAx val="44310528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1976,7 +4295,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97201536"/>
+        <c:axId val="44310528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2008,7 +4327,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97185152"/>
+        <c:crossAx val="89325952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2037,7 +4356,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2103,7 +4422,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000001-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2128,7 +4447,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000003-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2153,7 +4472,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000005-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2181,14 +4500,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+              <c16:uniqueId val="{00000006-012F-4AE0-9B30-C14C76CB6C4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2209,907 +4534,6 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId1"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Tags</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$D$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_ATL_02</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$D$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_ATL_02</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$F$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$E$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_ATL_02</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$E$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97122176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97123712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Features</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="3.3369832880226151E-2"/>
-          <c:y val="9.72480620155039E-2"/>
-          <c:w val="0.95324817070407986"/>
-          <c:h val="0.8601162790697674"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Try along section</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$F$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$H$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Try along section</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$H$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$G$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Try along section</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$G$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97540352"/>
-        <c:axId val="97550336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97540352"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97550336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97550336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97540352"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-        <c:minorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.3310417416097107E-2"/>
-          <c:y val="0.17399131020088515"/>
-          <c:w val="0.93298799578986624"/>
-          <c:h val="0.80271606659122552"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d prstMaterial="matte"/>
-          </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="51FF21"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'DB Data'!$C$2:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Features Passed</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Features Failed</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Features Skipped</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'DB Data'!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-1678-4457-8DD3-1C4694EC7DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="40"/>
-      </c:doughnutChart>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -3156,15 +4580,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Authors</a:t>
+              <a:t>Tags</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -3174,10 +4597,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -3189,7 +4612,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$D$21</c:f>
+              <c:f>Tags!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3224,37 +4647,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Mail</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$D$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$D$22:$D$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000000-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3263,7 +4682,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$F$21</c:f>
+              <c:f>Tags!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3298,37 +4717,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Mail</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$F$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$F$22:$F$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000001-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3337,7 +4752,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$E$21</c:f>
+              <c:f>Tags!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3372,37 +4787,41 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Mail</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$E$22</c:f>
+              <c:f>Tags!$E$22:$E$23</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000002-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3416,11 +4835,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3430,7 +4849,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3438,7 +4857,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3456,7 +4875,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -3464,14 +4883,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3506,672 +4924,1681 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>43815</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>158115</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190500" y="142875"/>
-          <a:ext cx="3749040" cy="777240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Duration</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828924</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472439</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>127635</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486774" y="142875"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Start Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>165735</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486775" y="561975"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>End Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1019175" y="152401"/>
-          <a:ext cx="2933700" cy="771524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
-            <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>0.252 s</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3790950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9448800" y="142875"/>
-          <a:ext cx="2800350" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:14 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3809999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9467849" y="561975"/>
-          <a:ext cx="2771775" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:15 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
+      <xdr:colOff>57148</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7"/>
+        <xdr:cNvPr id="9" name="Group 8"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="190499" y="28576"/>
-          <a:ext cx="12045316" cy="3657600"/>
-          <a:chOff x="171449" y="36548"/>
-          <a:chExt cx="12045316" cy="3399182"/>
+          <a:off x="190498" y="0"/>
+          <a:ext cx="12068177" cy="3438525"/>
+          <a:chOff x="161923" y="0"/>
+          <a:chExt cx="12068177" cy="3438525"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="9" name="Group 8"/>
+          <xdr:cNvPr id="42" name="Group 41"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="171449" y="815528"/>
-            <a:ext cx="3749040" cy="2620202"/>
-            <a:chOff x="171449" y="815528"/>
-            <a:chExt cx="3749040" cy="2620202"/>
+            <a:off x="161923" y="0"/>
+            <a:ext cx="12068177" cy="3438525"/>
+            <a:chOff x="171448" y="19050"/>
+            <a:chExt cx="12068177" cy="3438525"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="13" name="Group 12"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="8477248" y="133350"/>
+              <a:ext cx="3762377" cy="685800"/>
+              <a:chOff x="8477248" y="133350"/>
+              <a:chExt cx="3762377" cy="685800"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="4" name="Rectangle 3"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477248" y="133350"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0" algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Start Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="5" name="Rectangle 4"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477249" y="495300"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>End Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="TextBox 6"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9563100" y="133351"/>
+                <a:ext cx="2676525" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="8" name="TextBox 7"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9572625" y="495300"/>
+                <a:ext cx="2667000" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="2" name="Group 100"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="171448" y="19050"/>
+              <a:ext cx="12054842" cy="3438525"/>
+              <a:chOff x="171448" y="19050"/>
+              <a:chExt cx="12054842" cy="3438525"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="10" name="Group 9"/>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="171448" y="19050"/>
+                <a:ext cx="12054842" cy="3438525"/>
+                <a:chOff x="152398" y="27696"/>
+                <a:chExt cx="12054842" cy="3195586"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="16" name="Group 15"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="152398" y="656192"/>
+                  <a:ext cx="3749040" cy="2563550"/>
+                  <a:chOff x="152398" y="656192"/>
+                  <a:chExt cx="3749040" cy="2563550"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="31" name="Rectangle 30"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="152398" y="815526"/>
+                    <a:ext cx="3749040" cy="2381198"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:grpSp>
+                <xdr:nvGrpSpPr>
+                  <xdr:cNvPr id="32" name="Group 31"/>
+                  <xdr:cNvGrpSpPr/>
+                </xdr:nvGrpSpPr>
+                <xdr:grpSpPr>
+                  <a:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="3621406" cy="2563550"/>
+                    <a:chOff x="247650" y="656192"/>
+                    <a:chExt cx="3621406" cy="2563550"/>
+                  </a:xfrm>
+                </xdr:grpSpPr>
+                <xdr:grpSp>
+                  <xdr:nvGrpSpPr>
+                    <xdr:cNvPr id="33" name="Group 32"/>
+                    <xdr:cNvGrpSpPr/>
+                  </xdr:nvGrpSpPr>
+                  <xdr:grpSpPr>
+                    <a:xfrm>
+                      <a:off x="2771776" y="859785"/>
+                      <a:ext cx="1097280" cy="764816"/>
+                      <a:chOff x="2771776" y="859785"/>
+                      <a:chExt cx="1097280" cy="764816"/>
+                    </a:xfrm>
+                  </xdr:grpSpPr>
+                  <xdr:sp macro="" textlink="">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="35" name="Rounded Rectangle 34"/>
+                      <xdr:cNvSpPr/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="2771776" y="859785"/>
+                        <a:ext cx="1097280" cy="764816"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="roundRect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:ln w="3175"/>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="2">
+                        <a:schemeClr val="dk1"/>
+                      </a:lnRef>
+                      <a:fillRef idx="1">
+                        <a:schemeClr val="lt1"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:schemeClr val="dk1"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>PASSED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>FAILED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>SKIPPED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>TOTAL</a:t>
+                        </a:r>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$2">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="36" name="TextBox 35"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="868694"/>
+                        <a:ext cx="485775" cy="247651"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="27F959"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="27F959"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$3">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="37" name="TextBox 36"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="1027977"/>
+                        <a:ext cx="485775" cy="251635"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FF0000"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>2</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$4">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="38" name="TextBox 37"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3371850" y="1187314"/>
+                        <a:ext cx="495300" cy="239006"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FFFF00"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FFFF00"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                </xdr:grpSp>
+                <xdr:graphicFrame macro="">
+                  <xdr:nvGraphicFramePr>
+                    <xdr:cNvPr id="34" name="FeatureDough"/>
+                    <xdr:cNvGraphicFramePr>
+                      <a:graphicFrameLocks/>
+                    </xdr:cNvGraphicFramePr>
+                  </xdr:nvGraphicFramePr>
+                  <xdr:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="2562225" cy="2563550"/>
+                  </xdr:xfrm>
+                  <a:graphic>
+                    <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                      <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+                    </a:graphicData>
+                  </a:graphic>
+                </xdr:graphicFrame>
+              </xdr:grpSp>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="17" name="Group 16"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="3981450" y="27696"/>
+                  <a:ext cx="4391026" cy="3177881"/>
+                  <a:chOff x="3981450" y="27696"/>
+                  <a:chExt cx="4391026" cy="3177881"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="25" name="Rectangle 24"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="3981450" y="133921"/>
+                    <a:ext cx="4391026" cy="3059265"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="26" name="Rounded Rectangle 25"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7143750" y="183252"/>
+                    <a:ext cx="1188720" cy="849796"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1600" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="27" name="TextBox 26"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="213640"/>
+                    <a:ext cx="542925" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="28" name="TextBox 27"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="394614"/>
+                    <a:ext cx="542926" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="29" name="TextBox 28"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7781924" y="557888"/>
+                    <a:ext cx="533401" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="30" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="4019551" y="27696"/>
+                  <a:ext cx="3276600" cy="3177881"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="18" name="Group 17"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="8458200" y="682747"/>
+                  <a:ext cx="3749040" cy="2540535"/>
+                  <a:chOff x="8458200" y="682747"/>
+                  <a:chExt cx="3749040" cy="2540535"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="19" name="Rectangle 18"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="8458200" y="815526"/>
+                    <a:ext cx="3749040" cy="2379428"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="20" name="Rounded Rectangle 19"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11077576" y="856008"/>
+                    <a:ext cx="1097280" cy="764816"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1300" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="21" name="TextBox 20"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="859839"/>
+                    <a:ext cx="476250" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{ECACBD74-B5B9-479E-8C2E-C9684999A572}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>6</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="22" name="TextBox 21"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11658600" y="1023110"/>
+                    <a:ext cx="485776" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{E24417FB-CCF3-4060-A9AB-23F9E2CDA81A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="23" name="TextBox 22"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="1177529"/>
+                    <a:ext cx="476250" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{04B0E76C-90E2-4732-8606-78D62C393D8A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="24" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="8572501" y="682747"/>
+                  <a:ext cx="2543174" cy="2540535"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="'DB Data'!$F$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="39" name="TextBox 38"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7791450" y="781050"/>
+                <a:ext cx="542925" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C1C65169-A7E7-4F44-8F1B-A4A10551DED6}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>6</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$D$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="40" name="TextBox 39"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3390900" y="1438275"/>
+                <a:ext cx="495299" cy="257176"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C751D109-05C5-4D27-8561-41C7DB1DFED0}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>4</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1100" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$H$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="41" name="TextBox 40"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="11687174" y="1428750"/>
+                <a:ext cx="476251" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{9404FC27-F618-4129-9790-CCC5E3B452F7}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>8</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="Rectangle 23"/>
+            <xdr:cNvPr id="3" name="Rectangle 2"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="171449" y="952809"/>
-              <a:ext cx="3749040" cy="2464407"/>
+              <a:off x="171450" y="133349"/>
+              <a:ext cx="3749040" cy="685800"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
             <a:noFill/>
-            <a:ln w="6350"/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:ln>
           </xdr:spPr>
           <xdr:style>
             <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
             </a:lnRef>
             <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
+              <a:schemeClr val="accent1"/>
             </a:fillRef>
             <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1"/>
             </a:effectRef>
             <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="lt1"/>
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Duration</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="27" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="419100" y="815528"/>
-            <a:ext cx="3238500" cy="2620202"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
       </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="10" name="Group 9"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
+      <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="TextBox 5"/>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
           <a:xfrm>
-            <a:off x="4000498" y="36548"/>
-            <a:ext cx="4389120" cy="3390329"/>
-            <a:chOff x="4000498" y="36548"/>
-            <a:chExt cx="4389120" cy="3390329"/>
+            <a:off x="990601" y="114300"/>
+            <a:ext cx="2924174" cy="676275"/>
           </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="Rectangle 17"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4000498" y="142772"/>
-              <a:ext cx="4389120" cy="3271713"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
             <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="23" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="4400550" y="36548"/>
-            <a:ext cx="3590925" cy="3390329"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="11" name="Group 10"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="8467725" y="806675"/>
-            <a:ext cx="3749040" cy="2609869"/>
-            <a:chOff x="8467725" y="806675"/>
-            <a:chExt cx="3749040" cy="2609869"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="Rectangle 11"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8467725" y="952137"/>
-              <a:ext cx="3749040" cy="2464407"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="17" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="8734425" y="806675"/>
-            <a:ext cx="3200400" cy="2602499"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
+              <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:pPr algn="ctr"/>
+              <a:t>0.253 s</a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4182,22 +6609,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35</cdr:x>
-      <cdr:y>0.34014</cdr:y>
+      <cdr:x>0.34572</cdr:x>
+      <cdr:y>0.37983</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.65294</cdr:x>
-      <cdr:y>0.69728</cdr:y>
+      <cdr:x>0.72119</cdr:x>
+      <cdr:y>0.71478</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1133475" y="952503"/>
-          <a:ext cx="981075" cy="1000125"/>
+          <a:off x="885825" y="1047749"/>
+          <a:ext cx="962024" cy="923925"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4323,7 +6750,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
+          <a:fld id="{790B2992-122F-4DED-8027-8C90CA641799}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4331,7 +6758,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4349,22 +6776,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.33156</cdr:x>
-      <cdr:y>0.36031</cdr:y>
+      <cdr:x>0.3343</cdr:x>
+      <cdr:y>0.34819</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.68208</cdr:x>
-      <cdr:y>0.70496</cdr:y>
+      <cdr:x>0.7064</cdr:x>
+      <cdr:y>0.70474</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1190625" y="1314450"/>
-          <a:ext cx="1258673" cy="1257300"/>
+          <a:off x="1095367" y="1190625"/>
+          <a:ext cx="1219223" cy="1219200"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4490,17 +6917,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{55E37DD8-520B-4F7A-9381-E422E7073C87}" type="TxLink">
+            <a:rPr lang="en-US" sz="3000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="3600" b="1">
+          <a:endParaRPr lang="en-US" sz="3000" b="1">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -4516,22 +6943,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35119</cdr:x>
-      <cdr:y>0.35374</cdr:y>
+      <cdr:x>0.33708</cdr:x>
+      <cdr:y>0.36934</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.66667</cdr:x>
-      <cdr:y>0.71088</cdr:y>
+      <cdr:x>0.70786</cdr:x>
+      <cdr:y>0.71429</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$H$5">
+    <cdr:sp macro="" textlink="'DB Data'!$H$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1123950" y="990599"/>
-          <a:ext cx="1009650" cy="1000125"/>
+          <a:off x="857253" y="1009650"/>
+          <a:ext cx="942958" cy="942975"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4657,7 +7084,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{31691118-B83C-4A2D-970E-D212AA344C2F}" type="TxLink">
+          <a:fld id="{0C07208B-2D34-4675-9C99-827455C82BF1}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4665,7 +7092,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>75%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4690,16 +7117,14 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4748,15 +7173,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>228601</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1508761</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>1508760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150494</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4765,8 +7190,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="323851" y="180974"/>
-          <a:ext cx="1280160" cy="352426"/>
+          <a:off x="323850" y="180974"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4801,6 +7226,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -4810,13 +7257,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>876300</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1514476</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>104553</xdr:rowOff>
+      <xdr:rowOff>85503</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$F$2">
       <xdr:nvSpPr>
@@ -4825,7 +7272,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="971550" y="219075"/>
+          <a:off x="971550" y="200025"/>
           <a:ext cx="638176" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4855,7 +7302,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{8D92AF4D-37D8-4C38-8EA4-79D629C4A437}" type="TxLink">
+          <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="51FF21"/>
@@ -4863,11 +7310,151 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>2</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23284</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1504950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>99262</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962025" y="404284"/>
+          <a:ext cx="638175" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866776</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1514476</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104219</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962026" y="589494"/>
+          <a:ext cx="647700" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -4882,22 +7469,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.32161</cdr:x>
+      <cdr:y>0.41018</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.68844</cdr:x>
+      <cdr:y>0.71781</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="561975" y="933452"/>
-          <a:ext cx="952500" cy="923924"/>
+          <a:off x="609603" y="914412"/>
+          <a:ext cx="695317" cy="685798"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5023,17 +7610,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{BB53D87E-07A1-498D-A732-07528C1BCE6E}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5052,20 +7639,18 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5087,22 +7672,20 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1800226</xdr:colOff>
+      <xdr:colOff>1800225</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5153,13 +7736,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>171449</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1451609</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5168,8 +7751,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304799" y="190501"/>
-          <a:ext cx="1280160" cy="361950"/>
+          <a:off x="304799" y="190500"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -5204,6 +7787,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -5213,22 +7818,22 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>847725</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1409700</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>114078</xdr:rowOff>
+      <xdr:rowOff>104553</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$D$2">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
+        <xdr:cNvPr id="12" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="228600"/>
+          <a:off x="981075" y="219075"/>
           <a:ext cx="561975" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5258,19 +7863,156 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{6831FE4E-352E-4F7B-A3D4-680EF38773CC}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
               <a:solidFill>
-                <a:srgbClr val="51FF21"/>
+                <a:srgbClr val="27F959"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
-              <a:srgbClr val="51FF21"/>
+              <a:srgbClr val="27F959"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>847724</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32808</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1400175</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>108786</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="981074" y="413808"/>
+          <a:ext cx="552451" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27519</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1419226</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>113744</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="971550" y="599019"/>
+          <a:ext cx="581026" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>1</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -5285,22 +8027,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.33503</cdr:x>
+      <cdr:y>0.4149</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.70558</cdr:x>
+      <cdr:y>0.73808</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="602111" y="1142827"/>
-          <a:ext cx="1020535" cy="1131157"/>
+          <a:off x="628650" y="904875"/>
+          <a:ext cx="695325" cy="704850"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5426,17 +8168,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{CE425BBE-7C02-4C07-B111-60BA1CB56900}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5446,29 +8188,6 @@
     </cdr:sp>
   </cdr:relSizeAnchor>
 </c:userShapes>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Dashboard"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="Tags"/>
-      <sheetName val="Features"/>
-      <sheetName val="Exceptions"/>
-      <sheetName val="DB Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5758,7 +8477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B19:G63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="2.0"/>
@@ -5769,8 +8488,119 @@
     <col min="6" max="6" customWidth="true" width="70.7109375"/>
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
-  <sheetData/>
-  <sheetProtection sheet="true" password="E2F3" scenarios="true" objects="true"/>
+  <sheetData>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="6"/>
+    </row>
+    <row r="37" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="61" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B61" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="38"/>
+      <c r="G62" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" s="49"/>
+      <c r="D63" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="49"/>
+      <c r="G63" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="95CD" scenarios="true" objects="true"/>
+  <mergeCells count="9">
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="E63:F63"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5779,94 +8609,97 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B20:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.42578125"/>
-    <col min="2" max="2" customWidth="true" width="45.85546875"/>
+    <col min="2" max="2" customWidth="true" width="50.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
     <col min="5" max="5" customWidth="true" width="50.7109375"/>
-    <col min="6" max="6" customWidth="true" width="12.7109375"/>
+    <col min="6" max="6" customWidth="true" width="12.85546875"/>
     <col min="7" max="10" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>43</v>
+      <c r="J21" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="57" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H22" s="58" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="60"/>
+      <c r="B22" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="50" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H22" s="55" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5876,104 +8709,141 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B20:I27"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="B20:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
-    <col min="2" max="2" customWidth="true" width="35.5703125"/>
+    <col min="2" max="2" customWidth="true" width="35.7109375"/>
     <col min="3" max="7" customWidth="true" width="12.7109375"/>
     <col min="8" max="8" customWidth="true" width="60.7109375"/>
     <col min="9" max="9" customWidth="true" width="18.7109375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="15.5703125"/>
   </cols>
   <sheetData>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
+      <c r="B20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="45"/>
-      <c r="C21" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>45</v>
+      <c r="B21" s="41"/>
+      <c r="C21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" t="s" s="54">
-        <v>58</v>
-      </c>
-      <c r="C22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D22" s="58" t="n">
+      <c r="D22" s="55"/>
+      <c r="E22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="61" t="s">
-        <v>54</v>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="49" t="s">
+    <row r="23">
+      <c r="B23" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="55"/>
+      <c r="E23" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="36" t="s">
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="35" t="s">
-        <v>22</v>
+      <c r="I27" s="34" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" s="55" t="s">
-        <v>29</v>
+    <row r="28">
+      <c r="B28" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C26:G26"/>
     <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5983,6 +8853,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B18:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5990,107 +8861,108 @@
     <col min="2" max="2" customWidth="true" width="60.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
-    <col min="5" max="11" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" customWidth="true" width="12.7109375"/>
+    <col min="5" max="13" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="4"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
+    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>43</v>
+      <c r="H21" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="F22" s="58" t="n">
+      <c r="F22" s="55"/>
+      <c r="G22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="G22" s="59"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="57" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="K22" s="58" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="50" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K22" s="55" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="J20:M20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
-    <mergeCell ref="J20:M20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6098,10 +8970,70 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="1.7109375"/>
+    <col min="2" max="3" customWidth="true" width="30.7109375"/>
+    <col min="4" max="4" customWidth="true" width="45.7109375"/>
+    <col min="5" max="5" customWidth="true" width="75.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="C121" scenarios="true" objects="true"/>
+  <mergeCells count="2">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.7109375"/>
@@ -6109,7 +9041,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" width="16.42578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="16.28515625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="3.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.5703125"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
     <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="22.42578125"/>
@@ -6137,25 +9069,21 @@
         <v>1</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="D2" s="0"/>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="F2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="F2" s="0"/>
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -6163,68 +9091,71 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D3" s="0"/>
-      <c r="E3" t="s">
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="F3"/>
-      <c r="G3" t="s">
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="H3"/>
+      <c r="H3" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s" s="0">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D4" s="0"/>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F4"/>
-      <c r="G4" t="s">
+      <c r="F4" s="0"/>
+      <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" s="0"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n" s="0">
-        <f>SUM(D2:D4)</f>
         <v>1.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n" s="0">
-        <f>SUM(F2:F4)</f>
         <v>1.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <f>SUM(H2:H4)</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6232,32 +9163,128 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>54</v>
+        <v>69</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s" s="49">
+        <v>72</v>
+      </c>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="H20" t="s" s="49">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L20" s="50"/>
+      <c r="P20" t="s" s="49">
+        <v>75</v>
+      </c>
+      <c r="Q20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="R20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="S20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T20" s="50"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="50"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="81">
   <si>
     <t>Duration</t>
   </si>
@@ -229,25 +229,22 @@
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>Feb 06, 2026 10:43:02 AM</t>
+    <t>Feb 10, 2026 2:04:24 pm</t>
   </si>
   <si>
-    <t>Feb 06, 2026 10:41:44 AM</t>
+    <t>Feb 10, 2026 2:03:02 pm</t>
   </si>
   <si>
-    <t>Feb 06, 2026 10:43:00 AM</t>
+    <t>Feb 10, 2026 2:04:23 pm</t>
   </si>
   <si>
-    <t>1 m 16.602 s</t>
+    <t>1 m 20.301 s</t>
   </si>
   <si>
     <t>0%</t>
   </si>
   <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>@TC_UI_Admin_OEV_01</t>
+    <t>@TC_UI_Admin_OEV_13</t>
   </si>
   <si>
     <t>@Mail</t>
@@ -256,93 +253,147 @@
     <t>Verify Order Email Flow</t>
   </si>
   <si>
-    <t>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</t>
+    <t>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</t>
   </si>
   <si>
-    <t>1 m 15.719 s</t>
+    <t>1 m 19.554 s</t>
   </si>
   <si>
-    <t>1 m 15.728 s</t>
+    <t>1 m 19.560 s</t>
   </si>
   <si>
-    <t>When Order confirmation email should be received for order placed, order shipped, order delivered.</t>
+    <t>Given User subscribes to the newsletter and verifies that the newsletter email is received.</t>
   </si>
   <si>
-    <t xml:space="preserve">org.openqa.selenium.NoSuchWindowException: no such window: target window already closed
-from unknown error: web view not found
-  (Session info: chrome=144.0.7559.110)
+    <t xml:space="preserve">org.openqa.selenium.remote.UnreachableBrowserException: Error communicating with the remote browser. It may have died.
 Build info: version: '4.34.0', revision: '707dcb4246*'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.6'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Command: [6c2dd4389e88820d450c8ad7b752fcc2, findElements {value=//table//tr//span[@class='bog']/span, using=xpath}]
-Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.110, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62452}, goog:processID: 1168, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62452/devtoo..., se:cdpVersion: 144.0.7559.110, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 6c2dd4389e88820d450c8ad7b752fcc2
-	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
-	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
-	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
-	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
-	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
-	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
-	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
-	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
-	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
-	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
-	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
-	at org.openqa.selenium.remote.ElementLocation$ElementFinder$2.findElements(ElementLocation.java:182)
-	at org.openqa.selenium.remote.ElementLocation.findElements(ElementLocation.java:103)
-	at org.openqa.selenium.remote.RemoteWebDriver.findElements(RemoteWebDriver.java:380)
-	at org.openqa.selenium.remote.RemoteWebDriver.findElements(RemoteWebDriver.java:374)
-	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke0(Native Method)
-	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke(NativeMethodAccessorImpl.java:62)
-	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
-	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+Command: [0022e91efb72461974c4a534aba8bb50, findElement [value, using]]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.133, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\GOWTHA~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55205}, goog:processID: 15904, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55205/devtoo..., se:cdpVersion: 144.0.7559.133, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 0022e91efb72461974c4a534aba8bb50
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:571)
+	at org.openqa.selenium.remote.ElementLocation$ElementFinder$2.findElement(ElementLocation.java:165)
+	at org.openqa.selenium.remote.ElementLocation.findElement(ElementLocation.java:59)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:367)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:361)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
 	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
 	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
 	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
-	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$sEA650lj.findElements(Unknown Source)
-	at pages.AdminEmailVerifyOrderFlowPage.verifyOrderConfirmationMail(AdminEmailVerifyOrderFlowPage.java:430)
-	at pages.AdminEmailVerifyOrderFlowPage.verifyOrderPlacedEmail(AdminEmailVerifyOrderFlowPage.java:2694)
-	at stepDef.AdminEmailVerifyOrderFlowStepDef.order_confirmation_email_should_be_received_for_order_placed_order_shipped_order_delivered(AdminEmailVerifyOrderFlowStepDef.java:26)
-	at ✽.Order confirmation email should be received for order placed, order shipped, order delivered.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever32/src/test/resources/features/AdminFeature/emailVerify.feature:7)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$IPahEkQi.findElement(Unknown Source)
+	at org.openqa.selenium.support.pagefactory.DefaultElementLocator.findElement(DefaultElementLocator.java:68)
+	at org.openqa.selenium.support.pagefactory.internal.LocatingElementHandler.invoke(LocatingElementHandler.java:38)
+	at jdk.proxy2/jdk.proxy2.$Proxy50.isDisplayed(Unknown Source)
+	at org.openqa.selenium.support.ui.ExpectedConditions.elementIfVisible(ExpectedConditions.java:304)
+	at org.openqa.selenium.support.ui.ExpectedConditions$10.apply(ExpectedConditions.java:290)
+	at org.openqa.selenium.support.ui.ExpectedConditions$10.apply(ExpectedConditions.java:287)
+	at org.openqa.selenium.support.ui.ExpectedConditions$23.apply(ExpectedConditions.java:656)
+	at org.openqa.selenium.support.ui.ExpectedConditions$23.apply(ExpectedConditions.java:652)
+	at org.openqa.selenium.support.ui.FluentWait.until(FluentWait.java:203)
+	at pages.AdminEmailVerifyOrderFlowPage.openTheNewsletterSubscribesInAdminPanel(AdminEmailVerifyOrderFlowPage.java:2721)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyNewLettermail(AdminEmailVerifyOrderFlowPage.java:3179)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.user_subscribes_to_the_newsletter_and_verifies_that_the_newsletter_email_is_received(AdminEmailVerifyOrderFlowStepDef.java:122)
+	at ✽.User subscribes to the newsletter and verifies that the newsletter email is received.(file:///C:/Users/gowthamraj/git/ZlaataQAsevernee/src/test/resources/features/AdminFeature/emailVerify.feature:123)
+Caused by: java.io.UncheckedIOException: java.io.IOException: HTTP/1.1 header parser received no bytes
+	at org.openqa.selenium.remote.http.jdk.JdkHttpClient.execute0(JdkHttpClient.java:500)
+	at org.openqa.selenium.remote.http.AddSeleniumUserAgent.lambda$apply$0(AddSeleniumUserAgent.java:42)
+	at org.openqa.selenium.remote.http.Filter.lambda$andFinally$1(Filter.java:55)
+	at org.openqa.selenium.remote.http.jdk.JdkHttpClient.lambda$executeAsync$2(JdkHttpClient.java:387)
+	at java.base/java.util.concurrent.Executors$RunnableAdapter.call(Executors.java:572)
+	at java.base/java.util.concurrent.FutureTask.run(FutureTask.java:317)
+	at java.base/java.util.concurrent.ThreadPoolExecutor.runWorker(ThreadPoolExecutor.java:1144)
+	at java.base/java.util.concurrent.ThreadPoolExecutor$Worker.run(ThreadPoolExecutor.java:642)
+	at java.base/java.lang.Thread.run(Thread.java:1583)
+Caused by: java.io.IOException: HTTP/1.1 header parser received no bytes
+	at java.net.http/jdk.internal.net.http.HttpClientImpl.send(HttpClientImpl.java:966)
+	at java.net.http/jdk.internal.net.http.HttpClientFacade.send(HttpClientFacade.java:133)
+	at org.openqa.selenium.remote.http.jdk.JdkHttpClient.execute0(JdkHttpClient.java:459)
+	... 8 more
+Caused by: java.io.IOException: HTTP/1.1 header parser received no bytes
+	at java.net.http/jdk.internal.net.http.common.Utils.wrapWithExtraDetail(Utils.java:388)
+	at java.net.http/jdk.internal.net.http.Http1Response$HeadersReader.onReadError(Http1Response.java:590)
+	at java.net.http/jdk.internal.net.http.Http1AsyncReceiver.checkForErrors(Http1AsyncReceiver.java:302)
+	at java.net.http/jdk.internal.net.http.Http1AsyncReceiver.flush(Http1AsyncReceiver.java:268)
+	at java.net.http/jdk.internal.net.http.common.SequentialScheduler$LockingRestartableTask.run(SequentialScheduler.java:182)
+	at java.net.http/jdk.internal.net.http.common.SequentialScheduler$CompleteRestartableTask.run(SequentialScheduler.java:149)
+	at java.net.http/jdk.internal.net.http.common.SequentialScheduler$SchedulableTask.run(SequentialScheduler.java:207)
+	... 3 more
+Caused by: java.net.SocketException: Connection reset
+	at java.base/sun.nio.ch.SocketChannelImpl.throwConnectionReset(SocketChannelImpl.java:401)
+	at java.base/sun.nio.ch.SocketChannelImpl.read(SocketChannelImpl.java:434)
+	at java.net.http/jdk.internal.net.http.SocketTube.readAvailable(SocketTube.java:1178)
+	at java.net.http/jdk.internal.net.http.SocketTube$InternalReadPublisher$InternalReadSubscription.read(SocketTube.java:841)
+	at java.net.http/jdk.internal.net.http.SocketTube$SocketFlowTask.run(SocketTube.java:181)
+	at java.net.http/jdk.internal.net.http.common.SequentialScheduler$SchedulableTask.run(SequentialScheduler.java:207)
+	at java.net.http/jdk.internal.net.http.common.SequentialScheduler.runOrSchedule(SequentialScheduler.java:280)
+	at java.net.http/jdk.internal.net.http.common.SequentialScheduler.runOrSchedule(SequentialScheduler.java:233)
+	at java.net.http/jdk.internal.net.http.SocketTube$InternalReadPublisher$InternalReadSubscription.signalReadable(SocketTube.java:782)
+	at java.net.http/jdk.internal.net.http.SocketTube$InternalReadPublisher$ReadEvent.signalEvent(SocketTube.java:965)
+	at java.net.http/jdk.internal.net.http.SocketTube$SocketFlowEvent.handle(SocketTube.java:253)
+	at java.net.http/jdk.internal.net.http.HttpClientImpl$SelectorManager.handleEvent(HttpClientImpl.java:1469)
+	at java.net.http/jdk.internal.net.http.HttpClientImpl$SelectorManager.lambda$run$3(HttpClientImpl.java:1414)
+	at java.base/java.util.ArrayList.forEach(ArrayList.java:1596)
+	at java.net.http/jdk.internal.net.http.HttpClientImpl$SelectorManager.run(HttpClientImpl.java:1414)
 </t>
   </si>
   <si>
     <t>stepDef.Hooks.tearDown(io.cucumber.java.Scenario)</t>
   </si>
   <si>
-    <t xml:space="preserve">org.openqa.selenium.NoSuchWindowException: no such window: target window already closed
-from unknown error: web view not found
-  (Session info: chrome=144.0.7559.110)
+    <t xml:space="preserve">org.openqa.selenium.remote.UnreachableBrowserException: Error communicating with the remote browser. It may have died.
 Build info: version: '4.34.0', revision: '707dcb4246*'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.6'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Command: [6c2dd4389e88820d450c8ad7b752fcc2, screenshot {}]
-Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.110, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62452}, goog:processID: 1168, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62452/devtoo..., se:cdpVersion: 144.0.7559.110, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 6c2dd4389e88820d450c8ad7b752fcc2
-	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
-	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
-	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
-	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
-	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
-	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
-	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
-	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
-	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
-	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
-	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+Command: [0022e91efb72461974c4a534aba8bb50, screenshot []]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.133, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\GOWTHA~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55205}, goog:processID: 15904, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55205/devtoo..., se:cdpVersion: 144.0.7559.133, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 0022e91efb72461974c4a534aba8bb50
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:571)
 	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:617)
 	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:621)
 	at org.openqa.selenium.remote.RemoteWebDriver.getScreenshotAs(RemoteWebDriver.java:333)
-	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke0(Native Method)
-	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke(NativeMethodAccessorImpl.java:62)
-	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
-	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
 	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
 	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
 	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
-	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$sEA650lj.getScreenshotAs(Unknown Source)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$IPahEkQi.getScreenshotAs(Unknown Source)
 	at utils.ExcelReportUtil.captureScreenshot(ExcelReportUtil.java:68)
 	at stepDef.Hooks.tearDown(Hooks.java:298)
+Caused by: java.io.UncheckedIOException: java.net.ConnectException
+	at org.openqa.selenium.remote.http.jdk.JdkHttpClient.execute0(JdkHttpClient.java:500)
+	at org.openqa.selenium.remote.http.AddSeleniumUserAgent.lambda$apply$0(AddSeleniumUserAgent.java:42)
+	at org.openqa.selenium.remote.http.Filter.lambda$andFinally$1(Filter.java:55)
+	at org.openqa.selenium.remote.http.jdk.JdkHttpClient.lambda$executeAsync$2(JdkHttpClient.java:387)
+	at java.base/java.util.concurrent.Executors$RunnableAdapter.call(Executors.java:572)
+	at java.base/java.util.concurrent.FutureTask.run(FutureTask.java:317)
+	at java.base/java.util.concurrent.ThreadPoolExecutor.runWorker(ThreadPoolExecutor.java:1144)
+	at java.base/java.util.concurrent.ThreadPoolExecutor$Worker.run(ThreadPoolExecutor.java:642)
+	at java.base/java.lang.Thread.run(Thread.java:1583)
+Caused by: java.net.ConnectException
+	at java.net.http/jdk.internal.net.http.HttpClientImpl.send(HttpClientImpl.java:951)
+	at java.net.http/jdk.internal.net.http.HttpClientFacade.send(HttpClientFacade.java:133)
+	at org.openqa.selenium.remote.http.jdk.JdkHttpClient.execute0(JdkHttpClient.java:459)
+	... 8 more
+Caused by: java.net.ConnectException
+	at java.net.http/jdk.internal.net.http.common.Utils.toConnectException(Utils.java:1041)
+	at java.net.http/jdk.internal.net.http.PlainHttpConnection.connectAsync(PlainHttpConnection.java:227)
+	at java.net.http/jdk.internal.net.http.PlainHttpConnection.checkRetryConnect(PlainHttpConnection.java:280)
+	at java.net.http/jdk.internal.net.http.PlainHttpConnection.lambda$connectAsync$2(PlainHttpConnection.java:238)
+	at java.base/java.util.concurrent.CompletableFuture.uniHandle(CompletableFuture.java:934)
+	at java.base/java.util.concurrent.CompletableFuture$UniHandle.tryFire(CompletableFuture.java:911)
+	at java.base/java.util.concurrent.CompletableFuture.postComplete(CompletableFuture.java:510)
+	at java.base/java.util.concurrent.CompletableFuture$AsyncSupply.run(CompletableFuture.java:1773)
+	... 3 more
+Caused by: java.nio.channels.ClosedChannelException
+	at java.base/sun.nio.ch.SocketChannelImpl.ensureOpen(SocketChannelImpl.java:202)
+	at java.base/sun.nio.ch.SocketChannelImpl.beginConnect(SocketChannelImpl.java:786)
+	at java.base/sun.nio.ch.SocketChannelImpl.connect(SocketChannelImpl.java:874)
+	at java.net.http/jdk.internal.net.http.PlainHttpConnection.lambda$connectAsync$1(PlainHttpConnection.java:210)
+	at java.base/java.security.AccessController.doPrivileged(AccessController.java:571)
+	at java.net.http/jdk.internal.net.http.PlainHttpConnection.connectAsync(PlainHttpConnection.java:212)
+	... 9 more
 </t>
   </si>
 </sst>
@@ -947,7 +998,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>@Mail</c:v>
@@ -1018,7 +1069,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>@Mail</c:v>
@@ -1089,7 +1140,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>@Mail</c:v>
@@ -2984,7 +3035,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2992,12 +3043,7 @@
           <c:val>
             <c:numRef>
               <c:f>'DB Data'!$R$20</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3056,7 +3102,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3123,7 +3169,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4102,7 +4148,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4110,12 +4156,7 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$H$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4174,7 +4215,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4241,7 +4282,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4657,7 +4698,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>@Mail</c:v>
@@ -4727,7 +4768,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>@Mail</c:v>
@@ -4797,7 +4838,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>@Mail</c:v>
@@ -8515,15 +8556,15 @@
     </row>
     <row r="39">
       <c r="B39" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39" s="52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D39" s="49"/>
       <c r="E39" s="49"/>
       <c r="F39" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G39" s="53" t="s">
         <v>40</v>
@@ -8531,15 +8572,15 @@
     </row>
     <row r="40">
       <c r="B40" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="52" t="s">
         <v>73</v>
-      </c>
-      <c r="C40" s="52" t="s">
-        <v>74</v>
       </c>
       <c r="D40" s="49"/>
       <c r="E40" s="49"/>
       <c r="F40" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G40" s="53" t="s">
         <v>40</v>
@@ -8576,14 +8617,14 @@
     </row>
     <row r="63">
       <c r="B63" s="52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" s="49"/>
       <c r="D63" s="53" t="s">
         <v>40</v>
       </c>
       <c r="E63" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F63" s="49"/>
       <c r="G63" s="53" t="s">
@@ -8591,7 +8632,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="95CD" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="E211" scenarios="true" objects="true"/>
   <mergeCells count="9">
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="B62:C62"/>
@@ -8670,26 +8711,24 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="50" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H22" s="55" t="n">
         <v>1.0</v>
       </c>
+      <c r="H22" s="55"/>
       <c r="I22" s="56" t="n">
         <v>1.0</v>
       </c>
@@ -8753,7 +8792,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" s="50" t="n">
         <v>1.0</v>
@@ -8769,7 +8808,7 @@
     </row>
     <row r="23">
       <c r="B23" s="51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="50" t="n">
         <v>1.0</v>
@@ -8803,17 +8842,17 @@
     </row>
     <row r="28">
       <c r="B28" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" s="49"/>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
       <c r="G28" s="49"/>
       <c r="H28" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I28" s="53" t="s">
         <v>40</v>
@@ -8821,17 +8860,17 @@
     </row>
     <row r="29">
       <c r="B29" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="52" t="s">
         <v>73</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>74</v>
       </c>
       <c r="D29" s="49"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
       <c r="G29" s="49"/>
       <c r="H29" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I29" s="53" t="s">
         <v>40</v>
@@ -8928,13 +8967,13 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>1.0</v>
@@ -8948,11 +8987,9 @@
         <v>70</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K22" s="55" t="n">
         <v>1.0</v>
       </c>
+      <c r="K22" s="55"/>
       <c r="L22" s="56" t="n">
         <v>1.0</v>
       </c>
@@ -8997,30 +9034,30 @@
     </row>
     <row r="3">
       <c r="B3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="52" t="s">
-        <v>75</v>
-      </c>
       <c r="D3" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="52" t="s">
         <v>78</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
       <c r="D4" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="52" t="s">
         <v>80</v>
-      </c>
-      <c r="E4" s="52" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="C121" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="BC15" scenarios="true" objects="true"/>
   <mergeCells count="2">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -9082,9 +9119,7 @@
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="H2" s="0"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
@@ -9155,7 +9190,7 @@
         <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9172,7 +9207,7 @@
         <v>70</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -9232,7 +9267,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s" s="49">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="50"/>
       <c r="C20" s="50" t="n">
@@ -9240,7 +9275,7 @@
       </c>
       <c r="D20" s="50"/>
       <c r="H20" t="s" s="49">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s" s="49">
         <v>40</v>
@@ -9251,14 +9286,12 @@
       </c>
       <c r="L20" s="50"/>
       <c r="P20" t="s" s="49">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q20" t="s" s="49">
         <v>40</v>
       </c>
-      <c r="R20" s="50" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="R20" s="50"/>
       <c r="S20" s="50" t="n">
         <v>1.0</v>
       </c>
@@ -9266,7 +9299,7 @@
     </row>
     <row r="21">
       <c r="A21" s="49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="50"/>
       <c r="C21" s="50" t="n">

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -13,31 +13,23 @@
     <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" tabRatio="785"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="13" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="14" r:id="rId2"/>
-    <sheet name="Tags" sheetId="18" r:id="rId3"/>
-    <sheet name="Features" sheetId="16" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="11" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="3" r:id="rId2"/>
+    <sheet name="Tags" sheetId="4" r:id="rId3"/>
+    <sheet name="Features" sheetId="2" r:id="rId4"/>
+    <sheet name="Exceptions" sheetId="12" r:id="rId5"/>
     <sheet name="DB Data" sheetId="5" r:id="rId8" state="veryHidden"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="Chart1" localSheetId="3">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="1">Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="2">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1">#REF!</definedName>
-    <definedName name="Chart10">#REF!</definedName>
-    <definedName name="Chart30">#REF!</definedName>
-    <definedName name="Chart49">#REF!</definedName>
-    <definedName name="Chart51">#REF!</definedName>
+    <definedName name="Chart1">Scenarios!#REF!</definedName>
+    <definedName name="Chart51">Scenarios!#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
   <si>
     <t>Duration</t>
   </si>
@@ -96,6 +88,9 @@
     <t>STATUS</t>
   </si>
   <si>
+    <t>FEATURE STATUS</t>
+  </si>
+  <si>
     <t>Features Total</t>
   </si>
   <si>
@@ -111,43 +106,109 @@
     <t>Excel Extent Report</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:16 PM</t>
+    <t>TAG</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:14 PM</t>
+    <t>Scenario Passed</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:15 PM</t>
+    <t>Scenario Failed</t>
   </si>
   <si>
-    <t>0.252 s</t>
+    <t>Scenario Skipped</t>
+  </si>
+  <si>
+    <t>Tag Name</t>
+  </si>
+  <si>
+    <t>Feature Name</t>
+  </si>
+  <si>
+    <t>Feature Status</t>
+  </si>
+  <si>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>Scenario Status</t>
+  </si>
+  <si>
+    <t>Step Passed</t>
+  </si>
+  <si>
+    <t>Step Failed</t>
+  </si>
+  <si>
+    <t>Step Skipped</t>
+  </si>
+  <si>
+    <t>FEATURE FAIL SKIP</t>
+  </si>
+  <si>
+    <t>SCENARIO FAIL SKIP</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>0.013 s</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>0.022 s</t>
+    <t>FAILED &amp; SKIPPED TAGS</t>
   </si>
   <si>
     <t>TAG NAME</t>
   </si>
   <si>
+    <t>FAILED &amp; SKIPPED SCENARIOS</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:11 PM</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:09 PM</t>
+  </si>
+  <si>
+    <t>0.253 s</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>0.015 s</t>
+  </si>
+  <si>
+    <t>0.023 s</t>
+  </si>
+  <si>
+    <t>tag1</t>
+  </si>
+  <si>
     <t>tag</t>
+  </si>
+  <si>
+    <t>STACKTRACE</t>
   </si>
   <si>
     <t>STEP / HOOK TEXT</t>
   </si>
   <si>
-    <t>STACKTRACE</t>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>STEPS</t>
+  </si>
+  <si>
+    <t>SCENARIOS</t>
+  </si>
+  <si>
+    <t>NAME</t>
   </si>
   <si>
     <t>SCENARIO</t>
@@ -156,70 +217,88 @@
     <t>FEATURE</t>
   </si>
   <si>
-    <t>STEPS</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>SCENARIOS</t>
-  </si>
-  <si>
     <t>PASS %</t>
   </si>
   <si>
     <t>AUTHOR NAME</t>
   </si>
   <si>
-    <t>author</t>
+    <t>device</t>
   </si>
   <si>
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>device</t>
+    <t>Feb 16, 2026 10:26:30 AM</t>
   </si>
   <si>
-    <t>Feb 13, 2026 12:20:15 pm</t>
+    <t>Feb 16, 2026 10:23:00 AM</t>
   </si>
   <si>
-    <t>Feb 13, 2026 12:16:13 pm</t>
+    <t>Feb 16, 2026 10:26:29 AM</t>
   </si>
   <si>
-    <t>Feb 13, 2026 12:20:14 pm</t>
+    <t>3 m 29.219 s</t>
   </si>
   <si>
-    <t>4 m 1.731 s</t>
+    <t>0%</t>
   </si>
   <si>
-    <t>100%</t>
+    <t>@Mail</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_CP_20 |Verify the functionality for news letter coupon in User Application.| "TD_UI_Zlaata_CP_20"</t>
+    <t>@TC_UI_Admin_OEV_14</t>
   </si>
   <si>
-    <t>4 m 1.007 s</t>
+    <t>Verify Order Email Flow</t>
   </si>
   <si>
-    <t>Coupon Module</t>
+    <t>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</t>
   </si>
   <si>
-    <t>@gow</t>
+    <t>3 m 28.253 s</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_CP_20</t>
+    <t>3 m 28.261 s</t>
   </si>
   <si>
-    <t>4 m 1.012 s</t>
+    <t>Given the Admin verifies the RTO order flow before the order is delivered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.ElementClickInterceptedException: element click intercepted: Element &lt;span class="mr-1 truncate font-medium" data-testid="Netbanking"&gt;...&lt;/span&gt; is not clickable at point (621, 604). Other element would receive the click: &lt;div class=" mx-auto flex h-16 w-full items-center justify-center bg-gradient-to-t from-surface-25 to-transparent"&gt;...&lt;/div&gt;
+  (Session info: chrome=144.0.7559.133)
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [a682dbd50fe6443cfacd7d9d3ee7cab0, clickElement {id=f.CE7ED2AFA5C296F8DDB9D9641EE61A89.d.9DF3649F1ED7E546346971DB6FB952E6.e.2}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.133, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61793}, goog:processID: 18120, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61793/devtoo..., se:cdpVersion: 144.0.7559.133, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Element: [[ChromeDriver: chrome on windows (a682dbd50fe6443cfacd7d9d3ee7cab0)] -&gt; xpath: //span[@data-testid='Netbanking']]
+Session ID: a682dbd50fe6443cfacd7d9d3ee7cab0
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.RemoteWebElement.execute(RemoteWebElement.java:223)
+	at org.openqa.selenium.remote.RemoteWebElement.click(RemoteWebElement.java:76)
+	at jdk.internal.reflect.GeneratedMethodAccessor91.invoke(Unknown Source)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$aQemIBmi.click(Unknown Source)
+	at pages.AdminEmailVerifyOrderFlowPage.addProductToCartAndPlacedTheOrder(AdminEmailVerifyOrderFlowPage.java:264)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyNormalRTOFlowDelivered(AdminEmailVerifyOrderFlowPage.java:3704)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.the_admin_verifies_the_rto_order_flow_before_the_order_is_delivered(AdminEmailVerifyOrderFlowStepDef.java:128)
+	at ✽.the Admin verifies the RTO order flow before the order is delivered.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:132)
+</t>
   </si>
 </sst>
 </file>
@@ -227,7 +306,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="0"/>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +317,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -287,9 +390,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FF51FF21"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -307,7 +416,7 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FF51FF21"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -320,7 +429,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
-      <color rgb="00FF00"/>
+      <color rgb="FF0000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color rgb="FF0000"/>
       <b val="true"/>
     </font>
     <font>
@@ -348,11 +462,6 @@
       <sz val="11.0"/>
       <b val="true"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="00FF00"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -362,7 +471,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -377,6 +486,43 @@
       <right style="hair">
         <color auto="1"/>
       </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -444,9 +590,7 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
@@ -474,173 +618,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,24 +808,30 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Features</a:t>
+              <a:t>Tags with</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> Failed &amp; Skipped Scenarios</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.1929905820595947E-3"/>
-          <c:y val="5.6284335775106678E-2"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -717,10 +841,719 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11780714910636171"/>
-          <c:y val="8.0818739637467149E-2"/>
-          <c:w val="0.76899981252343452"/>
-          <c:h val="0.87885598708448542"/>
+          <c:x val="2.9880212949228394E-2"/>
+          <c:y val="0.11750877449771498"/>
+          <c:w val="0.95813725490196078"/>
+          <c:h val="0.84734403472530151"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Mail</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_14</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$B$20:$B$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Mail</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_14</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$D$20:$D$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Mail</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_14</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$C$20:$C$21</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46151168"/>
+        <c:axId val="46117248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46151168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46117248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46117248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46151168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.3309046751669701E-2"/>
+          <c:y val="0.10919339164237124"/>
+          <c:w val="0.95333333333333337"/>
+          <c:h val="0.84804664723032075"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$F$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$H$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$H$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$G$22</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46512000"/>
+        <c:axId val="46513536"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46512000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46513536"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46513536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46512000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3310417416097107E-2"/>
+          <c:y val="0.17399131020088515"/>
+          <c:w val="0.93298799578986624"/>
+          <c:h val="0.80271606659122552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -762,7 +1595,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000001-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -787,7 +1620,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000003-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -812,7 +1645,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000005-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -842,12 +1675,18 @@
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CEAE-4775-A1C6-116F718DC196}"/>
+              <c16:uniqueId val="{00000006-D2BC-4951-98B3-E41274AF2CA1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -883,7 +1722,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -909,15 +1748,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Devices</a:t>
+              <a:t>Authors</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -927,10 +1765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -942,7 +1780,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$D$21</c:f>
+              <c:f>Authors!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -977,37 +1815,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$D$22</c:f>
+              <c:f>Authors!$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000000-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1016,7 +1853,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$F$21</c:f>
+              <c:f>Authors!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1051,25 +1888,24 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$F$22</c:f>
+              <c:f>Authors!$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1081,7 +1917,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000001-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1090,7 +1926,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$E$21</c:f>
+              <c:f>Authors!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1125,37 +1961,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$E$22</c:f>
+              <c:f>Authors!$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000002-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1169,11 +2004,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1183,7 +2018,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1191,7 +2026,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1209,7 +2044,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -1217,14 +2052,379 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Devices</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$E$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46589440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46590976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46590976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1278,12 +2478,745 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features with Failed &amp; Skipped</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> Scenarios</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.587826839649571E-2"/>
+          <c:y val="0.10654873856176561"/>
+          <c:w val="0.89369296921336749"/>
+          <c:h val="0.85018673119905308"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$J$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$J$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9F7-4BBB-94B0-AEDC4FA75EC0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$L$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$L$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify Order Email Flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$K$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46193280"/>
+        <c:axId val="46285184"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46193280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46285184"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46285184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46193280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Scenarios</a:t>
+              <a:t>Scenarios with Failed &amp; Skipped Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0031919744642044E-2"/>
+          <c:y val="0.10668158781898149"/>
+          <c:w val="0.92990424076607392"/>
+          <c:h val="0.8499999379835731"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$R$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$R$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$S$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$T$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$T$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$S$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46328448"/>
+        <c:axId val="46408064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46328448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46408064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46408064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Steps</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46328448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Features</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1292,8 +3225,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.9364481457108926E-3"/>
-          <c:y val="3.2123800120282653E-2"/>
+          <c:x val="5.9362468167315514E-3"/>
+          <c:y val="6.4713026203216312E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1305,10 +3238,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.6498186400440001E-2"/>
-          <c:y val="0.10118873685128098"/>
-          <c:w val="0.87710436725913243"/>
-          <c:h val="0.86336406553156542"/>
+          <c:x val="7.3672686824927558E-2"/>
+          <c:y val="0.11902669624860428"/>
+          <c:w val="0.92151704085316477"/>
+          <c:h val="0.85596714084772552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1350,7 +3283,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000001-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1375,7 +3308,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000003-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1400,42 +3333,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000005-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$E$2:$E$4</c:f>
+              <c:f>'DB Data'!$C$2:$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Scenarios Passed</c:v>
+                  <c:v>Features Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Scenarios Failed</c:v>
+                  <c:v>Features Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scenarios Skipped</c:v>
+                  <c:v>Features Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$F$2:$F$4</c:f>
+              <c:f>'DB Data'!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F52A-4A06-BA5F-6C71FCEF3775}"/>
+              <c16:uniqueId val="{00000006-C5E1-437A-A52D-DCB97CB8ED06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1471,7 +3441,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1491,16 +3461,16 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr algn="ctr">
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1800" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Steps</a:t>
+              <a:t>Scenarios</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1509,8 +3479,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.6171728533933258E-3"/>
-          <c:y val="5.4421749273573204E-2"/>
+          <c:x val="5.9107001159738751E-3"/>
+          <c:y val="3.7140215132502832E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1522,10 +3492,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11769966254218223"/>
-          <c:y val="8.4263722654767198E-2"/>
-          <c:w val="0.78142825896762902"/>
-          <c:h val="0.89306054848124394"/>
+          <c:x val="5.6571751205517912E-2"/>
+          <c:y val="8.4536101166436714E-2"/>
+          <c:w val="0.92725874381981321"/>
+          <c:h val="0.88851560210722469"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1567,7 +3537,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000001-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1592,7 +3562,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000003-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1617,42 +3587,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000005-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:f>'DB Data'!$E$2:$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Steps Passed</c:v>
+                  <c:v>Scenarios Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Steps Failed</c:v>
+                  <c:v>Scenarios Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Steps Skipped</c:v>
+                  <c:v>Scenarios Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:f>'DB Data'!$F$2:$F$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-33E3-412A-9233-ED47CE12E57E}"/>
+              <c16:uniqueId val="{00000006-86A0-4454-A31A-15C1830346B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1688,7 +3695,261 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.0163677357506801E-2"/>
+          <c:y val="5.5749128919860627E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.6917458262785006E-2"/>
+          <c:y val="0.10406650388213669"/>
+          <c:w val="0.93302459414795369"/>
+          <c:h val="0.87775832898936412"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d prstMaterial="matte"/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="51FF21"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Steps Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Steps Failed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Steps Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2833-4D5B-98DA-2F8086DE2D67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="40"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId1"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1731,9 +3992,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.3309046751669701E-2"/>
+          <c:x val="3.3278738246891114E-2"/>
           <c:y val="0.10500003204542271"/>
-          <c:w val="0.95333333333333337"/>
+          <c:w val="0.953375796178344"/>
           <c:h val="0.85236429602767994"/>
         </c:manualLayout>
       </c:layout>
@@ -1791,7 +4052,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_CP_20 |Verify the functionality for news letter coupon in User Application.| "TD_UI_Zlaata_CP_20"</c:v>
+                  <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1799,17 +4060,12 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$H$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>4.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000000-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1863,7 +4119,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_CP_20 |Verify the functionality for news letter coupon in User Application.| "TD_UI_Zlaata_CP_20"</c:v>
+                  <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1876,7 +4132,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000002-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1930,7 +4186,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_CP_20 |Verify the functionality for news letter coupon in User Application.| "TD_UI_Zlaata_CP_20"</c:v>
+                  <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1938,12 +4194,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$I$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000001-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1957,11 +4218,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97185152"/>
-        <c:axId val="97201536"/>
+        <c:axId val="89325952"/>
+        <c:axId val="44310528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97185152"/>
+        <c:axId val="89325952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1971,7 +4232,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97201536"/>
+        <c:crossAx val="44310528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1979,7 +4240,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97201536"/>
+        <c:axId val="44310528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2011,7 +4272,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97185152"/>
+        <c:crossAx val="89325952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2040,7 +4301,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2106,7 +4367,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000001-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2131,7 +4392,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000003-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2156,7 +4417,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000005-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2184,14 +4445,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+              <c16:uniqueId val="{00000006-012F-4AE0-9B30-C14C76CB6C4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2212,919 +4479,6 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId1"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Tags</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$D$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>@gow</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_CP_20</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$D$22:$D$23</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>@gow</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_CP_20</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$F$22:$F$23</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$E$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>@gow</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_CP_20</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$E$22:$E$23</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97122176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97123712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Features</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="3.3369832880226151E-2"/>
-          <c:y val="9.72480620155039E-2"/>
-          <c:w val="0.95324817070407986"/>
-          <c:h val="0.8601162790697674"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Coupon Module</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$F$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$H$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Coupon Module</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$H$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$G$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Coupon Module</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$G$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97540352"/>
-        <c:axId val="97550336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97540352"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97550336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97550336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97540352"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-        <c:minorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.3310417416097107E-2"/>
-          <c:y val="0.17399131020088515"/>
-          <c:w val="0.93298799578986624"/>
-          <c:h val="0.80271606659122552"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d prstMaterial="matte"/>
-          </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="51FF21"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'DB Data'!$C$2:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Features Passed</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Features Failed</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Features Skipped</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'DB Data'!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-1678-4457-8DD3-1C4694EC7DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="40"/>
-      </c:doughnutChart>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -3171,15 +4525,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Authors</a:t>
+              <a:t>Tags</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -3189,10 +4542,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -3204,7 +4557,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$D$21</c:f>
+              <c:f>Tags!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3239,37 +4592,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Mail</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$D$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$D$22:$D$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000000-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3278,7 +4627,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$F$21</c:f>
+              <c:f>Tags!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3313,37 +4662,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Mail</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$F$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$F$22:$F$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000001-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3352,7 +4697,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$E$21</c:f>
+              <c:f>Tags!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3387,37 +4732,41 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Mail</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$E$22</c:f>
+              <c:f>Tags!$E$22:$E$23</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000002-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3431,11 +4780,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3445,7 +4794,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3453,7 +4802,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3471,7 +4820,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -3479,14 +4828,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3521,672 +4869,1681 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>43815</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>158115</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190500" y="142875"/>
-          <a:ext cx="3749040" cy="777240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Duration</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828924</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472439</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>127635</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486774" y="142875"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Start Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>165735</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486775" y="561975"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>End Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1019175" y="152401"/>
-          <a:ext cx="2933700" cy="771524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
-            <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>0.252 s</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3790950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9448800" y="142875"/>
-          <a:ext cx="2800350" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:14 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3809999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9467849" y="561975"/>
-          <a:ext cx="2771775" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:15 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
+      <xdr:colOff>57148</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7"/>
+        <xdr:cNvPr id="9" name="Group 8"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="190499" y="28576"/>
-          <a:ext cx="12045316" cy="3657600"/>
-          <a:chOff x="171449" y="36548"/>
-          <a:chExt cx="12045316" cy="3399182"/>
+          <a:off x="190498" y="0"/>
+          <a:ext cx="12068177" cy="3438525"/>
+          <a:chOff x="161923" y="0"/>
+          <a:chExt cx="12068177" cy="3438525"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="9" name="Group 8"/>
+          <xdr:cNvPr id="42" name="Group 41"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="171449" y="815528"/>
-            <a:ext cx="3749040" cy="2620202"/>
-            <a:chOff x="171449" y="815528"/>
-            <a:chExt cx="3749040" cy="2620202"/>
+            <a:off x="161923" y="0"/>
+            <a:ext cx="12068177" cy="3438525"/>
+            <a:chOff x="171448" y="19050"/>
+            <a:chExt cx="12068177" cy="3438525"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="13" name="Group 12"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="8477248" y="133350"/>
+              <a:ext cx="3762377" cy="685800"/>
+              <a:chOff x="8477248" y="133350"/>
+              <a:chExt cx="3762377" cy="685800"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="4" name="Rectangle 3"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477248" y="133350"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0" algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Start Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="5" name="Rectangle 4"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477249" y="495300"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>End Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="TextBox 6"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9563100" y="133351"/>
+                <a:ext cx="2676525" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="8" name="TextBox 7"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9572625" y="495300"/>
+                <a:ext cx="2667000" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="2" name="Group 100"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="171448" y="19050"/>
+              <a:ext cx="12054842" cy="3438525"/>
+              <a:chOff x="171448" y="19050"/>
+              <a:chExt cx="12054842" cy="3438525"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="10" name="Group 9"/>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="171448" y="19050"/>
+                <a:ext cx="12054842" cy="3438525"/>
+                <a:chOff x="152398" y="27696"/>
+                <a:chExt cx="12054842" cy="3195586"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="16" name="Group 15"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="152398" y="656192"/>
+                  <a:ext cx="3749040" cy="2563550"/>
+                  <a:chOff x="152398" y="656192"/>
+                  <a:chExt cx="3749040" cy="2563550"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="31" name="Rectangle 30"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="152398" y="815526"/>
+                    <a:ext cx="3749040" cy="2381198"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:grpSp>
+                <xdr:nvGrpSpPr>
+                  <xdr:cNvPr id="32" name="Group 31"/>
+                  <xdr:cNvGrpSpPr/>
+                </xdr:nvGrpSpPr>
+                <xdr:grpSpPr>
+                  <a:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="3621406" cy="2563550"/>
+                    <a:chOff x="247650" y="656192"/>
+                    <a:chExt cx="3621406" cy="2563550"/>
+                  </a:xfrm>
+                </xdr:grpSpPr>
+                <xdr:grpSp>
+                  <xdr:nvGrpSpPr>
+                    <xdr:cNvPr id="33" name="Group 32"/>
+                    <xdr:cNvGrpSpPr/>
+                  </xdr:nvGrpSpPr>
+                  <xdr:grpSpPr>
+                    <a:xfrm>
+                      <a:off x="2771776" y="859785"/>
+                      <a:ext cx="1097280" cy="764816"/>
+                      <a:chOff x="2771776" y="859785"/>
+                      <a:chExt cx="1097280" cy="764816"/>
+                    </a:xfrm>
+                  </xdr:grpSpPr>
+                  <xdr:sp macro="" textlink="">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="35" name="Rounded Rectangle 34"/>
+                      <xdr:cNvSpPr/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="2771776" y="859785"/>
+                        <a:ext cx="1097280" cy="764816"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="roundRect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:ln w="3175"/>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="2">
+                        <a:schemeClr val="dk1"/>
+                      </a:lnRef>
+                      <a:fillRef idx="1">
+                        <a:schemeClr val="lt1"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:schemeClr val="dk1"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>PASSED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>FAILED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>SKIPPED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>TOTAL</a:t>
+                        </a:r>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$2">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="36" name="TextBox 35"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="868694"/>
+                        <a:ext cx="485775" cy="247651"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="27F959"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="27F959"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$3">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="37" name="TextBox 36"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="1027977"/>
+                        <a:ext cx="485775" cy="251635"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FF0000"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>2</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$4">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="38" name="TextBox 37"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3371850" y="1187314"/>
+                        <a:ext cx="495300" cy="239006"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FFFF00"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FFFF00"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                </xdr:grpSp>
+                <xdr:graphicFrame macro="">
+                  <xdr:nvGraphicFramePr>
+                    <xdr:cNvPr id="34" name="FeatureDough"/>
+                    <xdr:cNvGraphicFramePr>
+                      <a:graphicFrameLocks/>
+                    </xdr:cNvGraphicFramePr>
+                  </xdr:nvGraphicFramePr>
+                  <xdr:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="2562225" cy="2563550"/>
+                  </xdr:xfrm>
+                  <a:graphic>
+                    <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                      <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+                    </a:graphicData>
+                  </a:graphic>
+                </xdr:graphicFrame>
+              </xdr:grpSp>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="17" name="Group 16"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="3981450" y="27696"/>
+                  <a:ext cx="4391026" cy="3177881"/>
+                  <a:chOff x="3981450" y="27696"/>
+                  <a:chExt cx="4391026" cy="3177881"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="25" name="Rectangle 24"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="3981450" y="133921"/>
+                    <a:ext cx="4391026" cy="3059265"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="26" name="Rounded Rectangle 25"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7143750" y="183252"/>
+                    <a:ext cx="1188720" cy="849796"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1600" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="27" name="TextBox 26"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="213640"/>
+                    <a:ext cx="542925" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="28" name="TextBox 27"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="394614"/>
+                    <a:ext cx="542926" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="29" name="TextBox 28"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7781924" y="557888"/>
+                    <a:ext cx="533401" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="30" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="4019551" y="27696"/>
+                  <a:ext cx="3276600" cy="3177881"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="18" name="Group 17"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="8458200" y="682747"/>
+                  <a:ext cx="3749040" cy="2540535"/>
+                  <a:chOff x="8458200" y="682747"/>
+                  <a:chExt cx="3749040" cy="2540535"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="19" name="Rectangle 18"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="8458200" y="815526"/>
+                    <a:ext cx="3749040" cy="2379428"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="20" name="Rounded Rectangle 19"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11077576" y="856008"/>
+                    <a:ext cx="1097280" cy="764816"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1300" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="21" name="TextBox 20"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="859839"/>
+                    <a:ext cx="476250" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{ECACBD74-B5B9-479E-8C2E-C9684999A572}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>6</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="22" name="TextBox 21"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11658600" y="1023110"/>
+                    <a:ext cx="485776" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{E24417FB-CCF3-4060-A9AB-23F9E2CDA81A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="23" name="TextBox 22"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="1177529"/>
+                    <a:ext cx="476250" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{04B0E76C-90E2-4732-8606-78D62C393D8A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="24" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="8572501" y="682747"/>
+                  <a:ext cx="2543174" cy="2540535"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="'DB Data'!$F$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="39" name="TextBox 38"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7791450" y="781050"/>
+                <a:ext cx="542925" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C1C65169-A7E7-4F44-8F1B-A4A10551DED6}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>6</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$D$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="40" name="TextBox 39"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3390900" y="1438275"/>
+                <a:ext cx="495299" cy="257176"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C751D109-05C5-4D27-8561-41C7DB1DFED0}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>4</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1100" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$H$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="41" name="TextBox 40"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="11687174" y="1428750"/>
+                <a:ext cx="476251" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{9404FC27-F618-4129-9790-CCC5E3B452F7}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>8</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="Rectangle 23"/>
+            <xdr:cNvPr id="3" name="Rectangle 2"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="171449" y="952809"/>
-              <a:ext cx="3749040" cy="2464407"/>
+              <a:off x="171450" y="133349"/>
+              <a:ext cx="3749040" cy="685800"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
             <a:noFill/>
-            <a:ln w="6350"/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:ln>
           </xdr:spPr>
           <xdr:style>
             <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
             </a:lnRef>
             <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
+              <a:schemeClr val="accent1"/>
             </a:fillRef>
             <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1"/>
             </a:effectRef>
             <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="lt1"/>
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Duration</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="27" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="419100" y="815528"/>
-            <a:ext cx="3238500" cy="2620202"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
       </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="10" name="Group 9"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
+      <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="TextBox 5"/>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
           <a:xfrm>
-            <a:off x="4000498" y="36548"/>
-            <a:ext cx="4389120" cy="3390329"/>
-            <a:chOff x="4000498" y="36548"/>
-            <a:chExt cx="4389120" cy="3390329"/>
+            <a:off x="990601" y="114300"/>
+            <a:ext cx="2924174" cy="676275"/>
           </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="Rectangle 17"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4000498" y="142772"/>
-              <a:ext cx="4389120" cy="3271713"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
             <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="23" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="4400550" y="36548"/>
-            <a:ext cx="3590925" cy="3390329"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="11" name="Group 10"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="8467725" y="806675"/>
-            <a:ext cx="3749040" cy="2609869"/>
-            <a:chOff x="8467725" y="806675"/>
-            <a:chExt cx="3749040" cy="2609869"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="Rectangle 11"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8467725" y="952137"/>
-              <a:ext cx="3749040" cy="2464407"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="17" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="8734425" y="806675"/>
-            <a:ext cx="3200400" cy="2602499"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
+              <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:pPr algn="ctr"/>
+              <a:t>0.253 s</a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4197,22 +6554,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35</cdr:x>
-      <cdr:y>0.34014</cdr:y>
+      <cdr:x>0.34572</cdr:x>
+      <cdr:y>0.37983</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.65294</cdr:x>
-      <cdr:y>0.69728</cdr:y>
+      <cdr:x>0.72119</cdr:x>
+      <cdr:y>0.71478</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1133475" y="952503"/>
-          <a:ext cx="981075" cy="1000125"/>
+          <a:off x="885825" y="1047749"/>
+          <a:ext cx="962024" cy="923925"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4338,7 +6695,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
+          <a:fld id="{790B2992-122F-4DED-8027-8C90CA641799}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4346,7 +6703,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4364,22 +6721,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.33156</cdr:x>
-      <cdr:y>0.36031</cdr:y>
+      <cdr:x>0.3343</cdr:x>
+      <cdr:y>0.34819</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.68208</cdr:x>
-      <cdr:y>0.70496</cdr:y>
+      <cdr:x>0.7064</cdr:x>
+      <cdr:y>0.70474</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1190625" y="1314450"/>
-          <a:ext cx="1258673" cy="1257300"/>
+          <a:off x="1095367" y="1190625"/>
+          <a:ext cx="1219223" cy="1219200"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4505,17 +6862,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{55E37DD8-520B-4F7A-9381-E422E7073C87}" type="TxLink">
+            <a:rPr lang="en-US" sz="3000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="3600" b="1">
+          <a:endParaRPr lang="en-US" sz="3000" b="1">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -4531,22 +6888,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35119</cdr:x>
-      <cdr:y>0.35374</cdr:y>
+      <cdr:x>0.33708</cdr:x>
+      <cdr:y>0.36934</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.66667</cdr:x>
-      <cdr:y>0.71088</cdr:y>
+      <cdr:x>0.70786</cdr:x>
+      <cdr:y>0.71429</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$H$5">
+    <cdr:sp macro="" textlink="'DB Data'!$H$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1123950" y="990599"/>
-          <a:ext cx="1009650" cy="1000125"/>
+          <a:off x="857253" y="1009650"/>
+          <a:ext cx="942958" cy="942975"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4672,7 +7029,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{31691118-B83C-4A2D-970E-D212AA344C2F}" type="TxLink">
+          <a:fld id="{0C07208B-2D34-4675-9C99-827455C82BF1}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4680,7 +7037,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>75%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4705,16 +7062,14 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4763,15 +7118,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>228601</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1508761</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>1508760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150494</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4780,8 +7135,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="323851" y="180974"/>
-          <a:ext cx="1280160" cy="352426"/>
+          <a:off x="323850" y="180974"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4816,6 +7171,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -4825,13 +7202,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>876300</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1514476</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>104553</xdr:rowOff>
+      <xdr:rowOff>85503</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$F$2">
       <xdr:nvSpPr>
@@ -4840,7 +7217,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="971550" y="219075"/>
+          <a:off x="971550" y="200025"/>
           <a:ext cx="638176" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4870,7 +7247,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{8D92AF4D-37D8-4C38-8EA4-79D629C4A437}" type="TxLink">
+          <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="51FF21"/>
@@ -4878,11 +7255,151 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>2</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23284</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1504950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>99262</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962025" y="404284"/>
+          <a:ext cx="638175" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866776</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1514476</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104219</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962026" y="589494"/>
+          <a:ext cx="647700" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -4897,22 +7414,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.32161</cdr:x>
+      <cdr:y>0.41018</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.68844</cdr:x>
+      <cdr:y>0.71781</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="561975" y="933452"/>
-          <a:ext cx="952500" cy="923924"/>
+          <a:off x="609603" y="914412"/>
+          <a:ext cx="695317" cy="685798"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5038,17 +7555,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{BB53D87E-07A1-498D-A732-07528C1BCE6E}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5067,20 +7584,18 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5102,22 +7617,20 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1800226</xdr:colOff>
+      <xdr:colOff>1800225</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5168,13 +7681,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>171449</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1451609</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5183,8 +7696,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304799" y="190501"/>
-          <a:ext cx="1280160" cy="361950"/>
+          <a:off x="304799" y="190500"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -5219,6 +7732,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -5228,22 +7763,22 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>847725</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1409700</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>114078</xdr:rowOff>
+      <xdr:rowOff>104553</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$D$2">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
+        <xdr:cNvPr id="12" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="228600"/>
+          <a:off x="981075" y="219075"/>
           <a:ext cx="561975" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5273,19 +7808,156 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{6831FE4E-352E-4F7B-A3D4-680EF38773CC}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
               <a:solidFill>
-                <a:srgbClr val="51FF21"/>
+                <a:srgbClr val="27F959"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
-              <a:srgbClr val="51FF21"/>
+              <a:srgbClr val="27F959"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>847724</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32808</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1400175</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>108786</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="981074" y="413808"/>
+          <a:ext cx="552451" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27519</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1419226</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>113744</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="971550" y="599019"/>
+          <a:ext cx="581026" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>1</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -5300,22 +7972,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.33503</cdr:x>
+      <cdr:y>0.4149</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.70558</cdr:x>
+      <cdr:y>0.73808</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="602111" y="1142827"/>
-          <a:ext cx="1020535" cy="1131157"/>
+          <a:off x="628650" y="904875"/>
+          <a:ext cx="695325" cy="704850"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5441,17 +8113,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{CE425BBE-7C02-4C07-B111-60BA1CB56900}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5461,29 +8133,6 @@
     </cdr:sp>
   </cdr:relSizeAnchor>
 </c:userShapes>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Dashboard"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="Tags"/>
-      <sheetName val="Features"/>
-      <sheetName val="Exceptions"/>
-      <sheetName val="DB Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5773,7 +8422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B19:G63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="2.0"/>
@@ -5784,8 +8433,119 @@
     <col min="6" max="6" customWidth="true" width="70.7109375"/>
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
-  <sheetData/>
-  <sheetProtection sheet="true" password="D12B" scenarios="true" objects="true"/>
+  <sheetData>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="6"/>
+    </row>
+    <row r="37" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="61" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B61" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="38"/>
+      <c r="G62" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="49"/>
+      <c r="D63" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="49"/>
+      <c r="G63" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="C973" scenarios="true" objects="true"/>
+  <mergeCells count="9">
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="E63:F63"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5794,94 +8554,95 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B20:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.42578125"/>
-    <col min="2" max="2" customWidth="true" width="45.85546875"/>
+    <col min="2" max="2" customWidth="true" width="50.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
     <col min="5" max="5" customWidth="true" width="50.7109375"/>
-    <col min="6" max="6" customWidth="true" width="12.7109375"/>
+    <col min="6" max="6" customWidth="true" width="12.85546875"/>
     <col min="7" max="10" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>43</v>
+      <c r="J21" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="57" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H22" s="58" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="60"/>
+      <c r="B22" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="55"/>
+      <c r="I22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5891,130 +8652,132 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B20:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
-    <col min="2" max="2" customWidth="true" width="35.5703125"/>
+    <col min="2" max="2" customWidth="true" width="35.7109375"/>
     <col min="3" max="7" customWidth="true" width="12.7109375"/>
     <col min="8" max="8" customWidth="true" width="60.7109375"/>
     <col min="9" max="9" customWidth="true" width="18.7109375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="15.5703125"/>
   </cols>
   <sheetData>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
+      <c r="B20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="45"/>
-      <c r="C21" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>45</v>
+      <c r="B21" s="41"/>
+      <c r="C21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" t="s" s="54">
-        <v>58</v>
-      </c>
-      <c r="C22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D22" s="58" t="n">
+      <c r="D22" s="55"/>
+      <c r="E22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="61" t="s">
-        <v>54</v>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="57" t="n">
+      <c r="B23" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D23" s="58" t="n">
+      <c r="D23" s="55"/>
+      <c r="E23" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E23" s="59"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="61" t="s">
-        <v>54</v>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="49" t="s">
+      <c r="B27" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="36" t="s">
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="35" t="s">
-        <v>22</v>
+      <c r="I27" s="34" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I28" s="55" t="s">
-        <v>29</v>
+      <c r="B28" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I29" s="55" t="s">
-        <v>29</v>
+      <c r="B29" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -6033,6 +8796,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B18:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6040,107 +8804,106 @@
     <col min="2" max="2" customWidth="true" width="60.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
-    <col min="5" max="11" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" customWidth="true" width="12.7109375"/>
+    <col min="5" max="13" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="4"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
+    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>43</v>
+      <c r="H21" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="F22" s="58" t="n">
+      <c r="F22" s="55"/>
+      <c r="G22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="G22" s="59"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="57" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="K22" s="58" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K22" s="55"/>
+      <c r="L22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="J20:M20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
-    <mergeCell ref="J20:M20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6148,10 +8911,56 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="1.7109375"/>
+    <col min="2" max="3" customWidth="true" width="30.7109375"/>
+    <col min="4" max="4" customWidth="true" width="45.7109375"/>
+    <col min="5" max="5" customWidth="true" width="75.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="C6EF" scenarios="true" objects="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.7109375"/>
@@ -6159,7 +8968,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" width="16.42578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="16.28515625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="3.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.5703125"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
     <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="22.42578125"/>
@@ -6187,94 +8996,91 @@
         <v>1</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="D2" s="0"/>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="F2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="F2" s="0"/>
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" t="n" s="0">
-        <v>4.0</v>
-      </c>
+      <c r="H2" s="0"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D3" s="0"/>
-      <c r="E3" t="s">
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="F3"/>
-      <c r="G3" t="s">
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="H3"/>
+      <c r="H3" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s" s="0">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D4" s="0"/>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F4"/>
-      <c r="G4" t="s">
+      <c r="F4" s="0"/>
+      <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" s="0"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n" s="0">
-        <f>SUM(D2:D4)</f>
         <v>1.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n" s="0">
-        <f>SUM(F2:F4)</f>
         <v>1.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <f>SUM(H2:H4)</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6282,32 +9088,126 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>54</v>
+        <v>69</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s" s="49">
+        <v>71</v>
+      </c>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="H20" t="s" s="49">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L20" s="50"/>
+      <c r="P20" t="s" s="49">
+        <v>74</v>
+      </c>
+      <c r="Q20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T20" s="50"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="50"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="136">
   <si>
     <t>Duration</t>
   </si>
@@ -229,51 +229,496 @@
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>Feb 16, 2026 10:26:30 AM</t>
-  </si>
-  <si>
-    <t>Feb 16, 2026 10:23:00 AM</t>
-  </si>
-  <si>
-    <t>Feb 16, 2026 10:26:29 AM</t>
-  </si>
-  <si>
-    <t>3 m 29.219 s</t>
+    <t>Feb 20, 2026 2:56:11 PM</t>
+  </si>
+  <si>
+    <t>Feb 20, 2026 1:49:00 PM</t>
+  </si>
+  <si>
+    <t>Feb 20, 2026 2:56:09 PM</t>
+  </si>
+  <si>
+    <t>67 m 8.231 s</t>
   </si>
   <si>
     <t>0%</t>
   </si>
   <si>
+    <t>53%</t>
+  </si>
+  <si>
+    <t>59%</t>
+  </si>
+  <si>
     <t>@Mail</t>
   </si>
   <si>
+    <t>@TC_UI_Admin_OEV_02</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_03</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_06</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_09</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_11</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_13</t>
+  </si>
+  <si>
     <t>@TC_UI_Admin_OEV_14</t>
   </si>
   <si>
     <t>Verify Order Email Flow</t>
   </si>
   <si>
+    <t>TC_UI_Admin_OEV_02 |Verify emails for cancel Order From User Side and Refund.| "TD_UI_Admin_OEV_02"</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_03 |Verify exchange order email notifications for Exchange, Shipped, and Delivered statuses.| "TD_UI_Admin_OEV_03"</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_06 |Verify that Return Order Cancellation email is received after the user cancels the return order.| "TD_UI_Admin_OEV_06"</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_09 |Verify that Exchange Order Cancelled email is received after the user cancels the exchange product.| "TD_UI_Admin_OEV_09"</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_11 |Verify that Exchange Reiceived Damage State Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_11"</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</t>
+  </si>
+  <si>
     <t>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</t>
   </si>
   <si>
-    <t>3 m 28.253 s</t>
-  </si>
-  <si>
-    <t>3 m 28.261 s</t>
-  </si>
-  <si>
-    <t>Given the Admin verifies the RTO order flow before the order is delivered.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org.openqa.selenium.ElementClickInterceptedException: element click intercepted: Element &lt;span class="mr-1 truncate font-medium" data-testid="Netbanking"&gt;...&lt;/span&gt; is not clickable at point (621, 604). Other element would receive the click: &lt;div class=" mx-auto flex h-16 w-full items-center justify-center bg-gradient-to-t from-surface-25 to-transparent"&gt;...&lt;/div&gt;
-  (Session info: chrome=144.0.7559.133)
+    <t>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</t>
+  </si>
+  <si>
+    <t>4 m 7.677 s</t>
+  </si>
+  <si>
+    <t>1 m 33.280 s</t>
+  </si>
+  <si>
+    <t>6 m 16.139 s</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_04 |Verify return order email notifications for return statuses.| "TD_UI_Admin_OEV_04"</t>
+  </si>
+  <si>
+    <t>5 m 40.410 s</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_05 |Verify emails for Order Cancelled by Admin Side.| "TD_UI_Admin_OEV_05"</t>
+  </si>
+  <si>
+    <t>3 m 31.040 s</t>
+  </si>
+  <si>
+    <t>5 m 10.472 s</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_07 |Verify that Return Order Cancellation email is received after the admin changes the status to Product Received in Damaged State.| "TD_UI_Admin_OEV_07"</t>
+  </si>
+  <si>
+    <t>5 m 2.402 s</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_08 |Verify that Return Order Rejection email is received after the admin changes the status to Rejected with reason Product Not Available.| "TD_UI_Admin_OEV_08"</t>
+  </si>
+  <si>
+    <t>5 m 45.115 s</t>
+  </si>
+  <si>
+    <t>6 m 6.721 s</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_10 |Verify that Exchange Out of Stock Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_10"</t>
+  </si>
+  <si>
+    <t>6 m 0.191 s</t>
+  </si>
+  <si>
+    <t>3 m 13.292 s</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_12 |Verify that Exchange Order Cancellation email is received after the admin cancels the exchange order once it has been shipped.| "TD_UI_Admin_OEV_12"</t>
+  </si>
+  <si>
+    <t>11 m 2.348 s</t>
+  </si>
+  <si>
+    <t>1 m 30.571 s</t>
+  </si>
+  <si>
+    <t>2 m 5.483 s</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_15 |Verify the RTO Order Flow for an exchange order before delivered.| "TD_UI_Admin_OEV_15"</t>
+  </si>
+  <si>
+    <t>1.665 s</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_01</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_04</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_05</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_07</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_08</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_10</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_12</t>
+  </si>
+  <si>
+    <t>@TC_UI_Admin_OEV_15</t>
+  </si>
+  <si>
+    <t>67 m 7.215 s</t>
+  </si>
+  <si>
+    <t>When Order Cancellation Confirmation email should be received for order cancel from user side.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.InvalidArgumentException: invalid argument
+  (Session info: chrome=145.0.7632.76)
 Build info: version: '4.34.0', revision: '707dcb4246*'
 System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
 Driver info: org.openqa.selenium.chrome.ChromeDriver
-Command: [a682dbd50fe6443cfacd7d9d3ee7cab0, clickElement {id=f.CE7ED2AFA5C296F8DDB9D9641EE61A89.d.9DF3649F1ED7E546346971DB6FB952E6.e.2}]
-Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 144.0.7559.133, chrome: {chromedriverVersion: 144.0.7559.133 (7da823b1d59..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61793}, goog:processID: 18120, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61793/devtoo..., se:cdpVersion: 144.0.7559.133, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Element: [[ChromeDriver: chrome on windows (a682dbd50fe6443cfacd7d9d3ee7cab0)] -&gt; xpath: //span[@data-testid='Netbanking']]
-Session ID: a682dbd50fe6443cfacd7d9d3ee7cab0
+Command: [ff4ff241342a56407e327a10dc28b19f, get {url=Na}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 145.0.7632.76, chrome: {chromedriverVersion: 145.0.7632.77 (da516187054a..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55833}, goog:processID: 3120, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55833/devtoo..., se:cdpVersion: 145.0.7632.76, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: ff4ff241342a56407e327a10dc28b19f
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.RemoteWebDriver.get(RemoteWebDriver.java:312)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke0(Native Method)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke(NativeMethodAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$5DKSD2UO.get(Unknown Source)
+	at pages.AdminEmailVerifyOrderFlowPage.orderRefundInitiateByAdmin(AdminEmailVerifyOrderFlowPage.java:947)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyOrderCancellationEmailFromUserSide(AdminEmailVerifyOrderFlowPage.java:3591)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.order_cancellation_confirmation_email_should_be_received_for_order_cancel_from_user_side(AdminEmailVerifyOrderFlowStepDef.java:39)
+	at ✽.Order Cancellation Confirmation email should be received for order cancel from user side.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:17)
+</t>
+  </si>
+  <si>
+    <t>When Admin accepts the exchange request, the Order Exchange email should be received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">java.lang.AssertionError: ORDER LABEL MISMATCH → UI: Exchange Delivered | Expected: Exchange Order Delivered
+	at org.junit.Assert.fail(Assert.java:89)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyOrderLabelforExchange(AdminEmailVerifyOrderFlowPage.java:2662)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyOrderExchangeAllEmail(AdminEmailVerifyOrderFlowPage.java:3632)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.admin_accepts_the_exchange_request_the_order_exchange_email_should_be_received(AdminEmailVerifyOrderFlowStepDef.java:54)
+	at ✽.Admin accepts the exchange request, the Order Exchange email should be received.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:28)
+</t>
+  </si>
+  <si>
+    <t>Given User cancels the return order, the Return Order Cancellation email should be received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.TimeoutException: Expected condition failed: waiting for element to be clickable: Proxy element for: DefaultElementLocator 'By.xpath: //a[contains(@class,'view_details_btn') and contains(text(),'View Order Details')]' (tried for 10 second(s) with 500 milliseconds interval)
+	at org.openqa.selenium.support.ui.WebDriverWait.timeoutException(WebDriverWait.java:84)
+	at org.openqa.selenium.support.ui.FluentWait.until(FluentWait.java:228)
+	at pages.AdminEmailVerifyOrderFlowPage.returnOrderCancelFromUserSide(AdminEmailVerifyOrderFlowPage.java:1817)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyReurnOrderCancellationEmailFromUserSide(AdminEmailVerifyOrderFlowPage.java:3699)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.user_cancels_the_return_order_the_return_order_cancellation_email_should_be_received(AdminEmailVerifyOrderFlowStepDef.java:84)
+	at ✽.User cancels the return order, the Return Order Cancellation email should be received.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:58)
+Caused by: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//a[contains(@class,'view_details_btn') and contains(text(),'View Order Details')]"}
+  (Session info: chrome=145.0.7632.76)
+For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [405392c3f80f5fe2a21ba5bdb33ff37c, findElement {value=//a[contains(@class,'view_details_btn') and contains(text(),'View Order Details')], using=xpath}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 145.0.7632.76, chrome: {chromedriverVersion: 145.0.7632.77 (da516187054a..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:57010}, goog:processID: 15828, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:57010/devtoo..., se:cdpVersion: 145.0.7632.76, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 405392c3f80f5fe2a21ba5bdb33ff37c
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.ElementLocation$ElementFinder$2.findElement(ElementLocation.java:165)
+	at org.openqa.selenium.remote.ElementLocation.findElement(ElementLocation.java:59)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:367)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:361)
+	at jdk.internal.reflect.GeneratedMethodAccessor89.invoke(Unknown Source)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$MxA9qCwo.findElement(Unknown Source)
+	at org.openqa.selenium.support.pagefactory.DefaultElementLocator.findElement(DefaultElementLocator.java:68)
+	at org.openqa.selenium.support.pagefactory.internal.LocatingElementHandler.invoke(LocatingElementHandler.java:38)
+	at com.sun.proxy.$Proxy50.isDisplayed(Unknown Source)
+	at org.openqa.selenium.support.ui.ExpectedConditions.elementIfVisible(ExpectedConditions.java:304)
+	at org.openqa.selenium.support.ui.ExpectedConditions$10.apply(ExpectedConditions.java:290)
+	at org.openqa.selenium.support.ui.ExpectedConditions$10.apply(ExpectedConditions.java:287)
+	at org.openqa.selenium.support.ui.ExpectedConditions$23.apply(ExpectedConditions.java:656)
+	at org.openqa.selenium.support.ui.ExpectedConditions$23.apply(ExpectedConditions.java:652)
+	at org.openqa.selenium.support.ui.FluentWait.until(FluentWait.java:203)
+	at pages.AdminEmailVerifyOrderFlowPage.returnOrderCancelFromUserSide(AdminEmailVerifyOrderFlowPage.java:1817)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyReurnOrderCancellationEmailFromUserSide(AdminEmailVerifyOrderFlowPage.java:3699)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.user_cancels_the_return_order_the_return_order_cancellation_email_should_be_received(AdminEmailVerifyOrderFlowStepDef.java:84)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke0(Native Method)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke(NativeMethodAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at io.cucumber.java.Invoker.doInvoke(Invoker.java:66)
+	at io.cucumber.java.Invoker.invoke(Invoker.java:24)
+	at io.cucumber.java.AbstractGlueDefinition.invokeMethod(AbstractGlueDefinition.java:47)
+	at io.cucumber.java.JavaStepDefinition.execute(JavaStepDefinition.java:29)
+	at io.cucumber.core.runner.CoreStepDefinition.execute(CoreStepDefinition.java:66)
+	at io.cucumber.core.runner.PickleStepDefinitionMatch.runStep(PickleStepDefinitionMatch.java:63)
+	at io.cucumber.core.runner.ExecutionMode$1.execute(ExecutionMode.java:10)
+	at io.cucumber.core.runner.TestStep.executeStep(TestStep.java:92)
+	at io.cucumber.core.runner.TestStep.run(TestStep.java:64)
+	at io.cucumber.core.runner.PickleStepTestStep.run(PickleStepTestStep.java:51)
+	at io.cucumber.core.runner.TestCase.run(TestCase.java:104)
+	at io.cucumber.core.runner.Runner.runPickle(Runner.java:71)
+	at io.cucumber.junit.PickleRunners$NoStepDescriptions.run(PickleRunners.java:151)
+	at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:135)
+	at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:27)
+	at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+	at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+	at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+	at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+	at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+	at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+	at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+	at io.cucumber.junit.Cucumber.runChild(Cucumber.java:199)
+	at io.cucumber.junit.Cucumber.runChild(Cucumber.java:90)
+	at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+	at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+	at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+	at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+	at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+	at io.cucumber.junit.Cucumber$RunCucumber.evaluate(Cucumber.java:234)
+	at org.junit.internal.runners.statements.RunAfters.evaluate(RunAfters.java:27)
+	at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+	at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+	at org.eclipse.jdt.internal.junit4.runner.JUnit4TestReference.run(JUnit4TestReference.java:93)
+	at org.eclipse.jdt.internal.junit.runner.TestExecution.run(TestExecution.java:40)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:520)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:748)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.run(RemoteTestRunner.java:443)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.main(RemoteTestRunner.java:211)
+</t>
+  </si>
+  <si>
+    <t>Given User cancels the exchange product, the Exchange Order Cancelled email should be received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.TimeoutException: Expected condition failed: waiting for element to be clickable: Proxy element for: DefaultElementLocator 'By.xpath: //a[contains(@class,'view_details_btn') and contains(text(),'View Order Details')]' (tried for 10 second(s) with 500 milliseconds interval)
+	at org.openqa.selenium.support.ui.WebDriverWait.timeoutException(WebDriverWait.java:84)
+	at org.openqa.selenium.support.ui.FluentWait.until(FluentWait.java:228)
+	at pages.AdminEmailVerifyOrderFlowPage.exchangeOrderCancelFromUserSide(AdminEmailVerifyOrderFlowPage.java:2220)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyExchangeOrderCancelEmailFromUserSide(AdminEmailVerifyOrderFlowPage.java:3753)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.user_cancels_the_exchange_product_the_exchange_order_cancelled_email_should_be_received(AdminEmailVerifyOrderFlowStepDef.java:100)
+	at ✽.User cancels the exchange product, the Exchange Order Cancelled email should be received.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:85)
+Caused by: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//a[contains(@class,'view_details_btn') and contains(text(),'View Order Details')]"}
+  (Session info: chrome=145.0.7632.76)
+For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [6a9a53cf4c08f1c831a68b7eb3319ebd, findElement {value=//a[contains(@class,'view_details_btn') and contains(text(),'View Order Details')], using=xpath}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 145.0.7632.76, chrome: {chromedriverVersion: 145.0.7632.77 (da516187054a..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62557}, goog:processID: 19260, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62557/devtoo..., se:cdpVersion: 145.0.7632.76, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 6a9a53cf4c08f1c831a68b7eb3319ebd
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.ElementLocation$ElementFinder$2.findElement(ElementLocation.java:165)
+	at org.openqa.selenium.remote.ElementLocation.findElement(ElementLocation.java:59)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:367)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:361)
+	at jdk.internal.reflect.GeneratedMethodAccessor89.invoke(Unknown Source)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$MRFKXjPk.findElement(Unknown Source)
+	at org.openqa.selenium.support.pagefactory.DefaultElementLocator.findElement(DefaultElementLocator.java:68)
+	at org.openqa.selenium.support.pagefactory.internal.LocatingElementHandler.invoke(LocatingElementHandler.java:38)
+	at com.sun.proxy.$Proxy50.isDisplayed(Unknown Source)
+	at org.openqa.selenium.support.ui.ExpectedConditions.elementIfVisible(ExpectedConditions.java:304)
+	at org.openqa.selenium.support.ui.ExpectedConditions$10.apply(ExpectedConditions.java:290)
+	at org.openqa.selenium.support.ui.ExpectedConditions$10.apply(ExpectedConditions.java:287)
+	at org.openqa.selenium.support.ui.ExpectedConditions$23.apply(ExpectedConditions.java:656)
+	at org.openqa.selenium.support.ui.ExpectedConditions$23.apply(ExpectedConditions.java:652)
+	at org.openqa.selenium.support.ui.FluentWait.until(FluentWait.java:203)
+	at pages.AdminEmailVerifyOrderFlowPage.exchangeOrderCancelFromUserSide(AdminEmailVerifyOrderFlowPage.java:2220)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyExchangeOrderCancelEmailFromUserSide(AdminEmailVerifyOrderFlowPage.java:3753)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.user_cancels_the_exchange_product_the_exchange_order_cancelled_email_should_be_received(AdminEmailVerifyOrderFlowStepDef.java:100)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke0(Native Method)
+	at java.base/jdk.internal.reflect.NativeMethodAccessorImpl.invoke(NativeMethodAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at io.cucumber.java.Invoker.doInvoke(Invoker.java:66)
+	at io.cucumber.java.Invoker.invoke(Invoker.java:24)
+	at io.cucumber.java.AbstractGlueDefinition.invokeMethod(AbstractGlueDefinition.java:47)
+	at io.cucumber.java.JavaStepDefinition.execute(JavaStepDefinition.java:29)
+	at io.cucumber.core.runner.CoreStepDefinition.execute(CoreStepDefinition.java:66)
+	at io.cucumber.core.runner.PickleStepDefinitionMatch.runStep(PickleStepDefinitionMatch.java:63)
+	at io.cucumber.core.runner.ExecutionMode$1.execute(ExecutionMode.java:10)
+	at io.cucumber.core.runner.TestStep.executeStep(TestStep.java:92)
+	at io.cucumber.core.runner.TestStep.run(TestStep.java:64)
+	at io.cucumber.core.runner.PickleStepTestStep.run(PickleStepTestStep.java:51)
+	at io.cucumber.core.runner.TestCase.run(TestCase.java:104)
+	at io.cucumber.core.runner.Runner.runPickle(Runner.java:71)
+	at io.cucumber.junit.PickleRunners$NoStepDescriptions.run(PickleRunners.java:151)
+	at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:135)
+	at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:27)
+	at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+	at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+	at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+	at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+	at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+	at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+	at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+	at io.cucumber.junit.Cucumber.runChild(Cucumber.java:199)
+	at io.cucumber.junit.Cucumber.runChild(Cucumber.java:90)
+	at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+	at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+	at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+	at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+	at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+	at io.cucumber.junit.Cucumber$RunCucumber.evaluate(Cucumber.java:234)
+	at org.junit.internal.runners.statements.RunAfters.evaluate(RunAfters.java:27)
+	at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+	at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+	at org.eclipse.jdt.internal.junit4.runner.JUnit4TestReference.run(JUnit4TestReference.java:93)
+	at org.eclipse.jdt.internal.junit.runner.TestExecution.run(TestExecution.java:40)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:520)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:748)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.run(RemoteTestRunner.java:443)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.main(RemoteTestRunner.java:211)
+</t>
+  </si>
+  <si>
+    <t>Given Admin changes the exchange order status to Product Received Damage State, the Exchange Out of Stock Cancellation email should be received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.TimeoutException: Expected condition failed: waiting for element to be clickable: Decorated {[[ChromeDriver: chrome on windows (5644b2e9f32c4a159cd826d8695e89fa)] -&gt; xpath: //select[@class='form-control order-status']]} (tried for 10 second(s) with 500 milliseconds interval)
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: net.bytebuddy.renamed.java.lang.Object$ByteBuddy$v3czXDLs
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 145.0.7632.76, chrome: {chromedriverVersion: 145.0.7632.77 (da516187054a..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:50810}, goog:processID: 4152, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:50810/devtoo..., se:cdpVersion: 145.0.7632.76, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 5644b2e9f32c4a159cd826d8695e89fa
+	at org.openqa.selenium.support.ui.WebDriverWait.timeoutException(WebDriverWait.java:84)
+	at org.openqa.selenium.support.ui.FluentWait.until(FluentWait.java:228)
+	at pages.AdminEmailVerifyOrderFlowPage.orderStatusShippedToDelivered(AdminEmailVerifyOrderFlowPage.java:731)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyExchangeOrderCancelReceivedDamageStateEmailFromAdminSide(AdminEmailVerifyOrderFlowPage.java:3786)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.admin_changes_the_exchange_order_status_to_product_received_damage_state_the_exchange_out_of_stock_cancellation_email_should_be_received(AdminEmailVerifyOrderFlowStepDef.java:110)
+	at ✽.Admin changes the exchange order status to Product Received Damage State, the Exchange Out of Stock Cancellation email should be received.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:103)
+</t>
+  </si>
+  <si>
+    <t>Given User subscribes to the newsletter and verifies that the newsletter email is received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//input[@role='searchbox']"}
+  (Session info: chrome=145.0.7632.76)
+For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [a9218507d933325318b6b82e1dc0da9f, findElement {value=//input[@role='searchbox'], using=xpath}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 145.0.7632.76, chrome: {chromedriverVersion: 145.0.7632.77 (da516187054a..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61780}, goog:processID: 19024, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61780/devtoo..., se:cdpVersion: 145.0.7632.76, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: a9218507d933325318b6b82e1dc0da9f
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
+	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
+	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:490)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.ElementLocation$ElementFinder$2.findElement(ElementLocation.java:165)
+	at org.openqa.selenium.remote.ElementLocation.findElement(ElementLocation.java:59)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:367)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:361)
+	at jdk.internal.reflect.GeneratedMethodAccessor89.invoke(Unknown Source)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$nG2E6dLW.findElement(Unknown Source)
+	at org.openqa.selenium.support.pagefactory.DefaultElementLocator.findElement(DefaultElementLocator.java:68)
+	at org.openqa.selenium.support.pagefactory.internal.LocatingElementHandler.invoke(LocatingElementHandler.java:38)
+	at com.sun.proxy.$Proxy50.sendKeys(Unknown Source)
+	at pages.AdminEmailVerifyOrderFlowPage.openTheNewsletterSubscribesInAdminPanel(AdminEmailVerifyOrderFlowPage.java:2742)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyNewLettermail(AdminEmailVerifyOrderFlowPage.java:3886)
+	at stepDef.AdminEmailVerifyOrderFlowStepDef.user_subscribes_to_the_newsletter_and_verifies_that_the_newsletter_email_is_received(AdminEmailVerifyOrderFlowStepDef.java:122)
+	at ✽.User subscribes to the newsletter and verifies that the newsletter email is received.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:123)
+</t>
+  </si>
+  <si>
+    <t>Given the Admin verifies the RTO order flow before the order is delivered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.ElementClickInterceptedException: element click intercepted: Element &lt;span data-value="save_and_back"&gt;...&lt;/span&gt; is not clickable at point (370, 721). Other element would receive the click: &lt;span class="phpdebugbar-text"&gt;...&lt;/span&gt;
+  (Session info: chrome=145.0.7632.76)
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '11.0.28'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [55a02b5558ad6c06d921b91336e9cd68, clickElement {id=f.74765E1E0F077A8E97AC95F99D84E89A.d.B1F96EF7974D1D490C80FE37BBF92E5A.e.1065}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 145.0.7632.76, chrome: {chromedriverVersion: 145.0.7632.77 (da516187054a..., userDataDir: C:\Users\SAROJK~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:62842}, goog:processID: 4472, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:62842/devtoo..., se:cdpVersion: 145.0.7632.76, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Element: [[ChromeDriver: chrome on windows (55a02b5558ad6c06d921b91336e9cd68)] -&gt; xpath: //span[@data-value='save_and_back']]
+Session ID: 55a02b5558ad6c06d921b91336e9cd68
 	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance0(Native Method)
 	at java.base/jdk.internal.reflect.NativeConstructorAccessorImpl.newInstance(NativeConstructorAccessorImpl.java:62)
 	at java.base/jdk.internal.reflect.DelegatingConstructorAccessorImpl.newInstance(DelegatingConstructorAccessorImpl.java:45)
@@ -287,15 +732,21 @@
 	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
 	at org.openqa.selenium.remote.RemoteWebElement.execute(RemoteWebElement.java:223)
 	at org.openqa.selenium.remote.RemoteWebElement.click(RemoteWebElement.java:76)
-	at jdk.internal.reflect.GeneratedMethodAccessor91.invoke(Unknown Source)
+	at jdk.internal.reflect.GeneratedMethodAccessor95.invoke(Unknown Source)
 	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
 	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
 	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
 	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
 	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
-	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$aQemIBmi.click(Unknown Source)
-	at pages.AdminEmailVerifyOrderFlowPage.addProductToCartAndPlacedTheOrder(AdminEmailVerifyOrderFlowPage.java:264)
-	at pages.AdminEmailVerifyOrderFlowPage.verifyNormalRTOFlowDelivered(AdminEmailVerifyOrderFlowPage.java:3704)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$yvL5dnQs.click(Unknown Source)
+	at jdk.internal.reflect.GeneratedMethodAccessor95.invoke(Unknown Source)
+	at java.base/jdk.internal.reflect.DelegatingMethodAccessorImpl.invoke(DelegatingMethodAccessorImpl.java:43)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:566)
+	at org.openqa.selenium.support.pagefactory.internal.LocatingElementHandler.invoke(LocatingElementHandler.java:51)
+	at com.sun.proxy.$Proxy50.click(Unknown Source)
+	at objectRepo.AdminEmailVerifyOrderFlowObjRepo.click(AdminEmailVerifyOrderFlowObjRepo.java:22)
+	at pages.AdminEmailVerifyOrderFlowPage.updateOrderStatusToShipped(AdminEmailVerifyOrderFlowPage.java:660)
+	at pages.AdminEmailVerifyOrderFlowPage.verifyNormalRTOFlowDelivered(AdminEmailVerifyOrderFlowPage.java:3827)
 	at stepDef.AdminEmailVerifyOrderFlowStepDef.the_admin_verifies_the_rto_order_flow_before_the_order_is_delivered(AdminEmailVerifyOrderFlowStepDef.java:128)
 	at ✽.the Admin verifies the RTO order flow before the order is delivered.(file:///C:/Users/Sarojkumar/git/ZlaataQAsever33/src/test/resources/features/AdminFeature/emailVerify.feature:132)
 </t>
@@ -306,7 +757,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="0"/>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,6 +891,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
+      <color rgb="00FF00"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
       <i val="true"/>
     </font>
     <font>
@@ -461,6 +918,11 @@
       <name val="Calibri"/>
       <sz val="11.0"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color rgb="00FF00"/>
     </font>
   </fonts>
   <fills count="2">
@@ -618,7 +1080,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -749,7 +1211,7 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true" horizontal="center"/>
+      <alignment vertical="top" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
@@ -759,6 +1221,12 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -898,13 +1366,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:f>'DB Data'!$A$20:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>@Mail</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>@TC_UI_Admin_OEV_03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>@TC_UI_Admin_OEV_06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>@TC_UI_Admin_OEV_09</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>@TC_UI_Admin_OEV_11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>@TC_UI_Admin_OEV_14</c:v>
                 </c:pt>
               </c:strCache>
@@ -912,8 +1398,13 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$B$20:$B$21</c:f>
-              <c:numCache/>
+              <c:f>'DB Data'!$B$20:$B$27</c:f>
+              <c:numCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>8.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -969,13 +1460,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:f>'DB Data'!$A$20:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>@Mail</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>@TC_UI_Admin_OEV_03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>@TC_UI_Admin_OEV_06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>@TC_UI_Admin_OEV_09</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>@TC_UI_Admin_OEV_11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>@TC_UI_Admin_OEV_14</c:v>
                 </c:pt>
               </c:strCache>
@@ -983,7 +1492,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$D$20:$D$21</c:f>
+              <c:f>'DB Data'!$D$20:$D$27</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -1040,13 +1549,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:f>'DB Data'!$A$20:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>@Mail</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>@TC_UI_Admin_OEV_02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>@TC_UI_Admin_OEV_03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>@TC_UI_Admin_OEV_06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>@TC_UI_Admin_OEV_09</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>@TC_UI_Admin_OEV_11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>@TC_UI_Admin_OEV_14</c:v>
                 </c:pt>
               </c:strCache>
@@ -1054,13 +1581,31 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$C$20:$C$21</c:f>
+              <c:f>'DB Data'!$C$20:$C$27</c:f>
               <c:numCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
+                  <c:v>7.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1.0</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1285,7 +1830,12 @@
           <c:val>
             <c:numRef>
               <c:f>Features!$F$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -1422,7 +1972,7 @@
               <c:numCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.0</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2584,7 +3134,12 @@
           <c:val>
             <c:numRef>
               <c:f>'DB Data'!$J$20</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -2721,7 +3276,7 @@
               <c:numCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.0</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2935,10 +3490,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$P$20</c:f>
+              <c:f>'DB Data'!$P$20:$P$26</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_02 |Verify emails for cancel Order From User Side and Refund.| "TD_UI_Admin_OEV_02"</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TC_UI_Admin_OEV_03 |Verify exchange order email notifications for Exchange, Shipped, and Delivered statuses.| "TD_UI_Admin_OEV_03"</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>TC_UI_Admin_OEV_06 |Verify that Return Order Cancellation email is received after the user cancels the return order.| "TD_UI_Admin_OEV_06"</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TC_UI_Admin_OEV_09 |Verify that Exchange Order Cancelled email is received after the user cancels the exchange product.| "TD_UI_Admin_OEV_09"</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TC_UI_Admin_OEV_11 |Verify that Exchange Reiceived Damage State Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_11"</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
                 </c:pt>
               </c:strCache>
@@ -2946,8 +3519,16 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$R$20</c:f>
-              <c:numCache/>
+              <c:f>'DB Data'!$R$20:$R$26</c:f>
+              <c:numCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3002,10 +3583,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$P$20</c:f>
+              <c:f>'DB Data'!$P$20:$P$26</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_02 |Verify emails for cancel Order From User Side and Refund.| "TD_UI_Admin_OEV_02"</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TC_UI_Admin_OEV_03 |Verify exchange order email notifications for Exchange, Shipped, and Delivered statuses.| "TD_UI_Admin_OEV_03"</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>TC_UI_Admin_OEV_06 |Verify that Return Order Cancellation email is received after the user cancels the return order.| "TD_UI_Admin_OEV_06"</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TC_UI_Admin_OEV_09 |Verify that Exchange Order Cancelled email is received after the user cancels the exchange product.| "TD_UI_Admin_OEV_09"</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TC_UI_Admin_OEV_11 |Verify that Exchange Reiceived Damage State Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_11"</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
                 </c:pt>
               </c:strCache>
@@ -3013,8 +3612,16 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$T$20</c:f>
-              <c:numCache/>
+              <c:f>'DB Data'!$T$20:$T$26</c:f>
+              <c:numCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3069,10 +3676,28 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$P$20</c:f>
+              <c:f>'DB Data'!$P$20:$P$26</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_02 |Verify emails for cancel Order From User Side and Refund.| "TD_UI_Admin_OEV_02"</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TC_UI_Admin_OEV_03 |Verify exchange order email notifications for Exchange, Shipped, and Delivered statuses.| "TD_UI_Admin_OEV_03"</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>TC_UI_Admin_OEV_06 |Verify that Return Order Cancellation email is received after the user cancels the return order.| "TD_UI_Admin_OEV_06"</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TC_UI_Admin_OEV_09 |Verify that Exchange Order Cancelled email is received after the user cancels the exchange product.| "TD_UI_Admin_OEV_09"</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TC_UI_Admin_OEV_11 |Verify that Exchange Reiceived Damage State Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_11"</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
                 </c:pt>
               </c:strCache>
@@ -3080,10 +3705,28 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$S$20</c:f>
+              <c:f>'DB Data'!$S$20:$S$26</c:f>
               <c:numCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4048,19 +4691,93 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Scenarios!$B$22</c:f>
+              <c:f>Scenarios!$B$22:$B$36</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TC_UI_Admin_OEV_02 |Verify emails for cancel Order From User Side and Refund.| "TD_UI_Admin_OEV_02"</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>TC_UI_Admin_OEV_03 |Verify exchange order email notifications for Exchange, Shipped, and Delivered statuses.| "TD_UI_Admin_OEV_03"</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TC_UI_Admin_OEV_04 |Verify return order email notifications for return statuses.| "TD_UI_Admin_OEV_04"</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TC_UI_Admin_OEV_05 |Verify emails for Order Cancelled by Admin Side.| "TD_UI_Admin_OEV_05"</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>TC_UI_Admin_OEV_06 |Verify that Return Order Cancellation email is received after the user cancels the return order.| "TD_UI_Admin_OEV_06"</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>TC_UI_Admin_OEV_07 |Verify that Return Order Cancellation email is received after the admin changes the status to Product Received in Damaged State.| "TD_UI_Admin_OEV_07"</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>TC_UI_Admin_OEV_08 |Verify that Return Order Rejection email is received after the admin changes the status to Rejected with reason Product Not Available.| "TD_UI_Admin_OEV_08"</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>TC_UI_Admin_OEV_09 |Verify that Exchange Order Cancelled email is received after the user cancels the exchange product.| "TD_UI_Admin_OEV_09"</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>TC_UI_Admin_OEV_10 |Verify that Exchange Out of Stock Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_10"</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>TC_UI_Admin_OEV_11 |Verify that Exchange Reiceived Damage State Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_11"</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>TC_UI_Admin_OEV_12 |Verify that Exchange Order Cancellation email is received after the admin cancels the exchange order once it has been shipped.| "TD_UI_Admin_OEV_12"</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>TC_UI_Admin_OEV_15 |Verify the RTO Order Flow for an exchange order before delivered.| "TD_UI_Admin_OEV_15"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Scenarios!$H$22</c:f>
-              <c:numCache/>
+              <c:f>Scenarios!$H$22:$H$36</c:f>
+              <c:numCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4115,19 +4832,69 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Scenarios!$B$22</c:f>
+              <c:f>Scenarios!$B$22:$B$36</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TC_UI_Admin_OEV_02 |Verify emails for cancel Order From User Side and Refund.| "TD_UI_Admin_OEV_02"</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>TC_UI_Admin_OEV_03 |Verify exchange order email notifications for Exchange, Shipped, and Delivered statuses.| "TD_UI_Admin_OEV_03"</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TC_UI_Admin_OEV_04 |Verify return order email notifications for return statuses.| "TD_UI_Admin_OEV_04"</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TC_UI_Admin_OEV_05 |Verify emails for Order Cancelled by Admin Side.| "TD_UI_Admin_OEV_05"</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>TC_UI_Admin_OEV_06 |Verify that Return Order Cancellation email is received after the user cancels the return order.| "TD_UI_Admin_OEV_06"</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>TC_UI_Admin_OEV_07 |Verify that Return Order Cancellation email is received after the admin changes the status to Product Received in Damaged State.| "TD_UI_Admin_OEV_07"</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>TC_UI_Admin_OEV_08 |Verify that Return Order Rejection email is received after the admin changes the status to Rejected with reason Product Not Available.| "TD_UI_Admin_OEV_08"</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>TC_UI_Admin_OEV_09 |Verify that Exchange Order Cancelled email is received after the user cancels the exchange product.| "TD_UI_Admin_OEV_09"</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>TC_UI_Admin_OEV_10 |Verify that Exchange Out of Stock Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_10"</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>TC_UI_Admin_OEV_11 |Verify that Exchange Reiceived Damage State Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_11"</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>TC_UI_Admin_OEV_12 |Verify that Exchange Order Cancellation email is received after the admin cancels the exchange order once it has been shipped.| "TD_UI_Admin_OEV_12"</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>TC_UI_Admin_OEV_15 |Verify the RTO Order Flow for an exchange order before delivered.| "TD_UI_Admin_OEV_15"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Scenarios!$J$22</c:f>
-              <c:numCache/>
+              <c:f>Scenarios!$J$22:$J$36</c:f>
+              <c:numCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4182,21 +4949,81 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Scenarios!$B$22</c:f>
+              <c:f>Scenarios!$B$22:$B$36</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>TC_UI_Admin_OEV_02 |Verify emails for cancel Order From User Side and Refund.| "TD_UI_Admin_OEV_02"</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>TC_UI_Admin_OEV_03 |Verify exchange order email notifications for Exchange, Shipped, and Delivered statuses.| "TD_UI_Admin_OEV_03"</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TC_UI_Admin_OEV_04 |Verify return order email notifications for return statuses.| "TD_UI_Admin_OEV_04"</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TC_UI_Admin_OEV_05 |Verify emails for Order Cancelled by Admin Side.| "TD_UI_Admin_OEV_05"</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>TC_UI_Admin_OEV_06 |Verify that Return Order Cancellation email is received after the user cancels the return order.| "TD_UI_Admin_OEV_06"</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>TC_UI_Admin_OEV_07 |Verify that Return Order Cancellation email is received after the admin changes the status to Product Received in Damaged State.| "TD_UI_Admin_OEV_07"</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>TC_UI_Admin_OEV_08 |Verify that Return Order Rejection email is received after the admin changes the status to Rejected with reason Product Not Available.| "TD_UI_Admin_OEV_08"</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>TC_UI_Admin_OEV_09 |Verify that Exchange Order Cancelled email is received after the user cancels the exchange product.| "TD_UI_Admin_OEV_09"</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>TC_UI_Admin_OEV_10 |Verify that Exchange Out of Stock Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_10"</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>TC_UI_Admin_OEV_11 |Verify that Exchange Reiceived Damage State Cancellation email is received after the admin changes the status to Product Out of Stock.| "TD_UI_Admin_OEV_11"</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>TC_UI_Admin_OEV_12 |Verify that Exchange Order Cancellation email is received after the admin cancels the exchange order once it has been shipped.| "TD_UI_Admin_OEV_12"</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>TC_UI_Admin_OEV_13 | Verify that a newsletter email is received after subscribing to the newsletter | "TD_UI_Admin_OEV_13"</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>TC_UI_Admin_OEV_14 |Verify the RTO Order Flow before the order is delivered.| "TD_UI_Admin_OEV_14"</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>TC_UI_Admin_OEV_15 |Verify the RTO Order Flow for an exchange order before delivered.| "TD_UI_Admin_OEV_15"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Scenarios!$I$22</c:f>
+              <c:f>Scenarios!$I$22:$I$36</c:f>
               <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
+                <c:ptCount val="15"/>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4598,22 +5425,93 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
+              <c:f>Tags!$B$22:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>@Mail</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>@TC_UI_Admin_OEV_02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>@TC_UI_Admin_OEV_03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>@TC_UI_Admin_OEV_04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>@TC_UI_Admin_OEV_05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>@TC_UI_Admin_OEV_06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>@TC_UI_Admin_OEV_07</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>@TC_UI_Admin_OEV_08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>@TC_UI_Admin_OEV_09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>@TC_UI_Admin_OEV_10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>@TC_UI_Admin_OEV_11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>@TC_UI_Admin_OEV_12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>@TC_UI_Admin_OEV_14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>@TC_UI_Admin_OEV_15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$D$22:$D$23</c:f>
-              <c:numCache/>
+              <c:f>Tags!$D$22:$D$37</c:f>
+              <c:numCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4668,21 +5566,63 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
+              <c:f>Tags!$B$22:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>@Mail</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>@TC_UI_Admin_OEV_02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>@TC_UI_Admin_OEV_03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>@TC_UI_Admin_OEV_04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>@TC_UI_Admin_OEV_05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>@TC_UI_Admin_OEV_06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>@TC_UI_Admin_OEV_07</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>@TC_UI_Admin_OEV_08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>@TC_UI_Admin_OEV_09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>@TC_UI_Admin_OEV_10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>@TC_UI_Admin_OEV_11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>@TC_UI_Admin_OEV_12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>@TC_UI_Admin_OEV_14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>@TC_UI_Admin_OEV_15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$F$22:$F$23</c:f>
+              <c:f>Tags!$F$22:$F$37</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -4738,27 +5678,87 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
+              <c:f>Tags!$B$22:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
+                  <c:v>@TC_UI_Admin_OEV_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>@Mail</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>@TC_UI_Admin_OEV_02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>@TC_UI_Admin_OEV_03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>@TC_UI_Admin_OEV_04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>@TC_UI_Admin_OEV_05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>@TC_UI_Admin_OEV_06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>@TC_UI_Admin_OEV_07</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>@TC_UI_Admin_OEV_08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>@TC_UI_Admin_OEV_09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>@TC_UI_Admin_OEV_10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>@TC_UI_Admin_OEV_11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>@TC_UI_Admin_OEV_12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>@TC_UI_Admin_OEV_13</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>@TC_UI_Admin_OEV_14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>@TC_UI_Admin_OEV_15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$E$22:$E$23</c:f>
+              <c:f>Tags!$E$22:$E$37</c:f>
               <c:numCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
+                <c:ptCount val="16"/>
+                <c:pt idx="1">
+                  <c:v>7.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1.0</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4902,13 +5902,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>38099</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1095375</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4934,13 +5934,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1181100</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -8422,7 +9422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B19:G63"/>
+  <dimension ref="B19:G81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="2.0"/>
@@ -8460,15 +9460,15 @@
     </row>
     <row r="39">
       <c r="B39" s="51" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C39" s="52" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D39" s="49"/>
       <c r="E39" s="49"/>
       <c r="F39" s="52" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G39" s="53" t="s">
         <v>40</v>
@@ -8476,75 +9476,329 @@
     </row>
     <row r="40">
       <c r="B40" s="51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C40" s="52" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D40" s="49"/>
       <c r="E40" s="49"/>
       <c r="F40" s="52" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G40" s="53" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-    </row>
-    <row r="61" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B61" s="7" t="s">
+    <row r="41">
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="G44" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="G45" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="G47" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="G49" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="G50" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+    </row>
+    <row r="73" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B73" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="36" t="s">
+    <row r="74" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B74" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="38"/>
-      <c r="D62" s="8" t="s">
+      <c r="C74" s="38"/>
+      <c r="D74" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E62" s="36" t="s">
+      <c r="E74" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="F62" s="38"/>
-      <c r="G62" s="8" t="s">
+      <c r="F74" s="38"/>
+      <c r="G74" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" s="49"/>
-      <c r="D63" s="53" t="s">
+    <row r="75">
+      <c r="B75" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="49"/>
+      <c r="D75" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="E63" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="F63" s="49"/>
-      <c r="G63" s="53" t="s">
+      <c r="E75" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F75" s="49"/>
+      <c r="G75" s="53" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="76">
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="F76" s="49"/>
+      <c r="G76" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="49"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="49"/>
+      <c r="E77" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="F77" s="49"/>
+      <c r="G77" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F78" s="49"/>
+      <c r="G78" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="F79" s="49"/>
+      <c r="G79" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="F80" s="49"/>
+      <c r="G80" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="49"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F81" s="49"/>
+      <c r="G81" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="true" password="C973" scenarios="true" objects="true"/>
-  <mergeCells count="9">
+  <sheetProtection sheet="true" password="9B79" scenarios="true" objects="true"/>
+  <mergeCells count="23">
     <mergeCell ref="C38:E38"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="E74:F74"/>
     <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="C40:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="B75:C81"/>
+    <mergeCell ref="D75:D81"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E81:F81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8555,7 +9809,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B20:J22"/>
+  <dimension ref="B20:J36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.42578125"/>
@@ -8615,28 +9869,386 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="54" t="s">
-        <v>75</v>
+        <v>89</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>90</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="50" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H22" s="56" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I22" s="57"/>
+      <c r="J22" s="58"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="50" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H23" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="H22" s="55"/>
-      <c r="I22" s="56" t="n">
+      <c r="I23" s="57" t="n">
         <v>1.0</v>
       </c>
-      <c r="J22" s="57"/>
+      <c r="J23" s="58" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="50" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H24" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I24" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J24" s="58" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="50" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H25" s="56" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="I25" s="57"/>
+      <c r="J25" s="58"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H26" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I26" s="57"/>
+      <c r="J26" s="58"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J27" s="58"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H28" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I28" s="57"/>
+      <c r="J28" s="58"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H29" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I29" s="57"/>
+      <c r="J29" s="58"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H30" s="56"/>
+      <c r="I30" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J30" s="58"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H31" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I31" s="57"/>
+      <c r="J31" s="58"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J32" s="58"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H33" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I33" s="57"/>
+      <c r="J33" s="58"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H34" s="56"/>
+      <c r="I34" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J34" s="58"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H35" s="56"/>
+      <c r="I35" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J35" s="58"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H36" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I36" s="57"/>
+      <c r="J36" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8653,7 +10265,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="B20:I29"/>
+  <dimension ref="B20:I71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
@@ -8696,97 +10308,786 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D22" s="55"/>
-      <c r="E22" s="56" t="n">
+      <c r="D22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="58" t="s">
-        <v>70</v>
+      <c r="E22" s="57"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="59" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="50" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="D23" s="56" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="E23" s="57" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="F23" s="58"/>
+      <c r="G23" s="59" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D23" s="55"/>
-      <c r="E23" s="56" t="n">
+      <c r="D24" s="56"/>
+      <c r="E24" s="57" t="n">
         <v>1.0</v>
       </c>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58" t="s">
+      <c r="F24" s="58"/>
+      <c r="G24" s="59" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>23</v>
+    <row r="25">
+      <c r="B25" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F25" s="58"/>
+      <c r="G25" s="59" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E26" s="57"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="57"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="59" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="I28" s="53" t="s">
-        <v>40</v>
+        <v>76</v>
+      </c>
+      <c r="C28" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D28" s="56"/>
+      <c r="E28" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F28" s="58"/>
+      <c r="G28" s="59" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D29" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E29" s="57"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D30" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E30" s="57"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D31" s="56"/>
+      <c r="E31" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F31" s="58"/>
+      <c r="G31" s="59" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D32" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E32" s="57"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D33" s="56"/>
+      <c r="E33" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F33" s="58"/>
+      <c r="G33" s="59" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D34" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E34" s="57"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D35" s="56"/>
+      <c r="E35" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F35" s="58"/>
+      <c r="G35" s="59" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F36" s="58"/>
+      <c r="G36" s="59" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D37" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E37" s="57"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="I42" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="52" t="s">
+      <c r="C43" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="I43" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I44" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I45" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="I46" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="I47" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="I48" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="I49" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I50" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="I51" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="I52" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="49"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
+      <c r="H53" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="I53" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="49"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="I54" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="I55" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="49"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="I56" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="I57" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="I29" s="53" t="s">
+      <c r="C58" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I58" s="53" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="59">
+      <c r="B59" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I59" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="I60" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D61" s="49"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="I61" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="I62" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="I63" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="C64" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="49"/>
+      <c r="H64" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I64" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="49"/>
+      <c r="H65" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="49"/>
+      <c r="E66" s="49"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="49"/>
+      <c r="H66" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="I66" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49"/>
+      <c r="H67" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="I67" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C68" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="I68" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="I69" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="I70" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="I71" s="54" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="21">
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B43:B57"/>
+    <mergeCell ref="C43:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8871,33 +11172,39 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="54" t="s">
-        <v>76</v>
+      <c r="D22" s="55" t="s">
+        <v>121</v>
       </c>
       <c r="E22" s="50" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F22" s="55"/>
-      <c r="G22" s="56" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H22" s="57"/>
-      <c r="I22" s="58" t="s">
-        <v>70</v>
+        <v>15.0</v>
+      </c>
+      <c r="F22" s="56" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="G22" s="57" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H22" s="58"/>
+      <c r="I22" s="59" t="s">
+        <v>71</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K22" s="55"/>
-      <c r="L22" s="56" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M22" s="57"/>
+        <v>22.0</v>
+      </c>
+      <c r="K22" s="56" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L22" s="57" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="M22" s="58" t="n">
+        <v>2.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8913,7 +11220,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E3"/>
+  <dimension ref="B2:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.7109375"/>
@@ -8938,20 +11245,95 @@
     </row>
     <row r="3">
       <c r="B3" s="52" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="E3" s="52" t="s">
-        <v>78</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="49"/>
+      <c r="C4" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="49"/>
+      <c r="C5" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="49"/>
+      <c r="C6" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="49"/>
+      <c r="C7" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="49"/>
+      <c r="C8" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="49"/>
+      <c r="C9" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="C6EF" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="C20B" scenarios="true" objects="true"/>
+  <mergeCells count="1">
+    <mergeCell ref="B3:B9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -9005,11 +11387,15 @@
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="F2" s="0"/>
+      <c r="F2" t="n" s="0">
+        <v>8.0</v>
+      </c>
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" s="0"/>
+      <c r="H2" t="n" s="0">
+        <v>13.0</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
@@ -9028,13 +11414,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>13</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -9055,7 +11441,9 @@
       <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4" s="0"/>
+      <c r="H4" t="n" s="0">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
@@ -9074,13 +11462,13 @@
         <v>21</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9094,10 +11482,10 @@
         <v>70</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -9157,51 +11545,183 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s" s="49">
-        <v>71</v>
-      </c>
-      <c r="B20" s="50"/>
+        <v>73</v>
+      </c>
+      <c r="B20" s="50" t="n">
+        <v>8.0</v>
+      </c>
       <c r="C20" s="50" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="D20" s="50"/>
       <c r="H20" t="s" s="49">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s" s="49">
         <v>40</v>
       </c>
-      <c r="J20" s="50"/>
+      <c r="J20" s="50" t="n">
+        <v>8.0</v>
+      </c>
       <c r="K20" s="50" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="L20" s="50"/>
       <c r="P20" t="s" s="49">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Q20" t="s" s="49">
         <v>40</v>
       </c>
-      <c r="R20" s="50"/>
+      <c r="R20" s="50" t="n">
+        <v>1.0</v>
+      </c>
       <c r="S20" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="T20" s="50"/>
+      <c r="T20" s="50" t="n">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="49" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B21" s="50"/>
       <c r="C21" s="50" t="n">
         <v>1.0</v>
       </c>
       <c r="D21" s="50"/>
+      <c r="P21" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q21" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="R21" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="S21" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T21" s="50" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D22" s="50"/>
+      <c r="P22" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q22" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="R22" s="50"/>
+      <c r="S22" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T22" s="50"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+      <c r="A23" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="50"/>
+      <c r="P23" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q23" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="R23" s="50"/>
+      <c r="S23" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T23" s="50"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D24" s="50"/>
+      <c r="P24" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q24" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="R24" s="50"/>
+      <c r="S24" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T24" s="50"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="50"/>
+      <c r="P25" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q25" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="R25" s="50"/>
+      <c r="S25" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T25" s="50"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+      <c r="A26" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" s="50"/>
+      <c r="P26" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q26" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T26" s="50"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="50"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -13,31 +13,23 @@
     <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" tabRatio="785"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="13" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="14" r:id="rId2"/>
-    <sheet name="Tags" sheetId="18" r:id="rId3"/>
-    <sheet name="Features" sheetId="16" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="11" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="3" r:id="rId2"/>
+    <sheet name="Tags" sheetId="4" r:id="rId3"/>
+    <sheet name="Features" sheetId="2" r:id="rId4"/>
+    <sheet name="Exceptions" sheetId="12" r:id="rId5"/>
     <sheet name="DB Data" sheetId="5" r:id="rId8" state="veryHidden"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="Chart1" localSheetId="3">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="1">Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="2">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1">#REF!</definedName>
-    <definedName name="Chart10">#REF!</definedName>
-    <definedName name="Chart30">#REF!</definedName>
-    <definedName name="Chart49">#REF!</definedName>
-    <definedName name="Chart51">#REF!</definedName>
+    <definedName name="Chart1">Scenarios!#REF!</definedName>
+    <definedName name="Chart51">Scenarios!#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
   <si>
     <t>Duration</t>
   </si>
@@ -96,6 +88,9 @@
     <t>STATUS</t>
   </si>
   <si>
+    <t>FEATURE STATUS</t>
+  </si>
+  <si>
     <t>Features Total</t>
   </si>
   <si>
@@ -111,43 +106,109 @@
     <t>Excel Extent Report</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:16 PM</t>
+    <t>TAG</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:14 PM</t>
+    <t>Scenario Passed</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:15 PM</t>
+    <t>Scenario Failed</t>
   </si>
   <si>
-    <t>0.252 s</t>
+    <t>Scenario Skipped</t>
+  </si>
+  <si>
+    <t>Tag Name</t>
+  </si>
+  <si>
+    <t>Feature Name</t>
+  </si>
+  <si>
+    <t>Feature Status</t>
+  </si>
+  <si>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>Scenario Status</t>
+  </si>
+  <si>
+    <t>Step Passed</t>
+  </si>
+  <si>
+    <t>Step Failed</t>
+  </si>
+  <si>
+    <t>Step Skipped</t>
+  </si>
+  <si>
+    <t>FEATURE FAIL SKIP</t>
+  </si>
+  <si>
+    <t>SCENARIO FAIL SKIP</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>0.013 s</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>0.022 s</t>
+    <t>FAILED &amp; SKIPPED TAGS</t>
   </si>
   <si>
     <t>TAG NAME</t>
   </si>
   <si>
+    <t>FAILED &amp; SKIPPED SCENARIOS</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:11 PM</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:09 PM</t>
+  </si>
+  <si>
+    <t>0.253 s</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>0.015 s</t>
+  </si>
+  <si>
+    <t>0.023 s</t>
+  </si>
+  <si>
+    <t>tag1</t>
+  </si>
+  <si>
     <t>tag</t>
+  </si>
+  <si>
+    <t>STACKTRACE</t>
   </si>
   <si>
     <t>STEP / HOOK TEXT</t>
   </si>
   <si>
-    <t>STACKTRACE</t>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>STEPS</t>
+  </si>
+  <si>
+    <t>SCENARIOS</t>
+  </si>
+  <si>
+    <t>NAME</t>
   </si>
   <si>
     <t>SCENARIO</t>
@@ -156,70 +217,61 @@
     <t>FEATURE</t>
   </si>
   <si>
-    <t>STEPS</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>SCENARIOS</t>
-  </si>
-  <si>
     <t>PASS %</t>
   </si>
   <si>
     <t>AUTHOR NAME</t>
   </si>
   <si>
-    <t>author</t>
+    <t>device</t>
   </si>
   <si>
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>device</t>
+    <t>Mar 16, 2026 2:42:12 PM</t>
   </si>
   <si>
-    <t>Mar 03, 2026 12:29:09 PM</t>
+    <t>Mar 16, 2026 2:36:32 PM</t>
   </si>
   <si>
-    <t>Mar 03, 2026 12:22:15 PM</t>
+    <t>Mar 16, 2026 2:42:10 PM</t>
   </si>
   <si>
-    <t>Mar 03, 2026 12:29:08 PM</t>
+    <t>5 m 37.944 s</t>
   </si>
   <si>
-    <t>6 m 53.041 s</t>
+    <t>0%</t>
   </si>
   <si>
-    <t>100%</t>
+    <t>@Calculation</t>
   </si>
   <si>
-    <t>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</t>
+    <t>@TC_UI_Zlaata_Calculate_02</t>
   </si>
   <si>
-    <t>6 m 52.163 s</t>
+    <t>Verify product order with Gift Wrap, Coupon, Gift Card, Gift Card Amount and Thread</t>
   </si>
   <si>
-    <t>Verify Order Email Flow</t>
+    <t>TC_UI_Zlaata_Calculate_02 |Verify price breakup for P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread.| "TD_UI_Zlaata_Calculate_02"</t>
   </si>
   <si>
-    <t>@TC_UI_Admin_OEV_01</t>
+    <t>5 m 36.883 s</t>
   </si>
   <si>
-    <t>@Mail</t>
+    <t>5 m 36.892 s</t>
   </si>
   <si>
-    <t>6 m 52.171 s</t>
+    <t>Given User adds Product P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">java.lang.AssertionError: ❌ COUPON DISCOUNT MISMATCH — UI: 0 | CalcFloor: 37 | CalcCeil: 38
+	at org.junit.Assert.fail(Assert.java:89)
+	at pages.Calculation_MyOrder_Page.verifyCouponSplit_P1(Calculation_MyOrder_Page.java:2320)
+	at pages.Calculation_MyOrder_Page.verify_P1_P2_With_GC_C_GW_GCA_T_E(Calculation_MyOrder_Page.java:5391)
+	at stepDef.Calculation_MyOrder_StepDef.user_adds_product_p1_p2_with_gift_wrap_coupon_gift_card_amount_and_thread(Calculation_MyOrder_StepDef.java:29)
+	at ✽.User adds Product P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread(file:///C:/Users/Sarojkumar/git/ZlaataQAsever0/src/test/resources/features/Calculation_MyOrder/Calculation_MyOrder.feature:17)
+</t>
   </si>
 </sst>
 </file>
@@ -227,7 +279,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="0"/>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +290,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -287,9 +363,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FF51FF21"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -307,7 +389,7 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FF51FF21"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -320,7 +402,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
-      <color rgb="00FF00"/>
+      <color rgb="FF0000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color rgb="FF0000"/>
       <b val="true"/>
     </font>
     <font>
@@ -348,11 +435,6 @@
       <sz val="11.0"/>
       <b val="true"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="00FF00"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -362,7 +444,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -377,6 +459,43 @@
       <right style="hair">
         <color auto="1"/>
       </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -444,9 +563,7 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
@@ -474,173 +591,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,24 +781,30 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Features</a:t>
+              <a:t>Tags with</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> Failed &amp; Skipped Scenarios</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.1929905820595947E-3"/>
-          <c:y val="5.6284335775106678E-2"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -717,10 +814,719 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11780714910636171"/>
-          <c:y val="8.0818739637467149E-2"/>
-          <c:w val="0.76899981252343452"/>
-          <c:h val="0.87885598708448542"/>
+          <c:x val="2.9880212949228394E-2"/>
+          <c:y val="0.11750877449771498"/>
+          <c:w val="0.95813725490196078"/>
+          <c:h val="0.84734403472530151"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Calculation</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Calculate_02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$B$20:$B$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Calculation</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Calculate_02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$D$20:$D$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Calculation</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Calculate_02</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$C$20:$C$21</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46151168"/>
+        <c:axId val="46117248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46151168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46117248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46117248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46151168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.3309046751669701E-2"/>
+          <c:y val="0.10919339164237124"/>
+          <c:w val="0.95333333333333337"/>
+          <c:h val="0.84804664723032075"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify product order with Gift Wrap, Coupon, Gift Card, Gift Card Amount and Thread</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$F$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$H$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify product order with Gift Wrap, Coupon, Gift Card, Gift Card Amount and Thread</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$H$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify product order with Gift Wrap, Coupon, Gift Card, Gift Card Amount and Thread</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$G$22</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46512000"/>
+        <c:axId val="46513536"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46512000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46513536"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46513536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46512000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3310417416097107E-2"/>
+          <c:y val="0.17399131020088515"/>
+          <c:w val="0.93298799578986624"/>
+          <c:h val="0.80271606659122552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -762,7 +1568,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000001-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -787,7 +1593,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000003-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -812,7 +1618,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000005-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -842,12 +1648,18 @@
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CEAE-4775-A1C6-116F718DC196}"/>
+              <c16:uniqueId val="{00000006-D2BC-4951-98B3-E41274AF2CA1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -883,7 +1695,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -909,15 +1721,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Devices</a:t>
+              <a:t>Authors</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -927,10 +1738,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -942,7 +1753,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$D$21</c:f>
+              <c:f>Authors!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -977,37 +1788,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$D$22</c:f>
+              <c:f>Authors!$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000000-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1016,7 +1826,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$F$21</c:f>
+              <c:f>Authors!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1051,25 +1861,24 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$F$22</c:f>
+              <c:f>Authors!$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1081,7 +1890,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000001-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1090,7 +1899,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$E$21</c:f>
+              <c:f>Authors!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1125,37 +1934,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$E$22</c:f>
+              <c:f>Authors!$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000002-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1169,11 +1977,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1183,7 +1991,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1191,7 +1999,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1209,7 +2017,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -1217,14 +2025,379 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Devices</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$E$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46589440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46590976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46590976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1278,12 +2451,750 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features with Failed &amp; Skipped</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> Scenarios</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.587826839649571E-2"/>
+          <c:y val="0.10654873856176561"/>
+          <c:w val="0.89369296921336749"/>
+          <c:h val="0.85018673119905308"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$J$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify product order with Gift Wrap, Coupon, Gift Card, Gift Card Amount and Thread</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$J$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9F7-4BBB-94B0-AEDC4FA75EC0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$L$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify product order with Gift Wrap, Coupon, Gift Card, Gift Card Amount and Thread</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$L$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Verify product order with Gift Wrap, Coupon, Gift Card, Gift Card Amount and Thread</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$K$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46193280"/>
+        <c:axId val="46285184"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46193280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46285184"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46285184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46193280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Scenarios</a:t>
+              <a:t>Scenarios with Failed &amp; Skipped Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0031919744642044E-2"/>
+          <c:y val="0.10668158781898149"/>
+          <c:w val="0.92990424076607392"/>
+          <c:h val="0.8499999379835731"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$R$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Calculate_02 |Verify price breakup for P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread.| "TD_UI_Zlaata_Calculate_02"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$R$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$S$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Calculate_02 |Verify price breakup for P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread.| "TD_UI_Zlaata_Calculate_02"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$T$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$T$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Calculate_02 |Verify price breakup for P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread.| "TD_UI_Zlaata_Calculate_02"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$S$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46328448"/>
+        <c:axId val="46408064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46328448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46408064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46408064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Steps</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46328448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Features</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1292,8 +3203,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.9364481457108926E-3"/>
-          <c:y val="3.2123800120282653E-2"/>
+          <c:x val="5.9362468167315514E-3"/>
+          <c:y val="6.4713026203216312E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1305,10 +3216,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.6498186400440001E-2"/>
-          <c:y val="0.10118873685128098"/>
-          <c:w val="0.87710436725913243"/>
-          <c:h val="0.86336406553156542"/>
+          <c:x val="7.3672686824927558E-2"/>
+          <c:y val="0.11902669624860428"/>
+          <c:w val="0.92151704085316477"/>
+          <c:h val="0.85596714084772552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1350,7 +3261,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000001-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1375,7 +3286,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000003-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1400,42 +3311,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000005-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$E$2:$E$4</c:f>
+              <c:f>'DB Data'!$C$2:$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Scenarios Passed</c:v>
+                  <c:v>Features Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Scenarios Failed</c:v>
+                  <c:v>Features Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scenarios Skipped</c:v>
+                  <c:v>Features Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$F$2:$F$4</c:f>
+              <c:f>'DB Data'!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F52A-4A06-BA5F-6C71FCEF3775}"/>
+              <c16:uniqueId val="{00000006-C5E1-437A-A52D-DCB97CB8ED06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1471,7 +3419,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1491,16 +3439,16 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr algn="ctr">
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1800" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Steps</a:t>
+              <a:t>Scenarios</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1509,8 +3457,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.6171728533933258E-3"/>
-          <c:y val="5.4421749273573204E-2"/>
+          <c:x val="5.9107001159738751E-3"/>
+          <c:y val="3.7140215132502832E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1522,10 +3470,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11769966254218223"/>
-          <c:y val="8.4263722654767198E-2"/>
-          <c:w val="0.78142825896762902"/>
-          <c:h val="0.89306054848124394"/>
+          <c:x val="5.6571751205517912E-2"/>
+          <c:y val="8.4536101166436714E-2"/>
+          <c:w val="0.92725874381981321"/>
+          <c:h val="0.88851560210722469"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1567,7 +3515,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000001-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1592,7 +3540,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000003-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1617,42 +3565,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000005-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:f>'DB Data'!$E$2:$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Steps Passed</c:v>
+                  <c:v>Scenarios Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Steps Failed</c:v>
+                  <c:v>Scenarios Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Steps Skipped</c:v>
+                  <c:v>Scenarios Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:f>'DB Data'!$F$2:$F$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-33E3-412A-9233-ED47CE12E57E}"/>
+              <c16:uniqueId val="{00000006-86A0-4454-A31A-15C1830346B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1688,7 +3673,261 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.0163677357506801E-2"/>
+          <c:y val="5.5749128919860627E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.6917458262785006E-2"/>
+          <c:y val="0.10406650388213669"/>
+          <c:w val="0.93302459414795369"/>
+          <c:h val="0.87775832898936412"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d prstMaterial="matte"/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="51FF21"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Steps Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Steps Failed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Steps Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2833-4D5B-98DA-2F8086DE2D67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="40"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId1"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1731,9 +3970,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.3309046751669701E-2"/>
+          <c:x val="3.3278738246891114E-2"/>
           <c:y val="0.10500003204542271"/>
-          <c:w val="0.95333333333333337"/>
+          <c:w val="0.953375796178344"/>
           <c:h val="0.85236429602767994"/>
         </c:manualLayout>
       </c:layout>
@@ -1791,7 +4030,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Calculate_02 |Verify price breakup for P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread.| "TD_UI_Zlaata_Calculate_02"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1799,17 +4038,12 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$H$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000000-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1863,7 +4097,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Calculate_02 |Verify price breakup for P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread.| "TD_UI_Zlaata_Calculate_02"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1871,12 +4105,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$J$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000002-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1930,7 +4169,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Admin_OEV_01 |Verify emails for order placed, shipped, and delivered.| "TD_UI_Admin_OEV_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Calculate_02 |Verify price breakup for P1 &amp; P2 with Gift Wrap, Coupon, Gift Card Amount, and Thread.| "TD_UI_Zlaata_Calculate_02"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1938,12 +4177,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$I$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000001-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1957,11 +4201,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97185152"/>
-        <c:axId val="97201536"/>
+        <c:axId val="89325952"/>
+        <c:axId val="44310528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97185152"/>
+        <c:axId val="89325952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1971,7 +4215,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97201536"/>
+        <c:crossAx val="44310528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1979,7 +4223,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97201536"/>
+        <c:axId val="44310528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2011,7 +4255,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97185152"/>
+        <c:crossAx val="89325952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2040,7 +4284,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2106,7 +4350,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000001-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2131,7 +4375,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000003-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2156,7 +4400,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000005-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2184,14 +4428,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+              <c16:uniqueId val="{00000006-012F-4AE0-9B30-C14C76CB6C4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2212,919 +4462,6 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId1"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Tags</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$D$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@Mail</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$D$22:$D$23</c:f>
-              <c:numCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@Mail</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$F$22:$F$23</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$E$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>@TC_UI_Admin_OEV_01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@Mail</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$E$22:$E$23</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97122176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97123712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Features</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="3.3369832880226151E-2"/>
-          <c:y val="9.72480620155039E-2"/>
-          <c:w val="0.95324817070407986"/>
-          <c:h val="0.8601162790697674"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify Order Email Flow</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$F$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$H$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify Order Email Flow</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$H$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$G$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify Order Email Flow</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$G$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97540352"/>
-        <c:axId val="97550336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97540352"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97550336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97550336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97540352"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-        <c:minorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.3310417416097107E-2"/>
-          <c:y val="0.17399131020088515"/>
-          <c:w val="0.93298799578986624"/>
-          <c:h val="0.80271606659122552"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d prstMaterial="matte"/>
-          </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="51FF21"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'DB Data'!$C$2:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Features Passed</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Features Failed</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Features Skipped</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'DB Data'!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-1678-4457-8DD3-1C4694EC7DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="40"/>
-      </c:doughnutChart>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -3171,15 +4508,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Authors</a:t>
+              <a:t>Tags</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -3189,10 +4525,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -3204,7 +4540,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$D$21</c:f>
+              <c:f>Tags!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3239,37 +4575,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Calculation</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Calculate_02</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$D$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$D$22:$D$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000000-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3278,7 +4610,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$F$21</c:f>
+              <c:f>Tags!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3313,37 +4645,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Calculation</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Calculate_02</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$F$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$F$22:$F$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000001-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3352,7 +4680,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$E$21</c:f>
+              <c:f>Tags!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3387,37 +4715,41 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Calculation</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Calculate_02</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$E$22</c:f>
+              <c:f>Tags!$E$22:$E$23</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000002-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3431,11 +4763,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3445,7 +4777,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3453,7 +4785,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3471,7 +4803,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -3479,14 +4811,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3521,672 +4852,1681 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>43815</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>158115</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190500" y="142875"/>
-          <a:ext cx="3749040" cy="777240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Duration</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828924</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472439</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>127635</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486774" y="142875"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Start Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>165735</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486775" y="561975"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>End Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1019175" y="152401"/>
-          <a:ext cx="2933700" cy="771524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
-            <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>0.252 s</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3790950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9448800" y="142875"/>
-          <a:ext cx="2800350" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:14 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3809999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9467849" y="561975"/>
-          <a:ext cx="2771775" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:15 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
+      <xdr:colOff>57148</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7"/>
+        <xdr:cNvPr id="9" name="Group 8"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="190499" y="28576"/>
-          <a:ext cx="12045316" cy="3657600"/>
-          <a:chOff x="171449" y="36548"/>
-          <a:chExt cx="12045316" cy="3399182"/>
+          <a:off x="190498" y="0"/>
+          <a:ext cx="12068177" cy="3438525"/>
+          <a:chOff x="161923" y="0"/>
+          <a:chExt cx="12068177" cy="3438525"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="9" name="Group 8"/>
+          <xdr:cNvPr id="42" name="Group 41"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="171449" y="815528"/>
-            <a:ext cx="3749040" cy="2620202"/>
-            <a:chOff x="171449" y="815528"/>
-            <a:chExt cx="3749040" cy="2620202"/>
+            <a:off x="161923" y="0"/>
+            <a:ext cx="12068177" cy="3438525"/>
+            <a:chOff x="171448" y="19050"/>
+            <a:chExt cx="12068177" cy="3438525"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="13" name="Group 12"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="8477248" y="133350"/>
+              <a:ext cx="3762377" cy="685800"/>
+              <a:chOff x="8477248" y="133350"/>
+              <a:chExt cx="3762377" cy="685800"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="4" name="Rectangle 3"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477248" y="133350"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0" algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Start Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="5" name="Rectangle 4"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477249" y="495300"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>End Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="TextBox 6"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9563100" y="133351"/>
+                <a:ext cx="2676525" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="8" name="TextBox 7"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9572625" y="495300"/>
+                <a:ext cx="2667000" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="2" name="Group 100"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="171448" y="19050"/>
+              <a:ext cx="12054842" cy="3438525"/>
+              <a:chOff x="171448" y="19050"/>
+              <a:chExt cx="12054842" cy="3438525"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="10" name="Group 9"/>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="171448" y="19050"/>
+                <a:ext cx="12054842" cy="3438525"/>
+                <a:chOff x="152398" y="27696"/>
+                <a:chExt cx="12054842" cy="3195586"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="16" name="Group 15"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="152398" y="656192"/>
+                  <a:ext cx="3749040" cy="2563550"/>
+                  <a:chOff x="152398" y="656192"/>
+                  <a:chExt cx="3749040" cy="2563550"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="31" name="Rectangle 30"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="152398" y="815526"/>
+                    <a:ext cx="3749040" cy="2381198"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:grpSp>
+                <xdr:nvGrpSpPr>
+                  <xdr:cNvPr id="32" name="Group 31"/>
+                  <xdr:cNvGrpSpPr/>
+                </xdr:nvGrpSpPr>
+                <xdr:grpSpPr>
+                  <a:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="3621406" cy="2563550"/>
+                    <a:chOff x="247650" y="656192"/>
+                    <a:chExt cx="3621406" cy="2563550"/>
+                  </a:xfrm>
+                </xdr:grpSpPr>
+                <xdr:grpSp>
+                  <xdr:nvGrpSpPr>
+                    <xdr:cNvPr id="33" name="Group 32"/>
+                    <xdr:cNvGrpSpPr/>
+                  </xdr:nvGrpSpPr>
+                  <xdr:grpSpPr>
+                    <a:xfrm>
+                      <a:off x="2771776" y="859785"/>
+                      <a:ext cx="1097280" cy="764816"/>
+                      <a:chOff x="2771776" y="859785"/>
+                      <a:chExt cx="1097280" cy="764816"/>
+                    </a:xfrm>
+                  </xdr:grpSpPr>
+                  <xdr:sp macro="" textlink="">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="35" name="Rounded Rectangle 34"/>
+                      <xdr:cNvSpPr/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="2771776" y="859785"/>
+                        <a:ext cx="1097280" cy="764816"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="roundRect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:ln w="3175"/>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="2">
+                        <a:schemeClr val="dk1"/>
+                      </a:lnRef>
+                      <a:fillRef idx="1">
+                        <a:schemeClr val="lt1"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:schemeClr val="dk1"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>PASSED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>FAILED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>SKIPPED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>TOTAL</a:t>
+                        </a:r>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$2">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="36" name="TextBox 35"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="868694"/>
+                        <a:ext cx="485775" cy="247651"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="27F959"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="27F959"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$3">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="37" name="TextBox 36"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="1027977"/>
+                        <a:ext cx="485775" cy="251635"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FF0000"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>2</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$4">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="38" name="TextBox 37"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3371850" y="1187314"/>
+                        <a:ext cx="495300" cy="239006"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FFFF00"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FFFF00"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                </xdr:grpSp>
+                <xdr:graphicFrame macro="">
+                  <xdr:nvGraphicFramePr>
+                    <xdr:cNvPr id="34" name="FeatureDough"/>
+                    <xdr:cNvGraphicFramePr>
+                      <a:graphicFrameLocks/>
+                    </xdr:cNvGraphicFramePr>
+                  </xdr:nvGraphicFramePr>
+                  <xdr:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="2562225" cy="2563550"/>
+                  </xdr:xfrm>
+                  <a:graphic>
+                    <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                      <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+                    </a:graphicData>
+                  </a:graphic>
+                </xdr:graphicFrame>
+              </xdr:grpSp>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="17" name="Group 16"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="3981450" y="27696"/>
+                  <a:ext cx="4391026" cy="3177881"/>
+                  <a:chOff x="3981450" y="27696"/>
+                  <a:chExt cx="4391026" cy="3177881"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="25" name="Rectangle 24"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="3981450" y="133921"/>
+                    <a:ext cx="4391026" cy="3059265"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="26" name="Rounded Rectangle 25"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7143750" y="183252"/>
+                    <a:ext cx="1188720" cy="849796"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1600" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="27" name="TextBox 26"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="213640"/>
+                    <a:ext cx="542925" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="28" name="TextBox 27"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="394614"/>
+                    <a:ext cx="542926" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="29" name="TextBox 28"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7781924" y="557888"/>
+                    <a:ext cx="533401" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="30" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="4019551" y="27696"/>
+                  <a:ext cx="3276600" cy="3177881"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="18" name="Group 17"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="8458200" y="682747"/>
+                  <a:ext cx="3749040" cy="2540535"/>
+                  <a:chOff x="8458200" y="682747"/>
+                  <a:chExt cx="3749040" cy="2540535"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="19" name="Rectangle 18"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="8458200" y="815526"/>
+                    <a:ext cx="3749040" cy="2379428"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="20" name="Rounded Rectangle 19"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11077576" y="856008"/>
+                    <a:ext cx="1097280" cy="764816"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1300" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="21" name="TextBox 20"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="859839"/>
+                    <a:ext cx="476250" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{ECACBD74-B5B9-479E-8C2E-C9684999A572}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>6</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="22" name="TextBox 21"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11658600" y="1023110"/>
+                    <a:ext cx="485776" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{E24417FB-CCF3-4060-A9AB-23F9E2CDA81A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="23" name="TextBox 22"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="1177529"/>
+                    <a:ext cx="476250" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{04B0E76C-90E2-4732-8606-78D62C393D8A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="24" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="8572501" y="682747"/>
+                  <a:ext cx="2543174" cy="2540535"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="'DB Data'!$F$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="39" name="TextBox 38"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7791450" y="781050"/>
+                <a:ext cx="542925" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C1C65169-A7E7-4F44-8F1B-A4A10551DED6}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>6</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$D$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="40" name="TextBox 39"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3390900" y="1438275"/>
+                <a:ext cx="495299" cy="257176"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C751D109-05C5-4D27-8561-41C7DB1DFED0}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>4</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1100" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$H$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="41" name="TextBox 40"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="11687174" y="1428750"/>
+                <a:ext cx="476251" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{9404FC27-F618-4129-9790-CCC5E3B452F7}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>8</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="Rectangle 23"/>
+            <xdr:cNvPr id="3" name="Rectangle 2"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="171449" y="952809"/>
-              <a:ext cx="3749040" cy="2464407"/>
+              <a:off x="171450" y="133349"/>
+              <a:ext cx="3749040" cy="685800"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
             <a:noFill/>
-            <a:ln w="6350"/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:ln>
           </xdr:spPr>
           <xdr:style>
             <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
             </a:lnRef>
             <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
+              <a:schemeClr val="accent1"/>
             </a:fillRef>
             <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1"/>
             </a:effectRef>
             <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="lt1"/>
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Duration</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="27" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="419100" y="815528"/>
-            <a:ext cx="3238500" cy="2620202"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
       </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="10" name="Group 9"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
+      <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="TextBox 5"/>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
           <a:xfrm>
-            <a:off x="4000498" y="36548"/>
-            <a:ext cx="4389120" cy="3390329"/>
-            <a:chOff x="4000498" y="36548"/>
-            <a:chExt cx="4389120" cy="3390329"/>
+            <a:off x="990601" y="114300"/>
+            <a:ext cx="2924174" cy="676275"/>
           </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="Rectangle 17"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4000498" y="142772"/>
-              <a:ext cx="4389120" cy="3271713"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
             <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="23" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="4400550" y="36548"/>
-            <a:ext cx="3590925" cy="3390329"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="11" name="Group 10"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="8467725" y="806675"/>
-            <a:ext cx="3749040" cy="2609869"/>
-            <a:chOff x="8467725" y="806675"/>
-            <a:chExt cx="3749040" cy="2609869"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="Rectangle 11"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8467725" y="952137"/>
-              <a:ext cx="3749040" cy="2464407"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="17" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="8734425" y="806675"/>
-            <a:ext cx="3200400" cy="2602499"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
+              <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:pPr algn="ctr"/>
+              <a:t>0.253 s</a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4197,22 +6537,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35</cdr:x>
-      <cdr:y>0.34014</cdr:y>
+      <cdr:x>0.34572</cdr:x>
+      <cdr:y>0.37983</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.65294</cdr:x>
-      <cdr:y>0.69728</cdr:y>
+      <cdr:x>0.72119</cdr:x>
+      <cdr:y>0.71478</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1133475" y="952503"/>
-          <a:ext cx="981075" cy="1000125"/>
+          <a:off x="885825" y="1047749"/>
+          <a:ext cx="962024" cy="923925"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4338,7 +6678,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
+          <a:fld id="{790B2992-122F-4DED-8027-8C90CA641799}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4346,7 +6686,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4364,22 +6704,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.33156</cdr:x>
-      <cdr:y>0.36031</cdr:y>
+      <cdr:x>0.3343</cdr:x>
+      <cdr:y>0.34819</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.68208</cdr:x>
-      <cdr:y>0.70496</cdr:y>
+      <cdr:x>0.7064</cdr:x>
+      <cdr:y>0.70474</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1190625" y="1314450"/>
-          <a:ext cx="1258673" cy="1257300"/>
+          <a:off x="1095367" y="1190625"/>
+          <a:ext cx="1219223" cy="1219200"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4505,17 +6845,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{55E37DD8-520B-4F7A-9381-E422E7073C87}" type="TxLink">
+            <a:rPr lang="en-US" sz="3000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="3600" b="1">
+          <a:endParaRPr lang="en-US" sz="3000" b="1">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -4531,22 +6871,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35119</cdr:x>
-      <cdr:y>0.35374</cdr:y>
+      <cdr:x>0.33708</cdr:x>
+      <cdr:y>0.36934</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.66667</cdr:x>
-      <cdr:y>0.71088</cdr:y>
+      <cdr:x>0.70786</cdr:x>
+      <cdr:y>0.71429</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$H$5">
+    <cdr:sp macro="" textlink="'DB Data'!$H$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1123950" y="990599"/>
-          <a:ext cx="1009650" cy="1000125"/>
+          <a:off x="857253" y="1009650"/>
+          <a:ext cx="942958" cy="942975"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4672,7 +7012,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{31691118-B83C-4A2D-970E-D212AA344C2F}" type="TxLink">
+          <a:fld id="{0C07208B-2D34-4675-9C99-827455C82BF1}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4680,7 +7020,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>75%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4705,16 +7045,14 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4763,15 +7101,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>228601</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1508761</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>1508760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150494</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4780,8 +7118,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="323851" y="180974"/>
-          <a:ext cx="1280160" cy="352426"/>
+          <a:off x="323850" y="180974"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4816,6 +7154,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -4825,13 +7185,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>876300</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1514476</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>104553</xdr:rowOff>
+      <xdr:rowOff>85503</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$F$2">
       <xdr:nvSpPr>
@@ -4840,7 +7200,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="971550" y="219075"/>
+          <a:off x="971550" y="200025"/>
           <a:ext cx="638176" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4870,7 +7230,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{8D92AF4D-37D8-4C38-8EA4-79D629C4A437}" type="TxLink">
+          <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="51FF21"/>
@@ -4878,11 +7238,151 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>2</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23284</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1504950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>99262</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962025" y="404284"/>
+          <a:ext cx="638175" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866776</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1514476</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104219</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962026" y="589494"/>
+          <a:ext cx="647700" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -4897,22 +7397,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.32161</cdr:x>
+      <cdr:y>0.41018</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.68844</cdr:x>
+      <cdr:y>0.71781</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="561975" y="933452"/>
-          <a:ext cx="952500" cy="923924"/>
+          <a:off x="609603" y="914412"/>
+          <a:ext cx="695317" cy="685798"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5038,17 +7538,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{BB53D87E-07A1-498D-A732-07528C1BCE6E}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5067,20 +7567,18 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5102,22 +7600,20 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1800226</xdr:colOff>
+      <xdr:colOff>1800225</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5168,13 +7664,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>171449</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1451609</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5183,8 +7679,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304799" y="190501"/>
-          <a:ext cx="1280160" cy="361950"/>
+          <a:off x="304799" y="190500"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -5219,6 +7715,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -5228,22 +7746,22 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>847725</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1409700</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>114078</xdr:rowOff>
+      <xdr:rowOff>104553</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$D$2">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
+        <xdr:cNvPr id="12" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="228600"/>
+          <a:off x="981075" y="219075"/>
           <a:ext cx="561975" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5273,19 +7791,156 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{6831FE4E-352E-4F7B-A3D4-680EF38773CC}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
               <a:solidFill>
-                <a:srgbClr val="51FF21"/>
+                <a:srgbClr val="27F959"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
-              <a:srgbClr val="51FF21"/>
+              <a:srgbClr val="27F959"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>847724</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32808</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1400175</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>108786</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="981074" y="413808"/>
+          <a:ext cx="552451" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27519</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1419226</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>113744</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="971550" y="599019"/>
+          <a:ext cx="581026" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>1</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -5300,22 +7955,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.33503</cdr:x>
+      <cdr:y>0.4149</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.70558</cdr:x>
+      <cdr:y>0.73808</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="602111" y="1142827"/>
-          <a:ext cx="1020535" cy="1131157"/>
+          <a:off x="628650" y="904875"/>
+          <a:ext cx="695325" cy="704850"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5441,17 +8096,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{CE425BBE-7C02-4C07-B111-60BA1CB56900}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5461,29 +8116,6 @@
     </cdr:sp>
   </cdr:relSizeAnchor>
 </c:userShapes>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Dashboard"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="Tags"/>
-      <sheetName val="Features"/>
-      <sheetName val="Exceptions"/>
-      <sheetName val="DB Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5773,7 +8405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B19:G63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="2.0"/>
@@ -5784,8 +8416,119 @@
     <col min="6" max="6" customWidth="true" width="70.7109375"/>
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
-  <sheetData/>
-  <sheetProtection sheet="true" password="C693" scenarios="true" objects="true"/>
+  <sheetData>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="6"/>
+    </row>
+    <row r="37" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="61" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B61" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="38"/>
+      <c r="G62" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="49"/>
+      <c r="D63" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="49"/>
+      <c r="G63" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="F4B7" scenarios="true" objects="true"/>
+  <mergeCells count="9">
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="E63:F63"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5794,94 +8537,97 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B20:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.42578125"/>
-    <col min="2" max="2" customWidth="true" width="45.85546875"/>
+    <col min="2" max="2" customWidth="true" width="50.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
     <col min="5" max="5" customWidth="true" width="50.7109375"/>
-    <col min="6" max="6" customWidth="true" width="12.7109375"/>
+    <col min="6" max="6" customWidth="true" width="12.85546875"/>
     <col min="7" max="10" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>43</v>
+      <c r="J21" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="50" t="n">
         <v>2.0</v>
       </c>
-      <c r="H22" s="58" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="60"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="57" t="n">
+        <v>1.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5891,130 +8637,132 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B20:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
-    <col min="2" max="2" customWidth="true" width="35.5703125"/>
+    <col min="2" max="2" customWidth="true" width="35.7109375"/>
     <col min="3" max="7" customWidth="true" width="12.7109375"/>
     <col min="8" max="8" customWidth="true" width="60.7109375"/>
     <col min="9" max="9" customWidth="true" width="18.7109375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="15.5703125"/>
   </cols>
   <sheetData>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
+      <c r="B20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="45"/>
-      <c r="C21" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>45</v>
+      <c r="B21" s="41"/>
+      <c r="C21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" t="s" s="54">
-        <v>58</v>
-      </c>
-      <c r="C22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D22" s="58" t="n">
+      <c r="D22" s="55"/>
+      <c r="E22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="61" t="s">
-        <v>54</v>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="57" t="n">
+      <c r="B23" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D23" s="58" t="n">
+      <c r="D23" s="55"/>
+      <c r="E23" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E23" s="59"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="61" t="s">
-        <v>54</v>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="49" t="s">
+      <c r="B27" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="36" t="s">
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="35" t="s">
-        <v>22</v>
+      <c r="I27" s="34" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I28" s="55" t="s">
-        <v>29</v>
+      <c r="B28" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I29" s="55" t="s">
-        <v>29</v>
+      <c r="B29" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -6033,6 +8781,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B18:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6040,107 +8789,108 @@
     <col min="2" max="2" customWidth="true" width="60.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
-    <col min="5" max="11" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" customWidth="true" width="12.7109375"/>
+    <col min="5" max="13" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="4"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
+    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>43</v>
+      <c r="H21" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="F22" s="58" t="n">
+      <c r="F22" s="55"/>
+      <c r="G22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="G22" s="59"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="57" t="n">
+      <c r="H22" s="57"/>
+      <c r="I22" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="50" t="n">
         <v>2.0</v>
       </c>
-      <c r="K22" s="58" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="57" t="n">
+        <v>1.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="J20:M20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
-    <mergeCell ref="J20:M20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6148,10 +8898,56 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="1.7109375"/>
+    <col min="2" max="3" customWidth="true" width="30.7109375"/>
+    <col min="4" max="4" customWidth="true" width="45.7109375"/>
+    <col min="5" max="5" customWidth="true" width="75.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="A407" scenarios="true" objects="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.7109375"/>
@@ -6159,7 +8955,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" width="16.42578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="16.28515625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="3.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.5703125"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
     <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="22.42578125"/>
@@ -6187,93 +8983,92 @@
         <v>1</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="D2" s="0"/>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="F2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="F2" s="0"/>
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" t="n" s="0">
-        <v>2.0</v>
-      </c>
+      <c r="H2" s="0"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D3" s="0"/>
-      <c r="E3" t="s">
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="F3"/>
-      <c r="G3" t="s">
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="H3"/>
+      <c r="H3" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s" s="0">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D4" s="0"/>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F4"/>
-      <c r="G4" t="s">
+      <c r="F4" s="0"/>
+      <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n" s="0">
-        <f>SUM(D2:D4)</f>
         <v>1.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n" s="0">
-        <f>SUM(F2:F4)</f>
         <v>1.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <f>SUM(H2:H4)</f>
         <v>2.0</v>
       </c>
     </row>
@@ -6282,32 +9077,128 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>54</v>
+        <v>69</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s" s="49">
+        <v>71</v>
+      </c>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="H20" t="s" s="49">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L20" s="50"/>
+      <c r="P20" t="s" s="49">
+        <v>74</v>
+      </c>
+      <c r="Q20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="50"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -13,31 +13,23 @@
     <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" tabRatio="785"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="13" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="14" r:id="rId2"/>
-    <sheet name="Tags" sheetId="18" r:id="rId3"/>
-    <sheet name="Features" sheetId="16" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="11" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="3" r:id="rId2"/>
+    <sheet name="Tags" sheetId="4" r:id="rId3"/>
+    <sheet name="Features" sheetId="2" r:id="rId4"/>
+    <sheet name="Exceptions" sheetId="12" r:id="rId5"/>
     <sheet name="DB Data" sheetId="5" r:id="rId8" state="veryHidden"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="Chart1" localSheetId="3">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="1">Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="2">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1">#REF!</definedName>
-    <definedName name="Chart10">#REF!</definedName>
-    <definedName name="Chart30">#REF!</definedName>
-    <definedName name="Chart49">#REF!</definedName>
-    <definedName name="Chart51">#REF!</definedName>
+    <definedName name="Chart1">Scenarios!#REF!</definedName>
+    <definedName name="Chart51">Scenarios!#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
   <si>
     <t>Duration</t>
   </si>
@@ -96,6 +88,9 @@
     <t>STATUS</t>
   </si>
   <si>
+    <t>FEATURE STATUS</t>
+  </si>
+  <si>
     <t>Features Total</t>
   </si>
   <si>
@@ -111,43 +106,109 @@
     <t>Excel Extent Report</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:16 PM</t>
+    <t>TAG</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:14 PM</t>
+    <t>Scenario Passed</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:15 PM</t>
+    <t>Scenario Failed</t>
   </si>
   <si>
-    <t>0.252 s</t>
+    <t>Scenario Skipped</t>
+  </si>
+  <si>
+    <t>Tag Name</t>
+  </si>
+  <si>
+    <t>Feature Name</t>
+  </si>
+  <si>
+    <t>Feature Status</t>
+  </si>
+  <si>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>Scenario Status</t>
+  </si>
+  <si>
+    <t>Step Passed</t>
+  </si>
+  <si>
+    <t>Step Failed</t>
+  </si>
+  <si>
+    <t>Step Skipped</t>
+  </si>
+  <si>
+    <t>FEATURE FAIL SKIP</t>
+  </si>
+  <si>
+    <t>SCENARIO FAIL SKIP</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>0.013 s</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>0.022 s</t>
+    <t>FAILED &amp; SKIPPED TAGS</t>
   </si>
   <si>
     <t>TAG NAME</t>
   </si>
   <si>
+    <t>FAILED &amp; SKIPPED SCENARIOS</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:11 PM</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:09 PM</t>
+  </si>
+  <si>
+    <t>0.253 s</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>0.015 s</t>
+  </si>
+  <si>
+    <t>0.023 s</t>
+  </si>
+  <si>
+    <t>tag1</t>
+  </si>
+  <si>
     <t>tag</t>
+  </si>
+  <si>
+    <t>STACKTRACE</t>
   </si>
   <si>
     <t>STEP / HOOK TEXT</t>
   </si>
   <si>
-    <t>STACKTRACE</t>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>STEPS</t>
+  </si>
+  <si>
+    <t>SCENARIOS</t>
+  </si>
+  <si>
+    <t>NAME</t>
   </si>
   <si>
     <t>SCENARIO</t>
@@ -156,73 +217,63 @@
     <t>FEATURE</t>
   </si>
   <si>
-    <t>STEPS</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>SCENARIOS</t>
-  </si>
-  <si>
     <t>PASS %</t>
   </si>
   <si>
     <t>AUTHOR NAME</t>
   </si>
   <si>
-    <t>author</t>
+    <t>device</t>
   </si>
   <si>
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>device</t>
+    <t>Apr 16, 2026 3:05:49 PM</t>
   </si>
   <si>
-    <t>Mar 25, 2026 10:51:16 AM</t>
+    <t>Apr 16, 2026 3:02:02 PM</t>
   </si>
   <si>
-    <t>Mar 25, 2026 10:49:59 AM</t>
+    <t>Apr 16, 2026 3:05:47 PM</t>
   </si>
   <si>
-    <t>Mar 25, 2026 10:51:12 AM</t>
+    <t>3 m 45.417 s</t>
   </si>
   <si>
-    <t>1 m 12.798 s</t>
+    <t>0%</t>
   </si>
   <si>
-    <t>100%</t>
+    <t>@TC_UI_Zlaata_Stock_01</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_Home_01 |Verify the Zlaata India banner upload in Admin and its display on the Zlaata India home page section.| "TD_UI_Zlaata_Home_01"</t>
+    <t>@Stock</t>
   </si>
   <si>
-    <t>1 m 11.716 s</t>
+    <t>Place Order Based on Product Stock Availability</t>
   </si>
   <si>
-    <t>Home Page Banner upload verification admin panel</t>
+    <t>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</t>
   </si>
   <si>
-    <t>@Home</t>
+    <t>3 m 44.200 s</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_Home_01</t>
+    <t>3 m 44.211 s</t>
   </si>
   <si>
-    <t>@Regression</t>
+    <t>Given the stock quantity for the product is greater than 0</t>
   </si>
   <si>
-    <t>1 m 11.728 s</t>
+    <t xml:space="preserve">java.lang.NumberFormatException: For input string: ""
+	at java.base/java.lang.NumberFormatException.forInputString(NumberFormatException.java:65)
+	at java.base/java.lang.Integer.parseInt(Integer.java:662)
+	at java.base/java.lang.Integer.parseInt(Integer.java:770)
+	at pages.StockQuantityPage.verifyOutOfStockProductFlow(StockQuantityPage.java:488)
+	at pages.StockQuantityPage.validateStockQuantity(StockQuantityPage.java:511)
+	at stepDef.StockQuantityStepDef.the_stock_quantity_for_the_product_is_greater_than(StockQuantityStepDef.java:18)
+	at ✽.the stock quantity for the product is greater than 0(file:///C:/Users/Sarojkumar/git/ZlaataQAsever1235/src/test/resources/features/Stock%20Quantity/StockQuantity.feature:7)
+</t>
   </si>
 </sst>
 </file>
@@ -230,7 +281,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="0"/>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +292,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -290,9 +365,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FF51FF21"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,7 +391,7 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FF51FF21"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -323,7 +404,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
-      <color rgb="00FF00"/>
+      <color rgb="FF0000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color rgb="FF0000"/>
       <b val="true"/>
     </font>
     <font>
@@ -351,11 +437,6 @@
       <sz val="11.0"/>
       <b val="true"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="00FF00"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -365,7 +446,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -380,6 +461,43 @@
       <right style="hair">
         <color auto="1"/>
       </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -447,9 +565,7 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
@@ -477,173 +593,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,24 +783,30 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Features</a:t>
+              <a:t>Tags with</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> Failed &amp; Skipped Scenarios</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.1929905820595947E-3"/>
-          <c:y val="5.6284335775106678E-2"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -720,10 +816,719 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11780714910636171"/>
-          <c:y val="8.0818739637467149E-2"/>
-          <c:w val="0.76899981252343452"/>
-          <c:h val="0.87885598708448542"/>
+          <c:x val="2.9880212949228394E-2"/>
+          <c:y val="0.11750877449771498"/>
+          <c:w val="0.95813725490196078"/>
+          <c:h val="0.84734403472530151"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Stock</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$B$20:$B$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Stock</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$D$20:$D$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Stock</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$C$20:$C$21</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46151168"/>
+        <c:axId val="46117248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46151168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46117248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46117248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46151168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.3309046751669701E-2"/>
+          <c:y val="0.10919339164237124"/>
+          <c:w val="0.95333333333333337"/>
+          <c:h val="0.84804664723032075"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$F$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$H$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$H$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$G$22</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46512000"/>
+        <c:axId val="46513536"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46512000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46513536"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46513536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46512000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3310417416097107E-2"/>
+          <c:y val="0.17399131020088515"/>
+          <c:w val="0.93298799578986624"/>
+          <c:h val="0.80271606659122552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -765,7 +1570,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000001-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -790,7 +1595,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000003-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -815,7 +1620,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000005-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -845,12 +1650,18 @@
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CEAE-4775-A1C6-116F718DC196}"/>
+              <c16:uniqueId val="{00000006-D2BC-4951-98B3-E41274AF2CA1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -886,7 +1697,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -912,15 +1723,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Devices</a:t>
+              <a:t>Authors</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -930,10 +1740,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -945,7 +1755,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$D$21</c:f>
+              <c:f>Authors!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -980,37 +1790,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$D$22</c:f>
+              <c:f>Authors!$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000000-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1019,7 +1828,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$F$21</c:f>
+              <c:f>Authors!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1054,25 +1863,24 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$F$22</c:f>
+              <c:f>Authors!$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1084,7 +1892,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000001-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1093,7 +1901,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$E$21</c:f>
+              <c:f>Authors!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1128,37 +1936,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$E$22</c:f>
+              <c:f>Authors!$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000002-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1172,11 +1979,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1186,7 +1993,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1194,7 +2001,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1212,7 +2019,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -1220,14 +2027,379 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Devices</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$E$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46589440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46590976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46590976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1281,12 +2453,750 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features with Failed &amp; Skipped</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> Scenarios</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.587826839649571E-2"/>
+          <c:y val="0.10654873856176561"/>
+          <c:w val="0.89369296921336749"/>
+          <c:h val="0.85018673119905308"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$J$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$J$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9F7-4BBB-94B0-AEDC4FA75EC0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$L$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$L$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$K$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46193280"/>
+        <c:axId val="46285184"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46193280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46285184"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46285184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46193280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Scenarios</a:t>
+              <a:t>Scenarios with Failed &amp; Skipped Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0031919744642044E-2"/>
+          <c:y val="0.10668158781898149"/>
+          <c:w val="0.92990424076607392"/>
+          <c:h val="0.8499999379835731"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$R$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$R$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$S$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$T$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$T$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$S$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46328448"/>
+        <c:axId val="46408064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46328448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46408064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46408064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Steps</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46328448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Features</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1295,8 +3205,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.9364481457108926E-3"/>
-          <c:y val="3.2123800120282653E-2"/>
+          <c:x val="5.9362468167315514E-3"/>
+          <c:y val="6.4713026203216312E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1308,10 +3218,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.6498186400440001E-2"/>
-          <c:y val="0.10118873685128098"/>
-          <c:w val="0.87710436725913243"/>
-          <c:h val="0.86336406553156542"/>
+          <c:x val="7.3672686824927558E-2"/>
+          <c:y val="0.11902669624860428"/>
+          <c:w val="0.92151704085316477"/>
+          <c:h val="0.85596714084772552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1353,7 +3263,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000001-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1378,7 +3288,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000003-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1403,42 +3313,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000005-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$E$2:$E$4</c:f>
+              <c:f>'DB Data'!$C$2:$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Scenarios Passed</c:v>
+                  <c:v>Features Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Scenarios Failed</c:v>
+                  <c:v>Features Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scenarios Skipped</c:v>
+                  <c:v>Features Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$F$2:$F$4</c:f>
+              <c:f>'DB Data'!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F52A-4A06-BA5F-6C71FCEF3775}"/>
+              <c16:uniqueId val="{00000006-C5E1-437A-A52D-DCB97CB8ED06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1474,7 +3421,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1494,16 +3441,16 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr algn="ctr">
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1800" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Steps</a:t>
+              <a:t>Scenarios</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1512,8 +3459,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.6171728533933258E-3"/>
-          <c:y val="5.4421749273573204E-2"/>
+          <c:x val="5.9107001159738751E-3"/>
+          <c:y val="3.7140215132502832E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1525,10 +3472,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11769966254218223"/>
-          <c:y val="8.4263722654767198E-2"/>
-          <c:w val="0.78142825896762902"/>
-          <c:h val="0.89306054848124394"/>
+          <c:x val="5.6571751205517912E-2"/>
+          <c:y val="8.4536101166436714E-2"/>
+          <c:w val="0.92725874381981321"/>
+          <c:h val="0.88851560210722469"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1570,7 +3517,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000001-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1595,7 +3542,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000003-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1620,42 +3567,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000005-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:f>'DB Data'!$E$2:$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Steps Passed</c:v>
+                  <c:v>Scenarios Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Steps Failed</c:v>
+                  <c:v>Scenarios Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Steps Skipped</c:v>
+                  <c:v>Scenarios Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:f>'DB Data'!$F$2:$F$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-33E3-412A-9233-ED47CE12E57E}"/>
+              <c16:uniqueId val="{00000006-86A0-4454-A31A-15C1830346B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1691,7 +3675,261 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.0163677357506801E-2"/>
+          <c:y val="5.5749128919860627E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.6917458262785006E-2"/>
+          <c:y val="0.10406650388213669"/>
+          <c:w val="0.93302459414795369"/>
+          <c:h val="0.87775832898936412"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d prstMaterial="matte"/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="51FF21"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Steps Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Steps Failed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Steps Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2833-4D5B-98DA-2F8086DE2D67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="40"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId1"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1734,9 +3972,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.3309046751669701E-2"/>
+          <c:x val="3.3278738246891114E-2"/>
           <c:y val="0.10500003204542271"/>
-          <c:w val="0.95333333333333337"/>
+          <c:w val="0.953375796178344"/>
           <c:h val="0.85236429602767994"/>
         </c:manualLayout>
       </c:layout>
@@ -1794,7 +4032,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Home_01 |Verify the Zlaata India banner upload in Admin and its display on the Zlaata India home page section.| "TD_UI_Zlaata_Home_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1802,17 +4040,12 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$H$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000000-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1866,7 +4099,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Home_01 |Verify the Zlaata India banner upload in Admin and its display on the Zlaata India home page section.| "TD_UI_Zlaata_Home_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1874,12 +4107,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$J$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000002-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1933,7 +4171,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Home_01 |Verify the Zlaata India banner upload in Admin and its display on the Zlaata India home page section.| "TD_UI_Zlaata_Home_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1941,12 +4179,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$I$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000001-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1960,11 +4203,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97185152"/>
-        <c:axId val="97201536"/>
+        <c:axId val="89325952"/>
+        <c:axId val="44310528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97185152"/>
+        <c:axId val="89325952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1974,7 +4217,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97201536"/>
+        <c:crossAx val="44310528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1982,7 +4225,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97201536"/>
+        <c:axId val="44310528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2014,7 +4257,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97185152"/>
+        <c:crossAx val="89325952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2043,7 +4286,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2109,7 +4352,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000001-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2134,7 +4377,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000003-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2159,7 +4402,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000005-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2187,14 +4430,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+              <c16:uniqueId val="{00000006-012F-4AE0-9B30-C14C76CB6C4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2215,931 +4464,6 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId1"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Tags</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$D$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>@Home</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_Home_01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$D$22:$D$24</c:f>
-              <c:numCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>@Home</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_Home_01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$F$22:$F$24</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$E$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>@Home</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_Home_01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$E$22:$E$24</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97122176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97123712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Features</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="3.3369832880226151E-2"/>
-          <c:y val="9.72480620155039E-2"/>
-          <c:w val="0.95324817070407986"/>
-          <c:h val="0.8601162790697674"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Home Page Banner upload verification admin panel</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$F$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$H$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Home Page Banner upload verification admin panel</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$H$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$G$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Home Page Banner upload verification admin panel</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$G$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97540352"/>
-        <c:axId val="97550336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97540352"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97550336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97550336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97540352"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-        <c:minorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.3310417416097107E-2"/>
-          <c:y val="0.17399131020088515"/>
-          <c:w val="0.93298799578986624"/>
-          <c:h val="0.80271606659122552"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d prstMaterial="matte"/>
-          </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="51FF21"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'DB Data'!$C$2:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Features Passed</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Features Failed</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Features Skipped</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'DB Data'!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-1678-4457-8DD3-1C4694EC7DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="40"/>
-      </c:doughnutChart>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -3186,15 +4510,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Authors</a:t>
+              <a:t>Tags</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -3204,10 +4527,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -3219,7 +4542,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$D$21</c:f>
+              <c:f>Tags!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3254,37 +4577,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Stock</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$D$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$D$22:$D$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000000-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3293,7 +4612,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$F$21</c:f>
+              <c:f>Tags!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3328,37 +4647,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Stock</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$F$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$F$22:$F$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000001-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3367,7 +4682,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$E$21</c:f>
+              <c:f>Tags!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3402,37 +4717,41 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@Stock</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$E$22</c:f>
+              <c:f>Tags!$E$22:$E$23</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000002-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3446,11 +4765,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3460,7 +4779,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3468,7 +4787,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3486,7 +4805,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -3494,14 +4813,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3536,672 +4854,1681 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>43815</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>158115</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190500" y="142875"/>
-          <a:ext cx="3749040" cy="777240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Duration</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828924</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472439</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>127635</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486774" y="142875"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Start Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>165735</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486775" y="561975"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>End Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1019175" y="152401"/>
-          <a:ext cx="2933700" cy="771524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
-            <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>0.252 s</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3790950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9448800" y="142875"/>
-          <a:ext cx="2800350" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:14 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3809999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9467849" y="561975"/>
-          <a:ext cx="2771775" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:15 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
+      <xdr:colOff>57148</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7"/>
+        <xdr:cNvPr id="9" name="Group 8"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="190499" y="28576"/>
-          <a:ext cx="12045316" cy="3657600"/>
-          <a:chOff x="171449" y="36548"/>
-          <a:chExt cx="12045316" cy="3399182"/>
+          <a:off x="190498" y="0"/>
+          <a:ext cx="12068177" cy="3438525"/>
+          <a:chOff x="161923" y="0"/>
+          <a:chExt cx="12068177" cy="3438525"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="9" name="Group 8"/>
+          <xdr:cNvPr id="42" name="Group 41"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="171449" y="815528"/>
-            <a:ext cx="3749040" cy="2620202"/>
-            <a:chOff x="171449" y="815528"/>
-            <a:chExt cx="3749040" cy="2620202"/>
+            <a:off x="161923" y="0"/>
+            <a:ext cx="12068177" cy="3438525"/>
+            <a:chOff x="171448" y="19050"/>
+            <a:chExt cx="12068177" cy="3438525"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="13" name="Group 12"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="8477248" y="133350"/>
+              <a:ext cx="3762377" cy="685800"/>
+              <a:chOff x="8477248" y="133350"/>
+              <a:chExt cx="3762377" cy="685800"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="4" name="Rectangle 3"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477248" y="133350"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0" algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Start Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="5" name="Rectangle 4"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477249" y="495300"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>End Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="TextBox 6"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9563100" y="133351"/>
+                <a:ext cx="2676525" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="8" name="TextBox 7"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9572625" y="495300"/>
+                <a:ext cx="2667000" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="2" name="Group 100"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="171448" y="19050"/>
+              <a:ext cx="12054842" cy="3438525"/>
+              <a:chOff x="171448" y="19050"/>
+              <a:chExt cx="12054842" cy="3438525"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="10" name="Group 9"/>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="171448" y="19050"/>
+                <a:ext cx="12054842" cy="3438525"/>
+                <a:chOff x="152398" y="27696"/>
+                <a:chExt cx="12054842" cy="3195586"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="16" name="Group 15"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="152398" y="656192"/>
+                  <a:ext cx="3749040" cy="2563550"/>
+                  <a:chOff x="152398" y="656192"/>
+                  <a:chExt cx="3749040" cy="2563550"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="31" name="Rectangle 30"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="152398" y="815526"/>
+                    <a:ext cx="3749040" cy="2381198"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:grpSp>
+                <xdr:nvGrpSpPr>
+                  <xdr:cNvPr id="32" name="Group 31"/>
+                  <xdr:cNvGrpSpPr/>
+                </xdr:nvGrpSpPr>
+                <xdr:grpSpPr>
+                  <a:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="3621406" cy="2563550"/>
+                    <a:chOff x="247650" y="656192"/>
+                    <a:chExt cx="3621406" cy="2563550"/>
+                  </a:xfrm>
+                </xdr:grpSpPr>
+                <xdr:grpSp>
+                  <xdr:nvGrpSpPr>
+                    <xdr:cNvPr id="33" name="Group 32"/>
+                    <xdr:cNvGrpSpPr/>
+                  </xdr:nvGrpSpPr>
+                  <xdr:grpSpPr>
+                    <a:xfrm>
+                      <a:off x="2771776" y="859785"/>
+                      <a:ext cx="1097280" cy="764816"/>
+                      <a:chOff x="2771776" y="859785"/>
+                      <a:chExt cx="1097280" cy="764816"/>
+                    </a:xfrm>
+                  </xdr:grpSpPr>
+                  <xdr:sp macro="" textlink="">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="35" name="Rounded Rectangle 34"/>
+                      <xdr:cNvSpPr/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="2771776" y="859785"/>
+                        <a:ext cx="1097280" cy="764816"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="roundRect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:ln w="3175"/>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="2">
+                        <a:schemeClr val="dk1"/>
+                      </a:lnRef>
+                      <a:fillRef idx="1">
+                        <a:schemeClr val="lt1"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:schemeClr val="dk1"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>PASSED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>FAILED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>SKIPPED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>TOTAL</a:t>
+                        </a:r>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$2">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="36" name="TextBox 35"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="868694"/>
+                        <a:ext cx="485775" cy="247651"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="27F959"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="27F959"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$3">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="37" name="TextBox 36"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="1027977"/>
+                        <a:ext cx="485775" cy="251635"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FF0000"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>2</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$4">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="38" name="TextBox 37"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3371850" y="1187314"/>
+                        <a:ext cx="495300" cy="239006"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FFFF00"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FFFF00"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                </xdr:grpSp>
+                <xdr:graphicFrame macro="">
+                  <xdr:nvGraphicFramePr>
+                    <xdr:cNvPr id="34" name="FeatureDough"/>
+                    <xdr:cNvGraphicFramePr>
+                      <a:graphicFrameLocks/>
+                    </xdr:cNvGraphicFramePr>
+                  </xdr:nvGraphicFramePr>
+                  <xdr:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="2562225" cy="2563550"/>
+                  </xdr:xfrm>
+                  <a:graphic>
+                    <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                      <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+                    </a:graphicData>
+                  </a:graphic>
+                </xdr:graphicFrame>
+              </xdr:grpSp>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="17" name="Group 16"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="3981450" y="27696"/>
+                  <a:ext cx="4391026" cy="3177881"/>
+                  <a:chOff x="3981450" y="27696"/>
+                  <a:chExt cx="4391026" cy="3177881"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="25" name="Rectangle 24"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="3981450" y="133921"/>
+                    <a:ext cx="4391026" cy="3059265"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="26" name="Rounded Rectangle 25"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7143750" y="183252"/>
+                    <a:ext cx="1188720" cy="849796"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1600" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="27" name="TextBox 26"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="213640"/>
+                    <a:ext cx="542925" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="28" name="TextBox 27"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="394614"/>
+                    <a:ext cx="542926" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="29" name="TextBox 28"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7781924" y="557888"/>
+                    <a:ext cx="533401" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="30" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="4019551" y="27696"/>
+                  <a:ext cx="3276600" cy="3177881"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="18" name="Group 17"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="8458200" y="682747"/>
+                  <a:ext cx="3749040" cy="2540535"/>
+                  <a:chOff x="8458200" y="682747"/>
+                  <a:chExt cx="3749040" cy="2540535"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="19" name="Rectangle 18"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="8458200" y="815526"/>
+                    <a:ext cx="3749040" cy="2379428"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="20" name="Rounded Rectangle 19"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11077576" y="856008"/>
+                    <a:ext cx="1097280" cy="764816"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1300" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="21" name="TextBox 20"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="859839"/>
+                    <a:ext cx="476250" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{ECACBD74-B5B9-479E-8C2E-C9684999A572}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>6</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="22" name="TextBox 21"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11658600" y="1023110"/>
+                    <a:ext cx="485776" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{E24417FB-CCF3-4060-A9AB-23F9E2CDA81A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="23" name="TextBox 22"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="1177529"/>
+                    <a:ext cx="476250" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{04B0E76C-90E2-4732-8606-78D62C393D8A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="24" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="8572501" y="682747"/>
+                  <a:ext cx="2543174" cy="2540535"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="'DB Data'!$F$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="39" name="TextBox 38"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7791450" y="781050"/>
+                <a:ext cx="542925" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C1C65169-A7E7-4F44-8F1B-A4A10551DED6}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>6</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$D$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="40" name="TextBox 39"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3390900" y="1438275"/>
+                <a:ext cx="495299" cy="257176"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C751D109-05C5-4D27-8561-41C7DB1DFED0}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>4</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1100" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$H$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="41" name="TextBox 40"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="11687174" y="1428750"/>
+                <a:ext cx="476251" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{9404FC27-F618-4129-9790-CCC5E3B452F7}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>8</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="Rectangle 23"/>
+            <xdr:cNvPr id="3" name="Rectangle 2"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="171449" y="952809"/>
-              <a:ext cx="3749040" cy="2464407"/>
+              <a:off x="171450" y="133349"/>
+              <a:ext cx="3749040" cy="685800"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
             <a:noFill/>
-            <a:ln w="6350"/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:ln>
           </xdr:spPr>
           <xdr:style>
             <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
             </a:lnRef>
             <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
+              <a:schemeClr val="accent1"/>
             </a:fillRef>
             <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1"/>
             </a:effectRef>
             <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="lt1"/>
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Duration</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="27" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="419100" y="815528"/>
-            <a:ext cx="3238500" cy="2620202"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
       </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="10" name="Group 9"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
+      <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="TextBox 5"/>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
           <a:xfrm>
-            <a:off x="4000498" y="36548"/>
-            <a:ext cx="4389120" cy="3390329"/>
-            <a:chOff x="4000498" y="36548"/>
-            <a:chExt cx="4389120" cy="3390329"/>
+            <a:off x="990601" y="114300"/>
+            <a:ext cx="2924174" cy="676275"/>
           </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="Rectangle 17"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4000498" y="142772"/>
-              <a:ext cx="4389120" cy="3271713"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
             <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="23" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="4400550" y="36548"/>
-            <a:ext cx="3590925" cy="3390329"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="11" name="Group 10"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="8467725" y="806675"/>
-            <a:ext cx="3749040" cy="2609869"/>
-            <a:chOff x="8467725" y="806675"/>
-            <a:chExt cx="3749040" cy="2609869"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="Rectangle 11"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8467725" y="952137"/>
-              <a:ext cx="3749040" cy="2464407"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="17" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="8734425" y="806675"/>
-            <a:ext cx="3200400" cy="2602499"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
+              <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:pPr algn="ctr"/>
+              <a:t>0.253 s</a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4212,22 +6539,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35</cdr:x>
-      <cdr:y>0.34014</cdr:y>
+      <cdr:x>0.34572</cdr:x>
+      <cdr:y>0.37983</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.65294</cdr:x>
-      <cdr:y>0.69728</cdr:y>
+      <cdr:x>0.72119</cdr:x>
+      <cdr:y>0.71478</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1133475" y="952503"/>
-          <a:ext cx="981075" cy="1000125"/>
+          <a:off x="885825" y="1047749"/>
+          <a:ext cx="962024" cy="923925"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4353,7 +6680,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
+          <a:fld id="{790B2992-122F-4DED-8027-8C90CA641799}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4361,7 +6688,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4379,22 +6706,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.33156</cdr:x>
-      <cdr:y>0.36031</cdr:y>
+      <cdr:x>0.3343</cdr:x>
+      <cdr:y>0.34819</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.68208</cdr:x>
-      <cdr:y>0.70496</cdr:y>
+      <cdr:x>0.7064</cdr:x>
+      <cdr:y>0.70474</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1190625" y="1314450"/>
-          <a:ext cx="1258673" cy="1257300"/>
+          <a:off x="1095367" y="1190625"/>
+          <a:ext cx="1219223" cy="1219200"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4520,17 +6847,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{55E37DD8-520B-4F7A-9381-E422E7073C87}" type="TxLink">
+            <a:rPr lang="en-US" sz="3000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="3600" b="1">
+          <a:endParaRPr lang="en-US" sz="3000" b="1">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -4546,22 +6873,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35119</cdr:x>
-      <cdr:y>0.35374</cdr:y>
+      <cdr:x>0.33708</cdr:x>
+      <cdr:y>0.36934</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.66667</cdr:x>
-      <cdr:y>0.71088</cdr:y>
+      <cdr:x>0.70786</cdr:x>
+      <cdr:y>0.71429</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$H$5">
+    <cdr:sp macro="" textlink="'DB Data'!$H$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1123950" y="990599"/>
-          <a:ext cx="1009650" cy="1000125"/>
+          <a:off x="857253" y="1009650"/>
+          <a:ext cx="942958" cy="942975"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4687,7 +7014,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{31691118-B83C-4A2D-970E-D212AA344C2F}" type="TxLink">
+          <a:fld id="{0C07208B-2D34-4675-9C99-827455C82BF1}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4695,7 +7022,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>75%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4720,16 +7047,14 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4778,15 +7103,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>228601</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1508761</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>1508760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150494</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4795,8 +7120,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="323851" y="180974"/>
-          <a:ext cx="1280160" cy="352426"/>
+          <a:off x="323850" y="180974"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4831,6 +7156,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -4840,13 +7187,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>876300</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1514476</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>104553</xdr:rowOff>
+      <xdr:rowOff>85503</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$F$2">
       <xdr:nvSpPr>
@@ -4855,7 +7202,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="971550" y="219075"/>
+          <a:off x="971550" y="200025"/>
           <a:ext cx="638176" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4885,7 +7232,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{8D92AF4D-37D8-4C38-8EA4-79D629C4A437}" type="TxLink">
+          <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="51FF21"/>
@@ -4893,11 +7240,151 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>2</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23284</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1504950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>99262</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962025" y="404284"/>
+          <a:ext cx="638175" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866776</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1514476</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104219</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962026" y="589494"/>
+          <a:ext cx="647700" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -4912,22 +7399,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.32161</cdr:x>
+      <cdr:y>0.41018</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.68844</cdr:x>
+      <cdr:y>0.71781</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="561975" y="933452"/>
-          <a:ext cx="952500" cy="923924"/>
+          <a:off x="609603" y="914412"/>
+          <a:ext cx="695317" cy="685798"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5053,17 +7540,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{BB53D87E-07A1-498D-A732-07528C1BCE6E}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5082,20 +7569,18 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5117,22 +7602,20 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1800226</xdr:colOff>
+      <xdr:colOff>1800225</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5183,13 +7666,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>171449</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1451609</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5198,8 +7681,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304799" y="190501"/>
-          <a:ext cx="1280160" cy="361950"/>
+          <a:off x="304799" y="190500"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -5234,6 +7717,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -5243,22 +7748,22 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>847725</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1409700</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>114078</xdr:rowOff>
+      <xdr:rowOff>104553</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$D$2">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
+        <xdr:cNvPr id="12" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="228600"/>
+          <a:off x="981075" y="219075"/>
           <a:ext cx="561975" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5288,19 +7793,156 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{6831FE4E-352E-4F7B-A3D4-680EF38773CC}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
               <a:solidFill>
-                <a:srgbClr val="51FF21"/>
+                <a:srgbClr val="27F959"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
-              <a:srgbClr val="51FF21"/>
+              <a:srgbClr val="27F959"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>847724</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32808</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1400175</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>108786</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="981074" y="413808"/>
+          <a:ext cx="552451" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27519</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1419226</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>113744</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="971550" y="599019"/>
+          <a:ext cx="581026" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>1</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -5315,22 +7957,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.33503</cdr:x>
+      <cdr:y>0.4149</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.70558</cdr:x>
+      <cdr:y>0.73808</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="602111" y="1142827"/>
-          <a:ext cx="1020535" cy="1131157"/>
+          <a:off x="628650" y="904875"/>
+          <a:ext cx="695325" cy="704850"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5456,17 +8098,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{CE425BBE-7C02-4C07-B111-60BA1CB56900}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5476,29 +8118,6 @@
     </cdr:sp>
   </cdr:relSizeAnchor>
 </c:userShapes>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Dashboard"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="Tags"/>
-      <sheetName val="Features"/>
-      <sheetName val="Exceptions"/>
-      <sheetName val="DB Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5788,7 +8407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B19:G63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="2.0"/>
@@ -5799,8 +8418,119 @@
     <col min="6" max="6" customWidth="true" width="70.7109375"/>
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
-  <sheetData/>
-  <sheetProtection sheet="true" password="C58B" scenarios="true" objects="true"/>
+  <sheetData>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="6"/>
+    </row>
+    <row r="37" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="61" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B61" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="38"/>
+      <c r="G62" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="49"/>
+      <c r="D63" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="49"/>
+      <c r="G63" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="D17F" scenarios="true" objects="true"/>
+  <mergeCells count="9">
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="E63:F63"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5809,94 +8539,97 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B20:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.42578125"/>
-    <col min="2" max="2" customWidth="true" width="45.85546875"/>
+    <col min="2" max="2" customWidth="true" width="50.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
     <col min="5" max="5" customWidth="true" width="50.7109375"/>
-    <col min="6" max="6" customWidth="true" width="12.7109375"/>
+    <col min="6" max="6" customWidth="true" width="12.85546875"/>
     <col min="7" max="10" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>43</v>
+      <c r="J21" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="50" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H22" s="55"/>
+      <c r="I22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="57" t="n">
         <v>2.0</v>
       </c>
-      <c r="H22" s="58" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5906,174 +8639,141 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B20:I31"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="B20:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
-    <col min="2" max="2" customWidth="true" width="35.5703125"/>
+    <col min="2" max="2" customWidth="true" width="35.7109375"/>
     <col min="3" max="7" customWidth="true" width="12.7109375"/>
     <col min="8" max="8" customWidth="true" width="60.7109375"/>
     <col min="9" max="9" customWidth="true" width="18.7109375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="15.5703125"/>
   </cols>
   <sheetData>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
+      <c r="B20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="45"/>
-      <c r="C21" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>45</v>
+      <c r="B21" s="41"/>
+      <c r="C21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" t="s" s="54">
-        <v>58</v>
-      </c>
-      <c r="C22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D22" s="58" t="n">
+      <c r="D22" s="55"/>
+      <c r="E22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="61" t="s">
-        <v>54</v>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="57" t="n">
+      <c r="B23" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D23" s="58" t="n">
+      <c r="D23" s="55"/>
+      <c r="E23" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E23" s="59"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="61" t="s">
-        <v>54</v>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="57" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D24" s="58" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E24" s="59"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="61" t="s">
-        <v>54</v>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>16</v>
+    <row r="28">
+      <c r="B28" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>73</v>
       </c>
       <c r="D28" s="49"/>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
       <c r="G28" s="49"/>
-      <c r="H28" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="35" t="s">
-        <v>22</v>
+      <c r="H28" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I29" s="55" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" s="55" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I31" s="55" t="s">
-        <v>29</v>
+      <c r="B29" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C27:G27"/>
     <mergeCell ref="C28:G28"/>
     <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6083,6 +8783,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B18:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6090,107 +8791,108 @@
     <col min="2" max="2" customWidth="true" width="60.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
-    <col min="5" max="11" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" customWidth="true" width="12.7109375"/>
+    <col min="5" max="13" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="4"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
+    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>43</v>
+      <c r="H21" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="F22" s="58" t="n">
+      <c r="F22" s="55"/>
+      <c r="G22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="G22" s="59"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="57" t="n">
+      <c r="H22" s="57"/>
+      <c r="I22" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="50" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K22" s="55"/>
+      <c r="L22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="57" t="n">
         <v>2.0</v>
       </c>
-      <c r="K22" s="58" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="J20:M20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
-    <mergeCell ref="J20:M20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6198,10 +8900,56 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="1.7109375"/>
+    <col min="2" max="3" customWidth="true" width="30.7109375"/>
+    <col min="4" max="4" customWidth="true" width="45.7109375"/>
+    <col min="5" max="5" customWidth="true" width="75.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="869F" scenarios="true" objects="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.7109375"/>
@@ -6209,7 +8957,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" width="16.42578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="16.28515625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="3.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.5703125"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
     <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="22.42578125"/>
@@ -6237,94 +8985,93 @@
         <v>1</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="D2" s="0"/>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="F2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="F2" s="0"/>
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" t="n" s="0">
-        <v>2.0</v>
-      </c>
+      <c r="H2" s="0"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D3" s="0"/>
-      <c r="E3" t="s">
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="F3"/>
-      <c r="G3" t="s">
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="H3"/>
+      <c r="H3" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s" s="0">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D4" s="0"/>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F4"/>
-      <c r="G4" t="s">
+      <c r="F4" s="0"/>
+      <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" t="n" s="0">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n" s="0">
-        <f>SUM(D2:D4)</f>
         <v>1.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n" s="0">
-        <f>SUM(F2:F4)</f>
         <v>1.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <f>SUM(H2:H4)</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6332,32 +9079,128 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>54</v>
+        <v>69</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s" s="49">
+        <v>71</v>
+      </c>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="H20" t="s" s="49">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L20" s="50"/>
+      <c r="P20" t="s" s="49">
+        <v>74</v>
+      </c>
+      <c r="Q20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T20" s="50" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="50"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="80">
   <si>
     <t>Duration</t>
   </si>
@@ -229,19 +229,22 @@
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>Apr 16, 2026 3:05:49 PM</t>
+    <t>Apr 18, 2026 11:24:28 AM</t>
   </si>
   <si>
-    <t>Apr 16, 2026 3:02:02 PM</t>
+    <t>Apr 18, 2026 11:21:17 AM</t>
   </si>
   <si>
-    <t>Apr 16, 2026 3:05:47 PM</t>
+    <t>Apr 18, 2026 11:24:25 AM</t>
   </si>
   <si>
-    <t>3 m 45.417 s</t>
+    <t>3 m 7.389 s</t>
   </si>
   <si>
     <t>0%</t>
+  </si>
+  <si>
+    <t>67%</t>
   </si>
   <si>
     <t>@TC_UI_Zlaata_Stock_01</t>
@@ -256,24 +259,16 @@
     <t>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</t>
   </si>
   <si>
-    <t>3 m 44.200 s</t>
+    <t>3 m 5.563 s</t>
   </si>
   <si>
-    <t>3 m 44.211 s</t>
+    <t>3 m 5.580 s</t>
   </si>
   <si>
-    <t>Given the stock quantity for the product is greater than 0</t>
+    <t>Then the after order placed and shows Out of Stock</t>
   </si>
   <si>
-    <t xml:space="preserve">java.lang.NumberFormatException: For input string: ""
-	at java.base/java.lang.NumberFormatException.forInputString(NumberFormatException.java:65)
-	at java.base/java.lang.Integer.parseInt(Integer.java:662)
-	at java.base/java.lang.Integer.parseInt(Integer.java:770)
-	at pages.StockQuantityPage.verifyOutOfStockProductFlow(StockQuantityPage.java:488)
-	at pages.StockQuantityPage.validateStockQuantity(StockQuantityPage.java:511)
-	at stepDef.StockQuantityStepDef.the_stock_quantity_for_the_product_is_greater_than(StockQuantityStepDef.java:18)
-	at ✽.the stock quantity for the product is greater than 0(file:///C:/Users/Sarojkumar/git/ZlaataQAsever1235/src/test/resources/features/Stock%20Quantity/StockQuantity.feature:7)
-</t>
+    <t/>
   </si>
 </sst>
 </file>
@@ -2922,7 +2917,12 @@
           <c:val>
             <c:numRef>
               <c:f>'DB Data'!$R$20</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -2989,12 +2989,7 @@
           <c:val>
             <c:numRef>
               <c:f>'DB Data'!$T$20</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4040,7 +4035,12 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$H$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4107,12 +4107,7 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$J$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -8445,15 +8440,15 @@
     </row>
     <row r="39">
       <c r="B39" s="51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D39" s="49"/>
       <c r="E39" s="49"/>
       <c r="F39" s="52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G39" s="53" t="s">
         <v>40</v>
@@ -8461,15 +8456,15 @@
     </row>
     <row r="40">
       <c r="B40" s="51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C40" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" s="49"/>
       <c r="E40" s="49"/>
       <c r="F40" s="52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G40" s="53" t="s">
         <v>40</v>
@@ -8506,14 +8501,14 @@
     </row>
     <row r="63">
       <c r="B63" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C63" s="49"/>
       <c r="D63" s="53" t="s">
         <v>40</v>
       </c>
       <c r="E63" s="52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F63" s="49"/>
       <c r="G63" s="53" t="s">
@@ -8521,7 +8516,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="D17F" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="C9E9" scenarios="true" objects="true"/>
   <mergeCells count="9">
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="B62:C62"/>
@@ -8600,16 +8595,16 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F22" s="53" t="s">
         <v>40</v>
@@ -8617,13 +8612,13 @@
       <c r="G22" s="50" t="n">
         <v>3.0</v>
       </c>
-      <c r="H22" s="55"/>
+      <c r="H22" s="55" t="n">
+        <v>2.0</v>
+      </c>
       <c r="I22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="J22" s="57" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="J22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8683,7 +8678,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="50" t="n">
         <v>1.0</v>
@@ -8699,7 +8694,7 @@
     </row>
     <row r="23">
       <c r="B23" s="51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="50" t="n">
         <v>1.0</v>
@@ -8733,17 +8728,17 @@
     </row>
     <row r="28">
       <c r="B28" s="51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D28" s="49"/>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
       <c r="G28" s="49"/>
       <c r="H28" s="52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I28" s="53" t="s">
         <v>40</v>
@@ -8751,17 +8746,17 @@
     </row>
     <row r="29">
       <c r="B29" s="51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="49"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
       <c r="G29" s="49"/>
       <c r="H29" s="52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I29" s="53" t="s">
         <v>40</v>
@@ -8858,13 +8853,13 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>1.0</v>
@@ -8880,13 +8875,13 @@
       <c r="J22" s="50" t="n">
         <v>3.0</v>
       </c>
-      <c r="K22" s="55"/>
+      <c r="K22" s="55" t="n">
+        <v>2.0</v>
+      </c>
       <c r="L22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="M22" s="57" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="M22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8927,20 +8922,20 @@
     </row>
     <row r="3">
       <c r="B3" s="52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="869F" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="EEA5" scenarios="true" objects="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -8998,7 +8993,9 @@
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" s="0"/>
+      <c r="H2" t="n" s="0">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
@@ -9044,9 +9041,7 @@
       <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4" t="n" s="0">
-        <v>2.0</v>
-      </c>
+      <c r="H4" s="0"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
@@ -9088,7 +9083,7 @@
         <v>70</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -9148,7 +9143,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s" s="49">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" s="50"/>
       <c r="C20" s="50" t="n">
@@ -9156,7 +9151,7 @@
       </c>
       <c r="D20" s="50"/>
       <c r="H20" t="s" s="49">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" t="s" s="49">
         <v>40</v>
@@ -9167,22 +9162,22 @@
       </c>
       <c r="L20" s="50"/>
       <c r="P20" t="s" s="49">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q20" t="s" s="49">
         <v>40</v>
       </c>
-      <c r="R20" s="50"/>
+      <c r="R20" s="50" t="n">
+        <v>2.0</v>
+      </c>
       <c r="S20" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="T20" s="50" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="T20" s="50"/>
     </row>
     <row r="21">
       <c r="A21" s="49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" s="50"/>
       <c r="C21" s="50" t="n">

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
   <si>
     <t>Duration</t>
   </si>
@@ -229,43 +229,40 @@
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>Apr 18, 2026 11:24:28 AM</t>
+    <t>Apr 28, 2026 2:06:24 PM</t>
   </si>
   <si>
-    <t>Apr 18, 2026 11:21:17 AM</t>
+    <t>Apr 28, 2026 2:06:15 PM</t>
   </si>
   <si>
-    <t>Apr 18, 2026 11:24:25 AM</t>
+    <t>Apr 28, 2026 2:06:22 PM</t>
   </si>
   <si>
-    <t>3 m 7.389 s</t>
+    <t>7.058 s</t>
   </si>
   <si>
     <t>0%</t>
   </si>
   <si>
-    <t>67%</t>
+    <t>@TC_UI_Zlaata_Review_01</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_Stock_01</t>
+    <t>@Regression</t>
   </si>
   <si>
-    <t>@Stock</t>
+    <t>Verify Review Flow</t>
   </si>
   <si>
-    <t>Place Order Based on Product Stock Availability</t>
+    <t>TC_UI_Zlaata_Review_01 |Verify user able to  give review in user app.| "TD_UI_Zlaata_Review_01"</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</t>
+    <t>5.992 s</t>
   </si>
   <si>
-    <t>3 m 5.563 s</t>
+    <t>6.007 s</t>
   </si>
   <si>
-    <t>3 m 5.580 s</t>
-  </si>
-  <si>
-    <t>Then the after order placed and shows Out of Stock</t>
+    <t>Given user gives review</t>
   </si>
   <si>
     <t/>
@@ -872,10 +869,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Review_01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@Stock</c:v>
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -943,10 +940,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Review_01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@Stock</c:v>
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1014,10 +1011,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Review_01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@Stock</c:v>
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1247,7 +1244,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                  <c:v>Verify Review Flow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1314,7 +1311,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                  <c:v>Verify Review Flow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1381,7 +1378,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                  <c:v>Verify Review Flow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2546,7 +2543,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                  <c:v>Verify Review Flow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2613,7 +2610,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                  <c:v>Verify Review Flow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2680,7 +2677,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Place Order Based on Product Stock Availability</c:v>
+                  <c:v>Verify Review Flow</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2909,7 +2906,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Review_01 |Verify user able to  give review in user app.| "TD_UI_Zlaata_Review_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2917,12 +2914,7 @@
           <c:val>
             <c:numRef>
               <c:f>'DB Data'!$R$20</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -2981,7 +2973,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Review_01 |Verify user able to  give review in user app.| "TD_UI_Zlaata_Review_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2989,7 +2981,12 @@
           <c:val>
             <c:numRef>
               <c:f>'DB Data'!$T$20</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3048,7 +3045,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Review_01 |Verify user able to  give review in user app.| "TD_UI_Zlaata_Review_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4027,7 +4024,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Review_01 |Verify user able to  give review in user app.| "TD_UI_Zlaata_Review_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4035,12 +4032,7 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$H$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4099,7 +4091,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Review_01 |Verify user able to  give review in user app.| "TD_UI_Zlaata_Review_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4107,7 +4099,12 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$J$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -4166,7 +4163,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Stock_01 |Place order when stock is available.| "TD_UI_Zlaata_Stock_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Review_01 |Verify user able to  give review in user app.| "TD_UI_Zlaata_Review_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4582,10 +4579,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Review_01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@Stock</c:v>
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4652,10 +4649,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Review_01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@Stock</c:v>
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4722,10 +4719,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Stock_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Review_01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@Stock</c:v>
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8440,15 +8437,15 @@
     </row>
     <row r="39">
       <c r="B39" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39" s="52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D39" s="49"/>
       <c r="E39" s="49"/>
       <c r="F39" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G39" s="53" t="s">
         <v>40</v>
@@ -8456,15 +8453,15 @@
     </row>
     <row r="40">
       <c r="B40" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="52" t="s">
         <v>73</v>
-      </c>
-      <c r="C40" s="52" t="s">
-        <v>74</v>
       </c>
       <c r="D40" s="49"/>
       <c r="E40" s="49"/>
       <c r="F40" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G40" s="53" t="s">
         <v>40</v>
@@ -8501,14 +8498,14 @@
     </row>
     <row r="63">
       <c r="B63" s="52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" s="49"/>
       <c r="D63" s="53" t="s">
         <v>40</v>
       </c>
       <c r="E63" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F63" s="49"/>
       <c r="G63" s="53" t="s">
@@ -8516,7 +8513,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="C9E9" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="C35F" scenarios="true" objects="true"/>
   <mergeCells count="9">
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="B62:C62"/>
@@ -8595,30 +8592,30 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="50" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H22" s="55" t="n">
         <v>2.0</v>
       </c>
+      <c r="H22" s="55"/>
       <c r="I22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="J22" s="57"/>
+      <c r="J22" s="57" t="n">
+        <v>1.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8678,7 +8675,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" s="50" t="n">
         <v>1.0</v>
@@ -8694,7 +8691,7 @@
     </row>
     <row r="23">
       <c r="B23" s="51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="50" t="n">
         <v>1.0</v>
@@ -8728,17 +8725,17 @@
     </row>
     <row r="28">
       <c r="B28" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" s="49"/>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
       <c r="G28" s="49"/>
       <c r="H28" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I28" s="53" t="s">
         <v>40</v>
@@ -8746,17 +8743,17 @@
     </row>
     <row r="29">
       <c r="B29" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="52" t="s">
         <v>73</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>74</v>
       </c>
       <c r="D29" s="49"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
       <c r="G29" s="49"/>
       <c r="H29" s="52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I29" s="53" t="s">
         <v>40</v>
@@ -8853,13 +8850,13 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>1.0</v>
@@ -8873,15 +8870,15 @@
         <v>70</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="K22" s="55" t="n">
         <v>2.0</v>
       </c>
+      <c r="K22" s="55"/>
       <c r="L22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="M22" s="57"/>
+      <c r="M22" s="57" t="n">
+        <v>1.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8922,20 +8919,20 @@
     </row>
     <row r="3">
       <c r="B3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="52" t="s">
-        <v>75</v>
-      </c>
       <c r="D3" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="52" t="s">
         <v>78</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="EEA5" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="D8DB" scenarios="true" objects="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -8993,9 +8990,7 @@
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" t="n" s="0">
-        <v>2.0</v>
-      </c>
+      <c r="H2" s="0"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
@@ -9041,7 +9036,9 @@
       <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4" s="0"/>
+      <c r="H4" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
@@ -9066,7 +9063,7 @@
         <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9083,7 +9080,7 @@
         <v>70</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -9143,7 +9140,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s" s="49">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="50"/>
       <c r="C20" s="50" t="n">
@@ -9151,7 +9148,7 @@
       </c>
       <c r="D20" s="50"/>
       <c r="H20" t="s" s="49">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s" s="49">
         <v>40</v>
@@ -9162,22 +9159,22 @@
       </c>
       <c r="L20" s="50"/>
       <c r="P20" t="s" s="49">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q20" t="s" s="49">
         <v>40</v>
       </c>
-      <c r="R20" s="50" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="R20" s="50"/>
       <c r="S20" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="T20" s="50"/>
+      <c r="T20" s="50" t="n">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="50"/>
       <c r="C21" s="50" t="n">

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -13,31 +13,23 @@
     <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" tabRatio="785"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="13" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="14" r:id="rId2"/>
-    <sheet name="Tags" sheetId="18" r:id="rId3"/>
-    <sheet name="Features" sheetId="16" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="11" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="3" r:id="rId2"/>
+    <sheet name="Tags" sheetId="4" r:id="rId3"/>
+    <sheet name="Features" sheetId="2" r:id="rId4"/>
+    <sheet name="Exceptions" sheetId="12" r:id="rId5"/>
     <sheet name="DB Data" sheetId="5" r:id="rId8" state="veryHidden"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="Chart1" localSheetId="3">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="1">Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="2">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1">#REF!</definedName>
-    <definedName name="Chart10">#REF!</definedName>
-    <definedName name="Chart30">#REF!</definedName>
-    <definedName name="Chart49">#REF!</definedName>
-    <definedName name="Chart51">#REF!</definedName>
+    <definedName name="Chart1">Scenarios!#REF!</definedName>
+    <definedName name="Chart51">Scenarios!#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="80">
   <si>
     <t>Duration</t>
   </si>
@@ -96,6 +88,9 @@
     <t>STATUS</t>
   </si>
   <si>
+    <t>FEATURE STATUS</t>
+  </si>
+  <si>
     <t>Features Total</t>
   </si>
   <si>
@@ -111,43 +106,109 @@
     <t>Excel Extent Report</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:16 PM</t>
+    <t>TAG</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:14 PM</t>
+    <t>Scenario Passed</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:15 PM</t>
+    <t>Scenario Failed</t>
   </si>
   <si>
-    <t>0.252 s</t>
+    <t>Scenario Skipped</t>
+  </si>
+  <si>
+    <t>Tag Name</t>
+  </si>
+  <si>
+    <t>Feature Name</t>
+  </si>
+  <si>
+    <t>Feature Status</t>
+  </si>
+  <si>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>Scenario Status</t>
+  </si>
+  <si>
+    <t>Step Passed</t>
+  </si>
+  <si>
+    <t>Step Failed</t>
+  </si>
+  <si>
+    <t>Step Skipped</t>
+  </si>
+  <si>
+    <t>FEATURE FAIL SKIP</t>
+  </si>
+  <si>
+    <t>SCENARIO FAIL SKIP</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>0.013 s</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>0.022 s</t>
+    <t>FAILED &amp; SKIPPED TAGS</t>
   </si>
   <si>
     <t>TAG NAME</t>
   </si>
   <si>
+    <t>FAILED &amp; SKIPPED SCENARIOS</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:11 PM</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:09 PM</t>
+  </si>
+  <si>
+    <t>0.253 s</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>0.015 s</t>
+  </si>
+  <si>
+    <t>0.023 s</t>
+  </si>
+  <si>
+    <t>tag1</t>
+  </si>
+  <si>
     <t>tag</t>
+  </si>
+  <si>
+    <t>STACKTRACE</t>
   </si>
   <si>
     <t>STEP / HOOK TEXT</t>
   </si>
   <si>
-    <t>STACKTRACE</t>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>STEPS</t>
+  </si>
+  <si>
+    <t>SCENARIOS</t>
+  </si>
+  <si>
+    <t>NAME</t>
   </si>
   <si>
     <t>SCENARIO</t>
@@ -156,73 +217,321 @@
     <t>FEATURE</t>
   </si>
   <si>
-    <t>STEPS</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>SCENARIOS</t>
-  </si>
-  <si>
     <t>PASS %</t>
   </si>
   <si>
     <t>AUTHOR NAME</t>
   </si>
   <si>
-    <t>author</t>
+    <t>device</t>
   </si>
   <si>
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>device</t>
+    <t>May 04, 2026 6:58:29 pm</t>
   </si>
   <si>
-    <t>May 02, 2026 12:15:58 PM</t>
+    <t>May 04, 2026 6:58:08 pm</t>
   </si>
   <si>
-    <t>May 02, 2026 12:13:25 PM</t>
+    <t>May 04, 2026 6:58:28 pm</t>
   </si>
   <si>
-    <t>May 02, 2026 12:15:57 PM</t>
+    <t>19.503 s</t>
   </si>
   <si>
-    <t>2 m 31.353 s</t>
+    <t>0%</t>
   </si>
   <si>
-    <t>100%</t>
+    <t>@TC_UI_Zlaata_ExpressDelivery_01</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_Review_02 |Verify user able to  give My Order review in user app.| "TD_UI_Zlaata_Review_02"</t>
+    <t>This is Express Delivery feature</t>
   </si>
   <si>
-    <t>2 m 30.452 s</t>
+    <t>TC_UI_Zlaata_ExpressDelivery_01|Verify that Express delivery functionality is working fine| "TD_UI_Zlaata_ExpressDelivery_01"</t>
   </si>
   <si>
-    <t>Verify Review Flow</t>
+    <t>18.768 s</t>
   </si>
   <si>
-    <t>@Review</t>
+    <t>18.772 s</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_Review_02</t>
+    <t>Given the user verifies that Express delivery functionality is working fine</t>
   </si>
   <si>
-    <t>@Regression</t>
+    <t xml:space="preserve">org.openqa.selenium.json.JsonException: java.lang.reflect.InvocationTargetException
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.6'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [d2e6a4e66aa5850112d29bf076afd9be, actions {actions=[org.openqa.selenium.interactions.Sequence@775f15fd]}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 147.0.7727.139, chrome: {chromedriverVersion: 147.0.7727.117 (474cc805edd..., userDataDir: C:\Users\GOWTHA~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:50184}, goog:processID: 18904, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:50184/devtoo..., se:cdpVersion: 147.0.7727.139, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: d2e6a4e66aa5850112d29bf076afd9be
+	at org.openqa.selenium.json.JsonOutput.convertUsingMethod(JsonOutput.java:362)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$16(JsonOutput.java:154)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:287)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$22(JsonOutput.java:169)
+	at java.base/java.util.stream.ForEachOps$ForEachOp$OfRef.accept(ForEachOps.java:184)
+	at java.base/java.util.stream.ReferencePipeline$2$1.accept(ReferencePipeline.java:179)
+	at java.base/java.util.Iterator.forEachRemaining(Iterator.java:133)
+	at java.base/java.util.Spliterators$IteratorSpliterator.forEachRemaining(Spliterators.java:1939)
+	at java.base/java.util.stream.AbstractPipeline.copyInto(AbstractPipeline.java:509)
+	at java.base/java.util.stream.AbstractPipeline.wrapAndCopyInto(AbstractPipeline.java:499)
+	at java.base/java.util.stream.ForEachOps$ForEachOp.evaluateSequential(ForEachOps.java:151)
+	at java.base/java.util.stream.ForEachOps$ForEachOp$OfRef.evaluateSequential(ForEachOps.java:174)
+	at java.base/java.util.stream.AbstractPipeline.evaluate(AbstractPipeline.java:234)
+	at java.base/java.util.stream.ReferencePipeline.forEach(ReferencePipeline.java:596)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$23(JsonOutput.java:169)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:287)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$24(JsonOutput.java:182)
+	at java.base/java.util.Map.forEach(Map.java:733)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$25(JsonOutput.java:177)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:287)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:278)
+	at org.openqa.selenium.json.Json.toJson(Json.java:42)
+	at org.openqa.selenium.remote.codec.AbstractHttpCommandCodec.encode(AbstractHttpCommandCodec.java:236)
+	at org.openqa.selenium.remote.codec.AbstractHttpCommandCodec.encode(AbstractHttpCommandCodec.java:109)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:203)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.RemoteWebDriver.perform(RemoteWebDriver.java:630)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$o28ihqR3.perform(Unknown Source)
+	at org.openqa.selenium.interactions.Actions$BuiltAction.perform(Actions.java:616)
+	at org.openqa.selenium.interactions.Actions.perform(Actions.java:581)
+	at pages.ExpressDeliveryPage.RandomProduct(ExpressDeliveryPage.java:135)
+	at pages.ExpressDeliveryPage.verifyExpressDeliveryYesAndNo(ExpressDeliveryPage.java:185)
+	at stepDef.ExpressDeliveryStepDef.the_user_verifies_that_express_delivery_functionality_is_working_fine(ExpressDeliveryStepDef.java:25)
+	at ✽.the user verifies that Express delivery functionality is working fine(file:///C:/Users/gowthamraj/git/ZlaataQAsever04052026/src/test/resources/features/ExpressDelivery/expressDelivery.feature:14)
+	Suppressed: org.openqa.selenium.json.JsonException: Attempting to close incomplete json stream
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.6'
+Driver info: driver.version: RemoteWebDriver
+		at org.openqa.selenium.json.JsonOutput.close(JsonOutput.java:303)
+		at org.openqa.selenium.json.Json.toJson(Json.java:40)
+		at org.openqa.selenium.remote.codec.AbstractHttpCommandCodec.encode(AbstractHttpCommandCodec.java:236)
+		at org.openqa.selenium.remote.codec.AbstractHttpCommandCodec.encode(AbstractHttpCommandCodec.java:109)
+		at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:203)
+		at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+		at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+		at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+		at org.openqa.selenium.remote.RemoteWebDriver.perform(RemoteWebDriver.java:630)
+		at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+		at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+		at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+		at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+		at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+		at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$o28ihqR3.perform(Unknown Source)
+		at org.openqa.selenium.interactions.Actions$BuiltAction.perform(Actions.java:616)
+		at org.openqa.selenium.interactions.Actions.perform(Actions.java:581)
+		at pages.ExpressDeliveryPage.RandomProduct(ExpressDeliveryPage.java:135)
+		at pages.ExpressDeliveryPage.verifyExpressDeliveryYesAndNo(ExpressDeliveryPage.java:185)
+		at stepDef.ExpressDeliveryStepDef.the_user_verifies_that_express_delivery_functionality_is_working_fine(ExpressDeliveryStepDef.java:25)
+		at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+		at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+		at io.cucumber.java.Invoker.doInvoke(Invoker.java:66)
+		at io.cucumber.java.Invoker.invoke(Invoker.java:24)
+		at io.cucumber.java.AbstractGlueDefinition.invokeMethod(AbstractGlueDefinition.java:47)
+		at io.cucumber.java.JavaStepDefinition.execute(JavaStepDefinition.java:29)
+		at io.cucumber.core.runner.CoreStepDefinition.execute(CoreStepDefinition.java:66)
+		at io.cucumber.core.runner.PickleStepDefinitionMatch.runStep(PickleStepDefinitionMatch.java:63)
+		at io.cucumber.core.runner.ExecutionMode$1.execute(ExecutionMode.java:10)
+		at io.cucumber.core.runner.TestStep.executeStep(TestStep.java:92)
+		at io.cucumber.core.runner.TestStep.run(TestStep.java:64)
+		at io.cucumber.core.runner.PickleStepTestStep.run(PickleStepTestStep.java:51)
+		at io.cucumber.core.runner.TestCase.run(TestCase.java:104)
+		at io.cucumber.core.runner.Runner.runPickle(Runner.java:71)
+		at io.cucumber.junit.PickleRunners$NoStepDescriptions.run(PickleRunners.java:151)
+		at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:135)
+		at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:27)
+		at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+		at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+		at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+		at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+		at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+		at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+		at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+		at io.cucumber.junit.Cucumber.runChild(Cucumber.java:199)
+		at io.cucumber.junit.Cucumber.runChild(Cucumber.java:90)
+		at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+		at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+		at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+		at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+		at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+		at io.cucumber.junit.Cucumber$RunCucumber.evaluate(Cucumber.java:234)
+		at org.junit.internal.runners.statements.RunAfters.evaluate(RunAfters.java:27)
+		at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+		at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+		at org.eclipse.jdt.internal.junit4.runner.JUnit4TestReference.run(JUnit4TestReference.java:93)
+		at org.eclipse.jdt.internal.junit.runner.TestExecution.run(TestExecution.java:40)
+		at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:520)
+		at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:748)
+		at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.run(RemoteTestRunner.java:443)
+		at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.main(RemoteTestRunner.java:211)
+Caused by: java.lang.reflect.InvocationTargetException
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:118)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+	at org.openqa.selenium.json.JsonOutput.convertUsingMethod(JsonOutput.java:358)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$16(JsonOutput.java:154)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:287)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$22(JsonOutput.java:169)
+	at java.base/java.util.stream.ForEachOps$ForEachOp$OfRef.accept(ForEachOps.java:184)
+	at java.base/java.util.stream.ReferencePipeline$2$1.accept(ReferencePipeline.java:179)
+	at java.base/java.util.Iterator.forEachRemaining(Iterator.java:133)
+	at java.base/java.util.Spliterators$IteratorSpliterator.forEachRemaining(Spliterators.java:1939)
+	at java.base/java.util.stream.AbstractPipeline.copyInto(AbstractPipeline.java:509)
+	at java.base/java.util.stream.AbstractPipeline.wrapAndCopyInto(AbstractPipeline.java:499)
+	at java.base/java.util.stream.ForEachOps$ForEachOp.evaluateSequential(ForEachOps.java:151)
+	at java.base/java.util.stream.ForEachOps$ForEachOp$OfRef.evaluateSequential(ForEachOps.java:174)
+	at java.base/java.util.stream.AbstractPipeline.evaluate(AbstractPipeline.java:234)
+	at java.base/java.util.stream.ReferencePipeline.forEach(ReferencePipeline.java:596)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$23(JsonOutput.java:169)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:287)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$24(JsonOutput.java:182)
+	at java.base/java.util.Map.forEach(Map.java:733)
+	at org.openqa.selenium.json.JsonOutput.lambda$new$25(JsonOutput.java:177)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:287)
+	at org.openqa.selenium.json.JsonOutput.write(JsonOutput.java:278)
+	at org.openqa.selenium.json.Json.toJson(Json.java:42)
+	at org.openqa.selenium.remote.codec.AbstractHttpCommandCodec.encode(AbstractHttpCommandCodec.java:236)
+	at org.openqa.selenium.remote.codec.AbstractHttpCommandCodec.encode(AbstractHttpCommandCodec.java:109)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:203)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.RemoteWebDriver.perform(RemoteWebDriver.java:630)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$o28ihqR3.perform(Unknown Source)
+	at org.openqa.selenium.interactions.Actions$BuiltAction.perform(Actions.java:616)
+	at org.openqa.selenium.interactions.Actions.perform(Actions.java:581)
+	at pages.ExpressDeliveryPage.RandomProduct(ExpressDeliveryPage.java:135)
+	at pages.ExpressDeliveryPage.verifyExpressDeliveryYesAndNo(ExpressDeliveryPage.java:185)
+	at stepDef.ExpressDeliveryStepDef.the_user_verifies_that_express_delivery_functionality_is_working_fine(ExpressDeliveryStepDef.java:25)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+	at io.cucumber.java.Invoker.doInvoke(Invoker.java:66)
+	at io.cucumber.java.Invoker.invoke(Invoker.java:24)
+	at io.cucumber.java.AbstractGlueDefinition.invokeMethod(AbstractGlueDefinition.java:47)
+	at io.cucumber.java.JavaStepDefinition.execute(JavaStepDefinition.java:29)
+	at io.cucumber.core.runner.CoreStepDefinition.execute(CoreStepDefinition.java:66)
+	at io.cucumber.core.runner.PickleStepDefinitionMatch.runStep(PickleStepDefinitionMatch.java:63)
+	at io.cucumber.core.runner.ExecutionMode$1.execute(ExecutionMode.java:10)
+	at io.cucumber.core.runner.TestStep.executeStep(TestStep.java:92)
+	at io.cucumber.core.runner.TestStep.run(TestStep.java:64)
+	at io.cucumber.core.runner.PickleStepTestStep.run(PickleStepTestStep.java:51)
+	at io.cucumber.core.runner.TestCase.run(TestCase.java:104)
+	at io.cucumber.core.runner.Runner.runPickle(Runner.java:71)
+	at io.cucumber.junit.PickleRunners$NoStepDescriptions.run(PickleRunners.java:151)
+	at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:135)
+	at io.cucumber.junit.FeatureRunner.runChild(FeatureRunner.java:27)
+	at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+	at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+	at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+	at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+	at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+	at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+	at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+	at io.cucumber.junit.Cucumber.runChild(Cucumber.java:199)
+	at io.cucumber.junit.Cucumber.runChild(Cucumber.java:90)
+	at org.junit.runners.ParentRunner$4.run(ParentRunner.java:331)
+	at org.junit.runners.ParentRunner$1.schedule(ParentRunner.java:79)
+	at org.junit.runners.ParentRunner.runChildren(ParentRunner.java:329)
+	at org.junit.runners.ParentRunner.access$100(ParentRunner.java:66)
+	at org.junit.runners.ParentRunner$2.evaluate(ParentRunner.java:293)
+	at io.cucumber.junit.Cucumber$RunCucumber.evaluate(Cucumber.java:234)
+	at org.junit.internal.runners.statements.RunAfters.evaluate(RunAfters.java:27)
+	at org.junit.runners.ParentRunner$3.evaluate(ParentRunner.java:306)
+	at org.junit.runners.ParentRunner.run(ParentRunner.java:413)
+	at org.eclipse.jdt.internal.junit4.runner.JUnit4TestReference.run(JUnit4TestReference.java:93)
+	at org.eclipse.jdt.internal.junit.runner.TestExecution.run(TestExecution.java:40)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:520)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.runTests(RemoteTestRunner.java:748)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.run(RemoteTestRunner.java:443)
+	at org.eclipse.jdt.internal.junit.runner.RemoteTestRunner.main(RemoteTestRunner.java:211)
+Caused by: org.openqa.selenium.NoSuchSessionException: invalid session id: session deleted as the browser has closed the connection
+from disconnected: unable to send message to renderer
+  (Session info: chrome=147.0.7727.139)
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.6'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [d2e6a4e66aa5850112d29bf076afd9be, findElement {using=xpath, value=//a[normalize-space()='dresses']}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 147.0.7727.139, chrome: {chromedriverVersion: 147.0.7727.117 (474cc805edd..., userDataDir: C:\Users\GOWTHA~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:50184}, goog:processID: 18904, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:50184/devtoo..., se:cdpVersion: 147.0.7727.139, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: d2e6a4e66aa5850112d29bf076afd9be
+	at java.base/jdk.internal.reflect.DirectConstructorHandleAccessor.newInstance(DirectConstructorHandleAccessor.java:62)
+	at java.base/java.lang.reflect.Constructor.newInstanceWithCaller(Constructor.java:502)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:486)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.ElementLocation$ElementFinder$2.findElement(ElementLocation.java:165)
+	at org.openqa.selenium.remote.ElementLocation.findElement(ElementLocation.java:59)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:367)
+	at org.openqa.selenium.remote.RemoteWebDriver.findElement(RemoteWebDriver.java:361)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$o28ihqR3.findElement(Unknown Source)
+	at org.openqa.selenium.support.pagefactory.DefaultElementLocator.findElement(DefaultElementLocator.java:68)
+	at org.openqa.selenium.support.pagefactory.internal.LocatingElementHandler.invoke(LocatingElementHandler.java:38)
+	at jdk.proxy2/jdk.proxy2.$Proxy49.getWrappedElement(Unknown Source)
+	at org.openqa.selenium.interactions.PointerInput$Origin.asArg(PointerInput.java:262)
+	at org.openqa.selenium.interactions.PointerInput$Move.encode(PointerInput.java:211)
+	at org.openqa.selenium.interactions.Sequence.encode(Sequence.java:74)
+	at org.openqa.selenium.interactions.Sequence.toJson(Sequence.java:83)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	... 82 more
+</t>
   </si>
   <si>
-    <t>2 m 30.458 s</t>
+    <t>stepDef.Hooks.tearDown(io.cucumber.java.Scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.NoSuchSessionException: invalid session id
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.6'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [d2e6a4e66aa5850112d29bf076afd9be, screenshot {}]
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 147.0.7727.139, chrome: {chromedriverVersion: 147.0.7727.117 (474cc805edd..., userDataDir: C:\Users\GOWTHA~1\AppData\L...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:50184}, goog:processID: 18904, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:50184/devtoo..., se:cdpVersion: 147.0.7727.139, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: d2e6a4e66aa5850112d29bf076afd9be
+	at java.base/jdk.internal.reflect.DirectConstructorHandleAccessor.newInstance(DirectConstructorHandleAccessor.java:62)
+	at java.base/java.lang.reflect.Constructor.newInstanceWithCaller(Constructor.java:502)
+	at java.base/java.lang.reflect.Constructor.newInstance(Constructor.java:486)
+	at org.openqa.selenium.remote.ErrorCodec.decode(ErrorCodec.java:167)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:138)
+	at org.openqa.selenium.remote.codec.w3c.W3CHttpResponseCodec.decode(W3CHttpResponseCodec.java:50)
+	at org.openqa.selenium.remote.HttpCommandExecutor.execute(HttpCommandExecutor.java:215)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.invokeExecute(DriverCommandExecutor.java:216)
+	at org.openqa.selenium.remote.service.DriverCommandExecutor.execute(DriverCommandExecutor.java:174)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:544)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:617)
+	at org.openqa.selenium.remote.RemoteWebDriver.execute(RemoteWebDriver.java:621)
+	at org.openqa.selenium.remote.RemoteWebDriver.getScreenshotAs(RemoteWebDriver.java:333)
+	at java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(DirectMethodHandleAccessor.java:103)
+	at java.base/java.lang.reflect.Method.invoke(Method.java:580)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.call(WebDriverDecorator.java:315)
+	at org.openqa.selenium.support.decorators.DefaultDecorated.call(DefaultDecorated.java:48)
+	at org.openqa.selenium.support.decorators.WebDriverDecorator.lambda$createProxyFactory$3(WebDriverDecorator.java:405)
+	at net.bytebuddy.renamed.java.lang.Object$ByteBuddy$o28ihqR3.getScreenshotAs(Unknown Source)
+	at utils.ExcelReportUtil.captureScreenshot(ExcelReportUtil.java:68)
+	at stepDef.Hooks.tearDown(Hooks.java:298)
+</t>
   </si>
 </sst>
 </file>
@@ -230,7 +539,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="0"/>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +550,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -290,9 +623,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FF51FF21"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,7 +649,7 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FF51FF21"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -323,7 +662,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
-      <color rgb="00FF00"/>
+      <color rgb="FF0000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color rgb="FF0000"/>
       <b val="true"/>
     </font>
     <font>
@@ -351,11 +695,6 @@
       <sz val="11.0"/>
       <b val="true"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="00FF00"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -365,7 +704,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -380,6 +719,43 @@
       <right style="hair">
         <color auto="1"/>
       </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -447,9 +823,7 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
@@ -477,173 +851,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,24 +1041,30 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Features</a:t>
+              <a:t>Tags with</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> Failed &amp; Skipped Scenarios</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.1929905820595947E-3"/>
-          <c:y val="5.6284335775106678E-2"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -720,10 +1074,707 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11780714910636171"/>
-          <c:y val="8.0818739637467149E-2"/>
-          <c:w val="0.76899981252343452"/>
-          <c:h val="0.87885598708448542"/>
+          <c:x val="2.9880212949228394E-2"/>
+          <c:y val="0.11750877449771498"/>
+          <c:w val="0.95813725490196078"/>
+          <c:h val="0.84734403472530151"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Zlaata_ExpressDelivery_01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$B$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Zlaata_ExpressDelivery_01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$D$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>@TC_UI_Zlaata_ExpressDelivery_01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$C$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46151168"/>
+        <c:axId val="46117248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46151168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46117248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46117248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46151168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.3309046751669701E-2"/>
+          <c:y val="0.10919339164237124"/>
+          <c:w val="0.95333333333333337"/>
+          <c:h val="0.84804664723032075"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>This is Express Delivery feature</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$F$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$H$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>This is Express Delivery feature</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$H$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>This is Express Delivery feature</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$G$22</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46512000"/>
+        <c:axId val="46513536"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46512000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46513536"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46513536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46512000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3310417416097107E-2"/>
+          <c:y val="0.17399131020088515"/>
+          <c:w val="0.93298799578986624"/>
+          <c:h val="0.80271606659122552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -765,7 +1816,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000001-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -790,7 +1841,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000003-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -815,7 +1866,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000005-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -845,12 +1896,18 @@
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CEAE-4775-A1C6-116F718DC196}"/>
+              <c16:uniqueId val="{00000006-D2BC-4951-98B3-E41274AF2CA1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -886,7 +1943,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -912,15 +1969,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Devices</a:t>
+              <a:t>Authors</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -930,10 +1986,376 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Authors!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Authors!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AUTHOR NAME</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Authors!$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-77F2-4DDE-822F-16B38F6808E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Authors!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Authors!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AUTHOR NAME</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Authors!$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-77F2-4DDE-822F-16B38F6808E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Authors!$E$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Authors!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AUTHOR NAME</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Authors!$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-77F2-4DDE-822F-16B38F6808E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46589440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46590976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46590976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46589440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Devices</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -980,7 +2402,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
@@ -1003,14 +2424,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000000-FAA3-4CA3-AB56-81BA9F622F8E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1054,7 +2475,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
@@ -1084,7 +2504,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000001-FAA3-4CA3-AB56-81BA9F622F8E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1128,7 +2548,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
@@ -1151,14 +2570,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000002-FAA3-4CA3-AB56-81BA9F622F8E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1172,11 +2591,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1186,7 +2605,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1194,7 +2613,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1212,7 +2631,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -1220,14 +2639,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1281,12 +2699,745 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features with Failed &amp; Skipped</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> Scenarios</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.587826839649571E-2"/>
+          <c:y val="0.10654873856176561"/>
+          <c:w val="0.89369296921336749"/>
+          <c:h val="0.85018673119905308"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$J$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>This is Express Delivery feature</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$J$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9F7-4BBB-94B0-AEDC4FA75EC0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$L$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>This is Express Delivery feature</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$L$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>This is Express Delivery feature</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$K$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46193280"/>
+        <c:axId val="46285184"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46193280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46285184"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46285184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46193280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Scenarios</a:t>
+              <a:t>Scenarios with Failed &amp; Skipped Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0031919744642044E-2"/>
+          <c:y val="0.10668158781898149"/>
+          <c:w val="0.92990424076607392"/>
+          <c:h val="0.8499999379835731"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$R$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_ExpressDelivery_01|Verify that Express delivery functionality is working fine| "TD_UI_Zlaata_ExpressDelivery_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$R$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$S$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_ExpressDelivery_01|Verify that Express delivery functionality is working fine| "TD_UI_Zlaata_ExpressDelivery_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$T$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$T$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_ExpressDelivery_01|Verify that Express delivery functionality is working fine| "TD_UI_Zlaata_ExpressDelivery_01"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$S$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46328448"/>
+        <c:axId val="46408064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46328448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46408064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46408064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Steps</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46328448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Features</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1295,8 +3446,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.9364481457108926E-3"/>
-          <c:y val="3.2123800120282653E-2"/>
+          <c:x val="5.9362468167315514E-3"/>
+          <c:y val="6.4713026203216312E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1308,10 +3459,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.6498186400440001E-2"/>
-          <c:y val="0.10118873685128098"/>
-          <c:w val="0.87710436725913243"/>
-          <c:h val="0.86336406553156542"/>
+          <c:x val="7.3672686824927558E-2"/>
+          <c:y val="0.11902669624860428"/>
+          <c:w val="0.92151704085316477"/>
+          <c:h val="0.85596714084772552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1353,7 +3504,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000001-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1378,7 +3529,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000003-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1403,34 +3554,71 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000005-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$E$2:$E$4</c:f>
+              <c:f>'DB Data'!$C$2:$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Scenarios Passed</c:v>
+                  <c:v>Features Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Scenarios Failed</c:v>
+                  <c:v>Features Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scenarios Skipped</c:v>
+                  <c:v>Features Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$F$2:$F$4</c:f>
+              <c:f>'DB Data'!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1438,7 +3626,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F52A-4A06-BA5F-6C71FCEF3775}"/>
+              <c16:uniqueId val="{00000006-C5E1-437A-A52D-DCB97CB8ED06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1474,7 +3662,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1494,16 +3682,16 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr algn="ctr">
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1800" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Steps</a:t>
+              <a:t>Scenarios</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1512,8 +3700,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.6171728533933258E-3"/>
-          <c:y val="5.4421749273573204E-2"/>
+          <c:x val="5.9107001159738751E-3"/>
+          <c:y val="3.7140215132502832E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1525,10 +3713,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11769966254218223"/>
-          <c:y val="8.4263722654767198E-2"/>
-          <c:w val="0.78142825896762902"/>
-          <c:h val="0.89306054848124394"/>
+          <c:x val="5.6571751205517912E-2"/>
+          <c:y val="8.4536101166436714E-2"/>
+          <c:w val="0.92725874381981321"/>
+          <c:h val="0.88851560210722469"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1570,7 +3758,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000001-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1595,7 +3783,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000003-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1620,42 +3808,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000005-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:f>'DB Data'!$E$2:$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Steps Passed</c:v>
+                  <c:v>Scenarios Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Steps Failed</c:v>
+                  <c:v>Scenarios Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Steps Skipped</c:v>
+                  <c:v>Scenarios Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:f>'DB Data'!$F$2:$F$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-33E3-412A-9233-ED47CE12E57E}"/>
+              <c16:uniqueId val="{00000006-86A0-4454-A31A-15C1830346B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1691,7 +3916,261 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.0163677357506801E-2"/>
+          <c:y val="5.5749128919860627E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.6917458262785006E-2"/>
+          <c:y val="0.10406650388213669"/>
+          <c:w val="0.93302459414795369"/>
+          <c:h val="0.87775832898936412"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d prstMaterial="matte"/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="51FF21"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Steps Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Steps Failed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Steps Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2833-4D5B-98DA-2F8086DE2D67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="40"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId1"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1734,9 +4213,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.3309046751669701E-2"/>
+          <c:x val="3.3278738246891114E-2"/>
           <c:y val="0.10500003204542271"/>
-          <c:w val="0.95333333333333337"/>
+          <c:w val="0.953375796178344"/>
           <c:h val="0.85236429602767994"/>
         </c:manualLayout>
       </c:layout>
@@ -1794,7 +4273,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Review_02 |Verify user able to  give My Order review in user app.| "TD_UI_Zlaata_Review_02"</c:v>
+                  <c:v>TC_UI_Zlaata_ExpressDelivery_01|Verify that Express delivery functionality is working fine| "TD_UI_Zlaata_ExpressDelivery_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1802,17 +4281,12 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$H$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>3.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000000-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1866,7 +4340,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Review_02 |Verify user able to  give My Order review in user app.| "TD_UI_Zlaata_Review_02"</c:v>
+                  <c:v>TC_UI_Zlaata_ExpressDelivery_01|Verify that Express delivery functionality is working fine| "TD_UI_Zlaata_ExpressDelivery_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1879,7 +4353,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000002-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1933,7 +4407,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Review_02 |Verify user able to  give My Order review in user app.| "TD_UI_Zlaata_Review_02"</c:v>
+                  <c:v>TC_UI_Zlaata_ExpressDelivery_01|Verify that Express delivery functionality is working fine| "TD_UI_Zlaata_ExpressDelivery_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1941,12 +4415,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$I$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000001-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1960,11 +4439,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97185152"/>
-        <c:axId val="97201536"/>
+        <c:axId val="89325952"/>
+        <c:axId val="44310528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97185152"/>
+        <c:axId val="89325952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1974,7 +4453,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97201536"/>
+        <c:crossAx val="44310528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1982,7 +4461,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97201536"/>
+        <c:axId val="44310528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2014,7 +4493,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97185152"/>
+        <c:crossAx val="89325952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2043,7 +4522,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2109,7 +4588,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000001-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2134,7 +4613,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000003-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2159,7 +4638,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000005-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2187,14 +4666,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+              <c16:uniqueId val="{00000006-012F-4AE0-9B30-C14C76CB6C4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2235,7 +4720,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2261,7 +4746,7 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t>Tags</a:t>
@@ -2269,7 +4754,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -2279,10 +4763,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -2329,48 +4813,30 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
+              <c:f>Tags!$B$22</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>@Review</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_Review_02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
+                  <c:v>@TC_UI_Zlaata_ExpressDelivery_01</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$D$22:$D$24</c:f>
-              <c:numCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$D$22</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3911-4866-9AC3-280C20776CB8}"/>
+              <c16:uniqueId val="{00000000-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2414,37 +4880,30 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
+              <c:f>Tags!$B$22</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>@Review</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_Review_02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
+                  <c:v>@TC_UI_Zlaata_ExpressDelivery_01</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$F$22:$F$24</c:f>
+              <c:f>Tags!$F$22</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3911-4866-9AC3-280C20776CB8}"/>
+              <c16:uniqueId val="{00000001-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2488,37 +4947,35 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
+              <c:f>Tags!$B$22</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>@Review</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_Review_02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
+                  <c:v>@TC_UI_Zlaata_ExpressDelivery_01</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$E$22:$E$24</c:f>
-              <c:numCache/>
+              <c:f>Tags!$E$22</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3911-4866-9AC3-280C20776CB8}"/>
+              <c16:uniqueId val="{00000002-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2532,11 +4989,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2546,7 +5003,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2554,365 +5011,9 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Features</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="3.3369832880226151E-2"/>
-          <c:y val="9.72480620155039E-2"/>
-          <c:w val="0.95324817070407986"/>
-          <c:h val="0.8601162790697674"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify Review Flow</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$F$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$H$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify Review Flow</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$H$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$G$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify Review Flow</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$G$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97540352"/>
-        <c:axId val="97550336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97540352"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97550336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97550336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2942,566 +5043,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97540352"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-        <c:minorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.3310417416097107E-2"/>
-          <c:y val="0.17399131020088515"/>
-          <c:w val="0.93298799578986624"/>
-          <c:h val="0.80271606659122552"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d prstMaterial="matte"/>
-          </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="51FF21"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'DB Data'!$C$2:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Features Passed</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Features Failed</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Features Skipped</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'DB Data'!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-1678-4457-8DD3-1C4694EC7DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="40"/>
-      </c:doughnutChart>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId1"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Authors</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Authors!$D$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Authors!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>author</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Authors!$D$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C43D-4700-9C1F-8935523D5E0B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Authors!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Authors!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>author</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Authors!$F$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C43D-4700-9C1F-8935523D5E0B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Authors!$E$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Authors!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>author</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Authors!$E$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C43D-4700-9C1F-8935523D5E0B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97122176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97123712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3536,672 +5078,1681 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>43815</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>158115</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190500" y="142875"/>
-          <a:ext cx="3749040" cy="777240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Duration</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828924</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472439</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>127635</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486774" y="142875"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Start Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>165735</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486775" y="561975"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>End Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1019175" y="152401"/>
-          <a:ext cx="2933700" cy="771524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
-            <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>0.252 s</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3790950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9448800" y="142875"/>
-          <a:ext cx="2800350" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:14 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3809999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9467849" y="561975"/>
-          <a:ext cx="2771775" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:15 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
+      <xdr:colOff>57148</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7"/>
+        <xdr:cNvPr id="9" name="Group 8"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="190499" y="28576"/>
-          <a:ext cx="12045316" cy="3657600"/>
-          <a:chOff x="171449" y="36548"/>
-          <a:chExt cx="12045316" cy="3399182"/>
+          <a:off x="190498" y="0"/>
+          <a:ext cx="12068177" cy="3438525"/>
+          <a:chOff x="161923" y="0"/>
+          <a:chExt cx="12068177" cy="3438525"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="9" name="Group 8"/>
+          <xdr:cNvPr id="42" name="Group 41"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="171449" y="815528"/>
-            <a:ext cx="3749040" cy="2620202"/>
-            <a:chOff x="171449" y="815528"/>
-            <a:chExt cx="3749040" cy="2620202"/>
+            <a:off x="161923" y="0"/>
+            <a:ext cx="12068177" cy="3438525"/>
+            <a:chOff x="171448" y="19050"/>
+            <a:chExt cx="12068177" cy="3438525"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="13" name="Group 12"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="8477248" y="133350"/>
+              <a:ext cx="3762377" cy="685800"/>
+              <a:chOff x="8477248" y="133350"/>
+              <a:chExt cx="3762377" cy="685800"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="4" name="Rectangle 3"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477248" y="133350"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0" algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Start Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="5" name="Rectangle 4"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477249" y="495300"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>End Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="TextBox 6"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9563100" y="133351"/>
+                <a:ext cx="2676525" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="8" name="TextBox 7"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9572625" y="495300"/>
+                <a:ext cx="2667000" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="2" name="Group 100"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="171448" y="19050"/>
+              <a:ext cx="12054842" cy="3438525"/>
+              <a:chOff x="171448" y="19050"/>
+              <a:chExt cx="12054842" cy="3438525"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="10" name="Group 9"/>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="171448" y="19050"/>
+                <a:ext cx="12054842" cy="3438525"/>
+                <a:chOff x="152398" y="27696"/>
+                <a:chExt cx="12054842" cy="3195586"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="16" name="Group 15"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="152398" y="656192"/>
+                  <a:ext cx="3749040" cy="2563550"/>
+                  <a:chOff x="152398" y="656192"/>
+                  <a:chExt cx="3749040" cy="2563550"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="31" name="Rectangle 30"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="152398" y="815526"/>
+                    <a:ext cx="3749040" cy="2381198"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:grpSp>
+                <xdr:nvGrpSpPr>
+                  <xdr:cNvPr id="32" name="Group 31"/>
+                  <xdr:cNvGrpSpPr/>
+                </xdr:nvGrpSpPr>
+                <xdr:grpSpPr>
+                  <a:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="3621406" cy="2563550"/>
+                    <a:chOff x="247650" y="656192"/>
+                    <a:chExt cx="3621406" cy="2563550"/>
+                  </a:xfrm>
+                </xdr:grpSpPr>
+                <xdr:grpSp>
+                  <xdr:nvGrpSpPr>
+                    <xdr:cNvPr id="33" name="Group 32"/>
+                    <xdr:cNvGrpSpPr/>
+                  </xdr:nvGrpSpPr>
+                  <xdr:grpSpPr>
+                    <a:xfrm>
+                      <a:off x="2771776" y="859785"/>
+                      <a:ext cx="1097280" cy="764816"/>
+                      <a:chOff x="2771776" y="859785"/>
+                      <a:chExt cx="1097280" cy="764816"/>
+                    </a:xfrm>
+                  </xdr:grpSpPr>
+                  <xdr:sp macro="" textlink="">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="35" name="Rounded Rectangle 34"/>
+                      <xdr:cNvSpPr/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="2771776" y="859785"/>
+                        <a:ext cx="1097280" cy="764816"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="roundRect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:ln w="3175"/>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="2">
+                        <a:schemeClr val="dk1"/>
+                      </a:lnRef>
+                      <a:fillRef idx="1">
+                        <a:schemeClr val="lt1"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:schemeClr val="dk1"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>PASSED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>FAILED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>SKIPPED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>TOTAL</a:t>
+                        </a:r>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$2">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="36" name="TextBox 35"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="868694"/>
+                        <a:ext cx="485775" cy="247651"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="27F959"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="27F959"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$3">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="37" name="TextBox 36"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="1027977"/>
+                        <a:ext cx="485775" cy="251635"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FF0000"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>2</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$4">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="38" name="TextBox 37"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3371850" y="1187314"/>
+                        <a:ext cx="495300" cy="239006"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FFFF00"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FFFF00"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                </xdr:grpSp>
+                <xdr:graphicFrame macro="">
+                  <xdr:nvGraphicFramePr>
+                    <xdr:cNvPr id="34" name="FeatureDough"/>
+                    <xdr:cNvGraphicFramePr>
+                      <a:graphicFrameLocks/>
+                    </xdr:cNvGraphicFramePr>
+                  </xdr:nvGraphicFramePr>
+                  <xdr:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="2562225" cy="2563550"/>
+                  </xdr:xfrm>
+                  <a:graphic>
+                    <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                      <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+                    </a:graphicData>
+                  </a:graphic>
+                </xdr:graphicFrame>
+              </xdr:grpSp>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="17" name="Group 16"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="3981450" y="27696"/>
+                  <a:ext cx="4391026" cy="3177881"/>
+                  <a:chOff x="3981450" y="27696"/>
+                  <a:chExt cx="4391026" cy="3177881"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="25" name="Rectangle 24"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="3981450" y="133921"/>
+                    <a:ext cx="4391026" cy="3059265"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="26" name="Rounded Rectangle 25"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7143750" y="183252"/>
+                    <a:ext cx="1188720" cy="849796"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1600" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="27" name="TextBox 26"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="213640"/>
+                    <a:ext cx="542925" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="28" name="TextBox 27"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7772400" y="394614"/>
+                    <a:ext cx="542926" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$F$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="29" name="TextBox 28"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7781924" y="557888"/>
+                    <a:ext cx="533401" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>2</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="30" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="4019551" y="27696"/>
+                  <a:ext cx="3276600" cy="3177881"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="18" name="Group 17"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="8458200" y="682747"/>
+                  <a:ext cx="3749040" cy="2540535"/>
+                  <a:chOff x="8458200" y="682747"/>
+                  <a:chExt cx="3749040" cy="2540535"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="19" name="Rectangle 18"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="8458200" y="815526"/>
+                    <a:ext cx="3749040" cy="2379428"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="20" name="Rounded Rectangle 19"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11077576" y="856008"/>
+                    <a:ext cx="1097280" cy="764816"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1300" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1100">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$2">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="21" name="TextBox 20"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="859839"/>
+                    <a:ext cx="476250" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{ECACBD74-B5B9-479E-8C2E-C9684999A572}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="51FF21"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>6</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="51FF21"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$3">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="22" name="TextBox 21"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11658600" y="1023110"/>
+                    <a:ext cx="485776" cy="247651"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{E24417FB-CCF3-4060-A9AB-23F9E2CDA81A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FF0000"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="'DB Data'!$H$4">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="23" name="TextBox 22"/>
+                  <xdr:cNvSpPr txBox="1"/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="11668125" y="1177529"/>
+                    <a:ext cx="476250" cy="257174"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="9525" cmpd="sng">
+                    <a:noFill/>
+                  </a:ln>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:lnRef>
+                  <a:fillRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:scrgbClr r="0" g="0" b="0"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:fld id="{04B0E76C-90E2-4732-8606-78D62C393D8A}" type="TxLink">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                        <a:solidFill>
+                          <a:srgbClr val="FFFF00"/>
+                        </a:solidFill>
+                        <a:latin typeface="Calibri"/>
+                      </a:rPr>
+                      <a:pPr algn="ctr"/>
+                      <a:t>1</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" sz="1200" b="0">
+                      <a:solidFill>
+                        <a:srgbClr val="FFFF00"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:graphicFrame macro="">
+                <xdr:nvGraphicFramePr>
+                  <xdr:cNvPr id="24" name="FeatureDough"/>
+                  <xdr:cNvGraphicFramePr>
+                    <a:graphicFrameLocks/>
+                  </xdr:cNvGraphicFramePr>
+                </xdr:nvGraphicFramePr>
+                <xdr:xfrm>
+                  <a:off x="8572501" y="682747"/>
+                  <a:ext cx="2543174" cy="2540535"/>
+                </xdr:xfrm>
+                <a:graphic>
+                  <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                    <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+                  </a:graphicData>
+                </a:graphic>
+              </xdr:graphicFrame>
+            </xdr:grpSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="'DB Data'!$F$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="39" name="TextBox 38"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="7791450" y="781050"/>
+                <a:ext cx="542925" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C1C65169-A7E7-4F44-8F1B-A4A10551DED6}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>6</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$D$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="40" name="TextBox 39"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3390900" y="1438275"/>
+                <a:ext cx="495299" cy="257176"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C751D109-05C5-4D27-8561-41C7DB1DFED0}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>4</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1100" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="'DB Data'!$H$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="41" name="TextBox 40"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="11687174" y="1428750"/>
+                <a:ext cx="476251" cy="276725"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{9404FC27-F618-4129-9790-CCC5E3B452F7}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>8</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1200" b="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="Rectangle 23"/>
+            <xdr:cNvPr id="3" name="Rectangle 2"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="171449" y="952809"/>
-              <a:ext cx="3749040" cy="2464407"/>
+              <a:off x="171450" y="133349"/>
+              <a:ext cx="3749040" cy="685800"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
             <a:noFill/>
-            <a:ln w="6350"/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:ln>
           </xdr:spPr>
           <xdr:style>
             <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
             </a:lnRef>
             <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
+              <a:schemeClr val="accent1"/>
             </a:fillRef>
             <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="accent1"/>
             </a:effectRef>
             <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="lt1"/>
             </a:fontRef>
           </xdr:style>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Duration</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="27" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="419100" y="815528"/>
-            <a:ext cx="3238500" cy="2620202"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
       </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="10" name="Group 9"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
+      <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="TextBox 5"/>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
           <a:xfrm>
-            <a:off x="4000498" y="36548"/>
-            <a:ext cx="4389120" cy="3390329"/>
-            <a:chOff x="4000498" y="36548"/>
-            <a:chExt cx="4389120" cy="3390329"/>
+            <a:off x="990601" y="114300"/>
+            <a:ext cx="2924174" cy="676275"/>
           </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="Rectangle 17"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4000498" y="142772"/>
-              <a:ext cx="4389120" cy="3271713"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
             <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="23" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="4400550" y="36548"/>
-            <a:ext cx="3590925" cy="3390329"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="11" name="Group 10"/>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="8467725" y="806675"/>
-            <a:ext cx="3749040" cy="2609869"/>
-            <a:chOff x="8467725" y="806675"/>
-            <a:chExt cx="3749040" cy="2609869"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="Rectangle 11"/>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="8467725" y="952137"/>
-              <a:ext cx="3749040" cy="2464407"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="6350"/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="dk1"/>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="lt1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="dk1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="17" name="FeatureDough"/>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks/>
-            </xdr:cNvGraphicFramePr>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="8734425" y="806675"/>
-            <a:ext cx="3200400" cy="2602499"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </xdr:grpSp>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
+              <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:pPr algn="ctr"/>
+              <a:t>0.253 s</a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -4212,22 +6763,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35</cdr:x>
-      <cdr:y>0.34014</cdr:y>
+      <cdr:x>0.34572</cdr:x>
+      <cdr:y>0.37983</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.65294</cdr:x>
-      <cdr:y>0.69728</cdr:y>
+      <cdr:x>0.72119</cdr:x>
+      <cdr:y>0.71478</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1133475" y="952503"/>
-          <a:ext cx="981075" cy="1000125"/>
+          <a:off x="885825" y="1047749"/>
+          <a:ext cx="962024" cy="923925"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4353,7 +6904,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
+          <a:fld id="{790B2992-122F-4DED-8027-8C90CA641799}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4361,7 +6912,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4379,22 +6930,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.33156</cdr:x>
-      <cdr:y>0.36031</cdr:y>
+      <cdr:x>0.3343</cdr:x>
+      <cdr:y>0.34819</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.68208</cdr:x>
-      <cdr:y>0.70496</cdr:y>
+      <cdr:x>0.7064</cdr:x>
+      <cdr:y>0.70474</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1190625" y="1314450"/>
-          <a:ext cx="1258673" cy="1257300"/>
+          <a:off x="1095367" y="1190625"/>
+          <a:ext cx="1219223" cy="1219200"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4520,17 +7071,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{55E37DD8-520B-4F7A-9381-E422E7073C87}" type="TxLink">
+            <a:rPr lang="en-US" sz="3000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="3600" b="1">
+          <a:endParaRPr lang="en-US" sz="3000" b="1">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -4546,22 +7097,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.35119</cdr:x>
-      <cdr:y>0.35374</cdr:y>
+      <cdr:x>0.33708</cdr:x>
+      <cdr:y>0.36934</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.66667</cdr:x>
-      <cdr:y>0.71088</cdr:y>
+      <cdr:x>0.70786</cdr:x>
+      <cdr:y>0.71429</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$H$5">
+    <cdr:sp macro="" textlink="'DB Data'!$H$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1123950" y="990599"/>
-          <a:ext cx="1009650" cy="1000125"/>
+          <a:off x="857253" y="1009650"/>
+          <a:ext cx="942958" cy="942975"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -4687,7 +7238,7 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{31691118-B83C-4A2D-970E-D212AA344C2F}" type="TxLink">
+          <a:fld id="{0C07208B-2D34-4675-9C99-827455C82BF1}" type="TxLink">
             <a:rPr lang="en-US" sz="2400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
@@ -4695,7 +7246,7 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>75%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
             <a:solidFill>
@@ -4720,16 +7271,14 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4778,15 +7327,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>228601</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1508761</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>1508760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150494</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4795,8 +7344,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="323851" y="180974"/>
-          <a:ext cx="1280160" cy="352426"/>
+          <a:off x="323850" y="180974"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4831,6 +7380,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -4840,13 +7411,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>876300</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1514476</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>104553</xdr:rowOff>
+      <xdr:rowOff>85503</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$F$2">
       <xdr:nvSpPr>
@@ -4855,7 +7426,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="971550" y="219075"/>
+          <a:off x="971550" y="200025"/>
           <a:ext cx="638176" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4885,7 +7456,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{8D92AF4D-37D8-4C38-8EA4-79D629C4A437}" type="TxLink">
+          <a:fld id="{5E830E56-6EF0-481D-AF4F-B51C1C996EFA}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="51FF21"/>
@@ -4893,11 +7464,151 @@
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>2</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23284</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1504950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>99262</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962025" y="404284"/>
+          <a:ext cx="638175" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{BD0EF753-9A18-4975-B169-ECA4EE0CEA9F}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>866776</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1514476</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104219</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$F$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="962026" y="589494"/>
+          <a:ext cx="647700" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{A34595C3-6342-4982-8F51-D73860015449}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -4912,22 +7623,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.32161</cdr:x>
+      <cdr:y>0.41018</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.68844</cdr:x>
+      <cdr:y>0.71781</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$F$5">
+    <cdr:sp macro="" textlink="'DB Data'!$F$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="561975" y="933452"/>
-          <a:ext cx="952500" cy="923924"/>
+          <a:off x="609603" y="914412"/>
+          <a:ext cx="695317" cy="685798"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5053,17 +7764,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{EC401DB1-A780-48C9-8D04-3C77257FD87B}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{BB53D87E-07A1-498D-A732-07528C1BCE6E}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>33%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5082,20 +7793,18 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5117,22 +7826,20 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1800226</xdr:colOff>
+      <xdr:colOff>1800225</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5183,13 +7890,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>171449</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1451609</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5198,8 +7905,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="304799" y="190501"/>
-          <a:ext cx="1280160" cy="361950"/>
+          <a:off x="304799" y="190500"/>
+          <a:ext cx="1280160" cy="731520"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -5234,6 +7941,28 @@
             <a:t>PASSED</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FAILED</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SKIPPED</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -5243,22 +7972,22 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>847725</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1409700</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>114078</xdr:rowOff>
+      <xdr:rowOff>104553</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'DB Data'!$D$2">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
+        <xdr:cNvPr id="12" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="228600"/>
+          <a:off x="981075" y="219075"/>
           <a:ext cx="561975" cy="266478"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5288,19 +8017,156 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:fld id="{6831FE4E-352E-4F7B-A3D4-680EF38773CC}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
               <a:solidFill>
-                <a:srgbClr val="51FF21"/>
+                <a:srgbClr val="27F959"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>1</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1200" b="0">
             <a:solidFill>
-              <a:srgbClr val="51FF21"/>
+              <a:srgbClr val="27F959"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>847724</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32808</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1400175</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>108786</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$3">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="981074" y="413808"/>
+          <a:ext cx="552451" cy="266478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>2</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27519</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1419226</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>113744</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'DB Data'!$D$4">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="971550" y="599019"/>
+          <a:ext cx="581026" cy="276725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+            <a:rPr lang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t>1</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="1200" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -5315,22 +8181,22 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.28095</cdr:x>
-      <cdr:y>0.38583</cdr:y>
+      <cdr:x>0.33503</cdr:x>
+      <cdr:y>0.4149</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.75714</cdr:x>
-      <cdr:y>0.76772</cdr:y>
+      <cdr:x>0.70558</cdr:x>
+      <cdr:y>0.73808</cdr:y>
     </cdr:to>
-    <cdr:sp macro="" textlink="'DB Data'!$D$5">
+    <cdr:sp macro="" textlink="'DB Data'!$D$6">
       <cdr:nvSpPr>
         <cdr:cNvPr id="3" name="TextBox 21"/>
         <cdr:cNvSpPr txBox="1"/>
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="602111" y="1142827"/>
-          <a:ext cx="1020535" cy="1131157"/>
+          <a:off x="628650" y="904875"/>
+          <a:ext cx="695325" cy="704850"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5456,17 +8322,17 @@
         </a:lstStyle>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr algn="ctr"/>
-          <a:fld id="{5501BE5E-9668-4CE4-A888-5F85DFC126EE}" type="TxLink">
-            <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{CE425BBE-7C02-4C07-B111-60BA1CB56900}" type="TxLink">
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>1</a:t>
+            <a:t>25%</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1800" b="1">
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
@@ -5476,29 +8342,6 @@
     </cdr:sp>
   </cdr:relSizeAnchor>
 </c:userShapes>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Dashboard"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="Tags"/>
-      <sheetName val="Features"/>
-      <sheetName val="Exceptions"/>
-      <sheetName val="DB Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5788,7 +8631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B19:G62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="2.0"/>
@@ -5799,8 +8642,102 @@
     <col min="6" max="6" customWidth="true" width="70.7109375"/>
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
-  <sheetData/>
-  <sheetProtection sheet="true" password="A223" scenarios="true" objects="true"/>
+  <sheetData>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="6"/>
+    </row>
+    <row r="37" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="60" spans="2:7" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B60" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="38"/>
+      <c r="D61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="38"/>
+      <c r="G61" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" s="49"/>
+      <c r="D62" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E62" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="49"/>
+      <c r="G62" s="53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="FC0B" scenarios="true" objects="true"/>
+  <mergeCells count="8">
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5809,94 +8746,95 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B20:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.42578125"/>
-    <col min="2" max="2" customWidth="true" width="45.85546875"/>
+    <col min="2" max="2" customWidth="true" width="50.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
     <col min="5" max="5" customWidth="true" width="50.7109375"/>
-    <col min="6" max="6" customWidth="true" width="12.7109375"/>
+    <col min="6" max="6" customWidth="true" width="12.85546875"/>
     <col min="7" max="10" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+    <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>43</v>
+      <c r="J21" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="57" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H22" s="58" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="60"/>
+      <c r="B22" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="55"/>
+      <c r="I22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5906,174 +8844,106 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B20:I31"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="B20:I27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
-    <col min="2" max="2" customWidth="true" width="35.5703125"/>
+    <col min="2" max="2" customWidth="true" width="35.7109375"/>
     <col min="3" max="7" customWidth="true" width="12.7109375"/>
     <col min="8" max="8" customWidth="true" width="60.7109375"/>
     <col min="9" max="9" customWidth="true" width="18.7109375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="15.5703125"/>
   </cols>
   <sheetData>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48"/>
+      <c r="B20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="45"/>
-      <c r="C21" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>45</v>
+      <c r="B21" s="41"/>
+      <c r="C21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" t="s" s="54">
-        <v>58</v>
-      </c>
-      <c r="C22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="D22" s="58" t="n">
+      <c r="D22" s="55"/>
+      <c r="E22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="61" t="s">
-        <v>54</v>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="57" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D23" s="58" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E23" s="59"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="61" t="s">
-        <v>54</v>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="57" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D24" s="58" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E24" s="59"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="61" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I29" s="55" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" s="55" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I31" s="55" t="s">
-        <v>29</v>
+    <row r="27">
+      <c r="B27" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="5">
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6083,6 +8953,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B18:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6090,107 +8961,106 @@
     <col min="2" max="2" customWidth="true" width="60.7109375"/>
     <col min="3" max="3" customWidth="true" width="12.7109375"/>
     <col min="4" max="4" customWidth="true" width="16.7109375"/>
-    <col min="5" max="11" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" customWidth="true" width="12.7109375"/>
+    <col min="5" max="13" customWidth="true" width="9.7109375"/>
   </cols>
   <sheetData>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="4"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
+    <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>43</v>
+      <c r="H21" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="57" t="n">
+      <c r="B22" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="50" t="n">
         <v>1.0</v>
       </c>
-      <c r="F22" s="58" t="n">
+      <c r="F22" s="55"/>
+      <c r="G22" s="56" t="n">
         <v>1.0</v>
       </c>
-      <c r="G22" s="59"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="57" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="K22" s="58" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K22" s="55"/>
+      <c r="L22" s="56" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="J20:M20"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:I20"/>
-    <mergeCell ref="J20:M20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6198,10 +9068,70 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="1.7109375"/>
+    <col min="2" max="3" customWidth="true" width="30.7109375"/>
+    <col min="4" max="4" customWidth="true" width="45.7109375"/>
+    <col min="5" max="5" customWidth="true" width="75.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="true" password="C5A1" scenarios="true" objects="true"/>
+  <mergeCells count="2">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="14.7109375"/>
@@ -6209,7 +9139,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" width="16.42578125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="16.28515625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="3.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.5703125"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
     <col min="8" max="8" bestFit="true" customWidth="true" width="17.42578125"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="22.42578125"/>
@@ -6237,94 +9167,91 @@
         <v>1</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="D2" s="0"/>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="F2" t="n" s="0">
-        <v>1.0</v>
-      </c>
+      <c r="F2" s="0"/>
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" t="n" s="0">
-        <v>3.0</v>
-      </c>
+      <c r="H2" s="0"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D3" s="0"/>
-      <c r="E3" t="s">
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="F3"/>
-      <c r="G3" t="s">
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="H3"/>
+      <c r="H3" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s" s="0">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>8</v>
       </c>
       <c r="D4" s="0"/>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F4"/>
-      <c r="G4" t="s">
+      <c r="F4" s="0"/>
+      <c r="G4" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="H4"/>
+      <c r="H4" s="0"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="0">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n" s="0">
-        <f>SUM(D2:D4)</f>
         <v>1.0</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n" s="0">
-        <f>SUM(F2:F4)</f>
         <v>1.0</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n" s="0">
-        <f>SUM(H2:H4)</f>
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6332,32 +9259,116 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>54</v>
+        <v>69</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s" s="49">
+        <v>71</v>
+      </c>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="H20" t="s" s="49">
+        <v>72</v>
+      </c>
+      <c r="I20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L20" s="50"/>
+      <c r="P20" t="s" s="49">
+        <v>73</v>
+      </c>
+      <c r="Q20" t="s" s="49">
+        <v>40</v>
+      </c>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T20" s="50"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
   <si>
     <t>Duration</t>
   </si>
@@ -189,34 +189,37 @@
     <t>device</t>
   </si>
   <si>
-    <t>May 07, 2026 12:17:18 PM</t>
+    <t>May 11, 2026 2:02:59 pm</t>
   </si>
   <si>
-    <t>May 07, 2026 12:17:10 PM</t>
+    <t>May 11, 2026 1:55:42 pm</t>
   </si>
   <si>
-    <t>May 07, 2026 12:17:17 PM</t>
+    <t>May 11, 2026 2:02:57 pm</t>
   </si>
   <si>
-    <t>6.817 s</t>
+    <t>7 m 14.806 s</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_Estimate_01|Verify that Estimate delivery date functionality is working fine| "TD_UI_Zlaata_Estimate_01"</t>
+    <t>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</t>
   </si>
   <si>
-    <t>5.996 s</t>
+    <t>7 m 13.946 s</t>
   </si>
   <si>
     <t>This is Express Delivery feature</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_Estimate_01</t>
+    <t>@TC_UI_Zlaata_Estimate_02</t>
   </si>
   <si>
-    <t>6.002 s</t>
+    <t>@est</t>
+  </si>
+  <si>
+    <t>7 m 13.952 s</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1791,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Estimate_01|Verify that Estimate delivery date functionality is working fine| "TD_UI_Zlaata_Estimate_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1860,7 +1863,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Estimate_01|Verify that Estimate delivery date functionality is working fine| "TD_UI_Zlaata_Estimate_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1927,7 +1930,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Estimate_01|Verify that Estimate delivery date functionality is working fine| "TD_UI_Zlaata_Estimate_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2330,21 +2333,27 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Estimate_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Estimate_02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@est</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$D$22</c:f>
+              <c:f>Tags!$D$22:$D$23</c:f>
               <c:numCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2403,18 +2412,21 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Estimate_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Estimate_02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@est</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$F$22</c:f>
+              <c:f>Tags!$F$22:$F$23</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -2471,18 +2483,21 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Estimate_01</c:v>
+                  <c:v>@TC_UI_Zlaata_Estimate_02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@est</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$E$22</c:f>
+              <c:f>Tags!$E$22:$E$23</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -5770,7 +5785,7 @@
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
   <sheetData/>
-  <sheetProtection sheet="true" password="FF87" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="FA7B" scenarios="true" objects="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5876,7 +5891,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B20:I27"/>
+  <dimension ref="B20:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
@@ -5932,48 +5947,83 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="35" t="s">
+    <row r="23">
+      <c r="B23" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="58" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="61" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C27" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="36" t="s">
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="35" t="s">
+      <c r="I27" s="35" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="54" t="s">
+    <row r="28">
+      <c r="B28" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C28" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="62" t="s">
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="I27" s="55" t="s">
+      <c r="I28" s="55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="I29" s="55" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C26:G26"/>
     <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6064,7 +6114,7 @@
         <v>29</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="57" t="n">
         <v>1.0</v>

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Duration</t>
   </si>
@@ -189,37 +189,40 @@
     <t>device</t>
   </si>
   <si>
-    <t>May 11, 2026 2:02:59 pm</t>
+    <t>May 13, 2026 1:45:27 PM</t>
   </si>
   <si>
-    <t>May 11, 2026 1:55:42 pm</t>
+    <t>May 13, 2026 1:39:32 PM</t>
   </si>
   <si>
-    <t>May 11, 2026 2:02:57 pm</t>
+    <t>May 13, 2026 1:45:24 PM</t>
   </si>
   <si>
-    <t>7 m 14.806 s</t>
+    <t>5 m 52.417 s</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</t>
+    <t>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</t>
   </si>
   <si>
-    <t>7 m 13.946 s</t>
+    <t>5 m 50.808 s</t>
   </si>
   <si>
-    <t>This is Express Delivery feature</t>
+    <t>Verify New Label Feature</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_Estimate_02</t>
+    <t>@New</t>
   </si>
   <si>
-    <t>@est</t>
+    <t>@TC_UI_Zlaata_New_01</t>
   </si>
   <si>
-    <t>7 m 13.952 s</t>
+    <t>@Regression</t>
+  </si>
+  <si>
+    <t>5 m 50.825 s</t>
   </si>
 </sst>
 </file>
@@ -1791,7 +1794,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</c:v>
+                  <c:v>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1802,7 +1805,7 @@
               <c:numCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.0</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1863,7 +1866,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</c:v>
+                  <c:v>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1930,7 +1933,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_Estimate_02|Verify that Estimate delivery date functionality is working fine two Product | "TD_UI_Zlaata_Estimate_02"</c:v>
+                  <c:v>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2333,27 +2336,33 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
+              <c:f>Tags!$B$22:$B$24</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Estimate_02</c:v>
+                  <c:v>@New</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@est</c:v>
+                  <c:v>@TC_UI_Zlaata_New_01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$D$22:$D$23</c:f>
+              <c:f>Tags!$D$22:$D$24</c:f>
               <c:numCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2412,21 +2421,24 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
+              <c:f>Tags!$B$22:$B$24</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Estimate_02</c:v>
+                  <c:v>@New</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@est</c:v>
+                  <c:v>@TC_UI_Zlaata_New_01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$F$22:$F$23</c:f>
+              <c:f>Tags!$F$22:$F$24</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -2483,21 +2495,24 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tags!$B$22:$B$23</c:f>
+              <c:f>Tags!$B$22:$B$24</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_Estimate_02</c:v>
+                  <c:v>@New</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>@est</c:v>
+                  <c:v>@TC_UI_Zlaata_New_01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>@Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tags!$E$22:$E$23</c:f>
+              <c:f>Tags!$E$22:$E$24</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -2706,7 +2721,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>This is Express Delivery feature</c:v>
+                  <c:v>Verify New Label Feature</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2778,7 +2793,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>This is Express Delivery feature</c:v>
+                  <c:v>Verify New Label Feature</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2845,7 +2860,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>This is Express Delivery feature</c:v>
+                  <c:v>Verify New Label Feature</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5785,7 +5800,7 @@
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
   <sheetData/>
-  <sheetProtection sheet="true" password="FA7B" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="D74D" scenarios="true" objects="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5869,10 +5884,10 @@
         <v>29</v>
       </c>
       <c r="G22" s="57" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H22" s="58" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I22" s="59"/>
       <c r="J22" s="60"/>
@@ -5891,7 +5906,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B20:I29"/>
+  <dimension ref="B20:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="1.28515625"/>
@@ -5963,45 +5978,43 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
+    <row r="24">
+      <c r="B24" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D24" s="58" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E24" s="59"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="61" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="36" t="s">
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="35" t="s">
+      <c r="I28" s="35" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="I28" s="55" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="62" t="s">
         <v>57</v>
@@ -6017,13 +6030,50 @@
         <v>29</v>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="I30" s="55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="I31" s="55" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C27:G27"/>
     <mergeCell ref="C28:G28"/>
     <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6114,7 +6164,7 @@
         <v>29</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="57" t="n">
         <v>1.0</v>
@@ -6128,10 +6178,10 @@
         <v>54</v>
       </c>
       <c r="J22" s="57" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K22" s="58" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L22" s="59"/>
       <c r="M22" s="60"/>
@@ -6205,7 +6255,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -6274,7 +6324,7 @@
       </c>
       <c r="H5" t="n" s="0">
         <f>SUM(H2:H4)</f>
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">

--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -13,31 +13,23 @@
     <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" tabRatio="785"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="13" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="14" r:id="rId2"/>
-    <sheet name="Tags" sheetId="18" r:id="rId3"/>
-    <sheet name="Features" sheetId="16" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="11" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="3" r:id="rId2"/>
+    <sheet name="Tags" sheetId="4" r:id="rId3"/>
+    <sheet name="Features" sheetId="2" r:id="rId4"/>
+    <sheet name="Exceptions" sheetId="12" r:id="rId5"/>
     <sheet name="DB Data" sheetId="5" r:id="rId8" state="veryHidden"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="Chart1" localSheetId="3">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="1">Scenarios!#REF!</definedName>
-    <definedName name="Chart1" localSheetId="2">[1]Scenarios!#REF!</definedName>
-    <definedName name="Chart1">#REF!</definedName>
-    <definedName name="Chart10">#REF!</definedName>
-    <definedName name="Chart30">#REF!</definedName>
-    <definedName name="Chart49">#REF!</definedName>
-    <definedName name="Chart51">#REF!</definedName>
+    <definedName name="Chart1">Scenarios!#REF!</definedName>
+    <definedName name="Chart51">Scenarios!#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="80">
   <si>
     <t>Duration</t>
   </si>
@@ -96,6 +88,9 @@
     <t>STATUS</t>
   </si>
   <si>
+    <t>FEATURE STATUS</t>
+  </si>
+  <si>
     <t>Features Total</t>
   </si>
   <si>
@@ -111,43 +106,109 @@
     <t>Excel Extent Report</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:16 PM</t>
+    <t>TAG</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:14 PM</t>
+    <t>Scenario Passed</t>
   </si>
   <si>
-    <t>Jan 06, 2023 2:45:15 PM</t>
+    <t>Scenario Failed</t>
   </si>
   <si>
-    <t>0.252 s</t>
+    <t>Scenario Skipped</t>
+  </si>
+  <si>
+    <t>Tag Name</t>
+  </si>
+  <si>
+    <t>Feature Name</t>
+  </si>
+  <si>
+    <t>Feature Status</t>
+  </si>
+  <si>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>Scenario Status</t>
+  </si>
+  <si>
+    <t>Step Passed</t>
+  </si>
+  <si>
+    <t>Step Failed</t>
+  </si>
+  <si>
+    <t>Step Skipped</t>
+  </si>
+  <si>
+    <t>FEATURE FAIL SKIP</t>
+  </si>
+  <si>
+    <t>SCENARIO FAIL SKIP</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>0.013 s</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>0.022 s</t>
+    <t>FAILED &amp; SKIPPED TAGS</t>
   </si>
   <si>
     <t>TAG NAME</t>
   </si>
   <si>
+    <t>FAILED &amp; SKIPPED SCENARIOS</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:11 PM</t>
+  </si>
+  <si>
+    <t>Jan 06, 2023 2:45:09 PM</t>
+  </si>
+  <si>
+    <t>0.253 s</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>0.015 s</t>
+  </si>
+  <si>
+    <t>0.023 s</t>
+  </si>
+  <si>
+    <t>tag1</t>
+  </si>
+  <si>
     <t>tag</t>
+  </si>
+  <si>
+    <t>STACKTRACE</t>
   </si>
   <si>
     <t>STEP / HOOK TEXT</t>
   </si>
   <si>
-    <t>STACKTRACE</t>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>STEPS</t>
+  </si>
+  <si>
+    <t>SCENARIOS</t>
+  </si>
+  <si>
+    <t>NAME</t>
   </si>
   <si>
     <t>SCENARIO</t>
@@ -156,73 +217,69 @@
     <t>FEATURE</t>
   </si>
   <si>
-    <t>STEPS</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>SCENARIOS</t>
-  </si>
-  <si>
     <t>PASS %</t>
   </si>
   <si>
     <t>AUTHOR NAME</t>
   </si>
   <si>
-    <t>author</t>
+    <t>device</t>
   </si>
   <si>
     <t>DEVICE NAME</t>
   </si>
   <si>
-    <t>device</t>
+    <t>Jun 20, 2026 10:24:48 am</t>
   </si>
   <si>
-    <t>May 13, 2026 1:45:27 PM</t>
+    <t>Jun 20, 2026 10:21:00 am</t>
   </si>
   <si>
-    <t>May 13, 2026 1:39:32 PM</t>
+    <t>Jun 20, 2026 10:24:44 am</t>
   </si>
   <si>
-    <t>May 13, 2026 1:45:24 PM</t>
+    <t>3 m 43.433 s</t>
   </si>
   <si>
-    <t>5 m 52.417 s</t>
+    <t>0%</t>
   </si>
   <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</t>
-  </si>
-  <si>
-    <t>5 m 50.808 s</t>
-  </si>
-  <si>
-    <t>Verify New Label Feature</t>
-  </si>
-  <si>
-    <t>@New</t>
-  </si>
-  <si>
-    <t>@TC_UI_Zlaata_New_01</t>
+    <t>75%</t>
   </si>
   <si>
     <t>@Regression</t>
   </si>
   <si>
-    <t>5 m 50.825 s</t>
+    <t>@TC_UI_Zlaata_Home_08</t>
+  </si>
+  <si>
+    <t>Home Page Banner upload verification admin panel</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Home_08 |Verify all uploaded Special Timer products appear in Admin and User App.| "TD_UI_Zlaata_Home_08"</t>
+  </si>
+  <si>
+    <t>3 m 40.342 s</t>
+  </si>
+  <si>
+    <t>3 m 40.351 s</t>
+  </si>
+  <si>
+    <t>And verify products from "Test.xlsx" should be visible in user app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org.openqa.selenium.TimeoutException: Expected condition failed: waiting for visibility of element located by By.id: searchProductWrapper (tried for 10 second(s) with 500 milliseconds interval)
+Build info: version: '4.34.0', revision: '707dcb4246*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.8'
+Driver info: net.bytebuddy.renamed.java.lang.Object$ByteBuddy$ZlU8m0WI
+Capabilities {acceptInsecureCerts: true, browserName: chrome, browserVersion: 148.0.7778.217, chrome: {chromedriverVersion: 148.0.7778.178 (d096af1c9e9..., userDataDir: C:\Users\Abdul\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55021}, goog:processID: 12384, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55021/devtoo..., se:cdpVersion: 148.0.7778.217, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: efe84dfc4fcbc224de23b8e005b01b8e
+	at org.openqa.selenium.support.ui.WebDriverWait.timeoutException(WebDriverWait.java:84)
+	at org.openqa.selenium.support.ui.FluentWait.until(FluentWait.java:228)
+	at pages.AdminPanelPage.verifyProductsUserApp(AdminPanelPage.java:2524)
+	at stepDef.AdminPanelStepDef.verify_products_from_should_be_visible_in_user_app(AdminPanelStepDef.java:133)
+	at ✽.verify products from "Test.xlsx" should be visible in user app(file:///C:/Users/Abdul/git/ZlaataQAseverRegression/src/test/resources/features/AdminFeature/allHomePage.feature:92)
+</t>
   </si>
 </sst>
 </file>
@@ -230,7 +287,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="0"/>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +298,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -290,9 +371,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FF51FF21"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,7 +397,7 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color rgb="FF51FF21"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -323,7 +410,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
-      <color rgb="00FF00"/>
+      <color rgb="FF0000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color rgb="FF0000"/>
       <b val="true"/>
     </font>
     <font>
@@ -351,11 +443,6 @@
       <sz val="11.0"/>
       <b val="true"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="00FF00"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -365,7 +452,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -380,6 +467,43 @@
       <right style="hair">
         <color auto="1"/>
       </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -447,9 +571,7 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
@@ -477,173 +599,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment vertical="top" wrapText="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,24 +789,30 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Features</a:t>
+              <a:t>Tags with</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> Failed &amp; Skipped Scenarios</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.1929905820595947E-3"/>
-          <c:y val="5.6284335775106678E-2"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -720,10 +822,719 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11780714910636171"/>
-          <c:y val="8.0818739637467149E-2"/>
-          <c:w val="0.76899981252343452"/>
-          <c:h val="0.87885598708448542"/>
+          <c:x val="2.9880212949228394E-2"/>
+          <c:y val="0.11750877449771498"/>
+          <c:w val="0.95813725490196078"/>
+          <c:h val="0.84734403472530151"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Regression</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Home_08</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$B$20:$B$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Regression</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Home_08</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$D$20:$D$21</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$A$20:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>@Regression</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Home_08</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$C$20:$C$21</c:f>
+              <c:numCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DB0E-4C20-A461-10AEB88517DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46151168"/>
+        <c:axId val="46117248"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46151168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46117248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46117248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46151168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.3309046751669701E-2"/>
+          <c:y val="0.10919339164237124"/>
+          <c:w val="0.95333333333333337"/>
+          <c:h val="0.84804664723032075"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Home Page Banner upload verification admin panel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$F$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$H$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Home Page Banner upload verification admin panel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$H$22</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Features!$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Features!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Home Page Banner upload verification admin panel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Features!$G$22</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5768-4C55-9686-6251C2C8BD33}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46512000"/>
+        <c:axId val="46513536"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46512000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46513536"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46513536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46512000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3310417416097107E-2"/>
+          <c:y val="0.17399131020088515"/>
+          <c:w val="0.93298799578986624"/>
+          <c:h val="0.80271606659122552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -765,7 +1576,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000001-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -790,7 +1601,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000003-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -815,7 +1626,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CEAE-4775-A1C6-116F718DC196}"/>
+                <c16:uniqueId val="{00000005-D2BC-4951-98B3-E41274AF2CA1}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -845,12 +1656,18 @@
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CEAE-4775-A1C6-116F718DC196}"/>
+              <c16:uniqueId val="{00000006-D2BC-4951-98B3-E41274AF2CA1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -886,7 +1703,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -912,15 +1729,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Devices</a:t>
+              <a:t>Authors</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -930,10 +1746,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -945,7 +1761,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$D$21</c:f>
+              <c:f>Authors!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -980,37 +1796,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$D$22</c:f>
+              <c:f>Authors!$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000000-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1019,7 +1834,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$F$21</c:f>
+              <c:f>Authors!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1054,25 +1869,24 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$F$22</c:f>
+              <c:f>Authors!$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1084,7 +1898,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000001-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1093,7 +1907,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Devices!$E$21</c:f>
+              <c:f>Authors!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1128,37 +1942,36 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Devices!$B$22</c:f>
+              <c:f>Authors!$B$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device</c:v>
+                  <c:v>AUTHOR NAME</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Devices!$E$22</c:f>
+              <c:f>Authors!$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AFAF-4E48-8694-E3C13D5D6545}"/>
+              <c16:uniqueId val="{00000002-77F2-4DDE-822F-16B38F6808E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1172,11 +1985,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1186,7 +1999,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1194,7 +2007,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1212,7 +2025,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -1220,14 +2033,379 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Devices</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKIPPED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Devices!$E$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Devices!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>device</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Devices!$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FAA3-4CA3-AB56-81BA9F622F8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46589440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46590976"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46590976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1281,12 +2459,750 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="0" i="1">
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Features with Failed &amp; Skipped</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> Scenarios</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.587826839649571E-2"/>
+          <c:y val="0.10654873856176561"/>
+          <c:w val="0.89369296921336749"/>
+          <c:h val="0.85018673119905308"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$J$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Home Page Banner upload verification admin panel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$J$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9F7-4BBB-94B0-AEDC4FA75EC0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$L$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Home Page Banner upload verification admin panel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$L$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scenario Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$H$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Home Page Banner upload verification admin panel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$K$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EDCE-4CDA-BBB7-BD88937029B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46193280"/>
+        <c:axId val="46285184"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46193280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46285184"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46285184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Scenarios</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46193280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Scenarios</a:t>
+              <a:t>Scenarios with Failed &amp; Skipped Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0031919744642044E-2"/>
+          <c:y val="0.10668158781898149"/>
+          <c:w val="0.92990424076607392"/>
+          <c:h val="0.8499999379835731"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$R$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Passed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="51FF21"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Home_08 |Verify all uploaded Special Timer products appear in Admin and User App.| "TD_UI_Zlaata_Home_08"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$R$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$S$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Home_08 |Verify all uploaded Special Timer products appear in Admin and User App.| "TD_UI_Zlaata_Home_08"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$T$20</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DB Data'!$T$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Step Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TC_UI_Zlaata_Home_08 |Verify all uploaded Special Timer products appear in Admin and User App.| "TD_UI_Zlaata_Home_08"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$S$20</c:f>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-97A8-4822-B247-3E0E0F2799A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="46328448"/>
+        <c:axId val="46408064"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="46328448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46408064"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="46408064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Steps</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="46328448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="6350">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Features</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1295,8 +3211,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="5.9364481457108926E-3"/>
-          <c:y val="3.2123800120282653E-2"/>
+          <c:x val="5.9362468167315514E-3"/>
+          <c:y val="6.4713026203216312E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1308,10 +3224,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.6498186400440001E-2"/>
-          <c:y val="0.10118873685128098"/>
-          <c:w val="0.87710436725913243"/>
-          <c:h val="0.86336406553156542"/>
+          <c:x val="7.3672686824927558E-2"/>
+          <c:y val="0.11902669624860428"/>
+          <c:w val="0.92151704085316477"/>
+          <c:h val="0.85596714084772552"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1353,7 +3269,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000001-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1378,7 +3294,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000003-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1403,42 +3319,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F52A-4A06-BA5F-6C71FCEF3775}"/>
+                <c16:uniqueId val="{00000005-C5E1-437A-A52D-DCB97CB8ED06}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$E$2:$E$4</c:f>
+              <c:f>'DB Data'!$C$2:$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Scenarios Passed</c:v>
+                  <c:v>Features Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Scenarios Failed</c:v>
+                  <c:v>Features Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scenarios Skipped</c:v>
+                  <c:v>Features Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$F$2:$F$4</c:f>
+              <c:f>'DB Data'!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-F52A-4A06-BA5F-6C71FCEF3775}"/>
+              <c16:uniqueId val="{00000006-C5E1-437A-A52D-DCB97CB8ED06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1474,7 +3427,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1494,16 +3447,16 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr algn="ctr">
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+              <a:rPr lang="en-US" sz="1800" b="0" i="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Steps</a:t>
+              <a:t>Scenarios</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1512,8 +3465,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.6171728533933258E-3"/>
-          <c:y val="5.4421749273573204E-2"/>
+          <c:x val="5.9107001159738751E-3"/>
+          <c:y val="3.7140215132502832E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1525,10 +3478,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11769966254218223"/>
-          <c:y val="8.4263722654767198E-2"/>
-          <c:w val="0.78142825896762902"/>
-          <c:h val="0.89306054848124394"/>
+          <c:x val="5.6571751205517912E-2"/>
+          <c:y val="8.4536101166436714E-2"/>
+          <c:w val="0.92725874381981321"/>
+          <c:h val="0.88851560210722469"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -1570,7 +3523,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000001-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1595,7 +3548,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000003-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1620,42 +3573,79 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-33E3-412A-9233-ED47CE12E57E}"/>
+                <c16:uniqueId val="{00000005-86A0-4454-A31A-15C1830346B8}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:f>'DB Data'!$E$2:$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Steps Passed</c:v>
+                  <c:v>Scenarios Passed</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Steps Failed</c:v>
+                  <c:v>Scenarios Failed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Steps Skipped</c:v>
+                  <c:v>Scenarios Skipped</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:f>'DB Data'!$F$2:$F$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-33E3-412A-9233-ED47CE12E57E}"/>
+              <c16:uniqueId val="{00000006-86A0-4454-A31A-15C1830346B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1691,7 +3681,261 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="126"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="26"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1600" b="0" i="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Steps</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.0163677357506801E-2"/>
+          <c:y val="5.5749128919860627E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.6917458262785006E-2"/>
+          <c:y val="0.10406650388213669"/>
+          <c:w val="0.93302459414795369"/>
+          <c:h val="0.87775832898936412"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d prstMaterial="matte"/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="51FF21"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln w="6350">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2833-4D5B-98DA-2F8086DE2D67}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'DB Data'!$G$2:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Steps Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Steps Failed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Steps Skipped</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DB Data'!$H$2:$H$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2833-4D5B-98DA-2F8086DE2D67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="40"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId1"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1734,9 +3978,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.3309046751669701E-2"/>
+          <c:x val="3.3278738246891114E-2"/>
           <c:y val="0.10500003204542271"/>
-          <c:w val="0.95333333333333337"/>
+          <c:w val="0.953375796178344"/>
           <c:h val="0.85236429602767994"/>
         </c:manualLayout>
       </c:layout>
@@ -1794,7 +4038,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Home_08 |Verify all uploaded Special Timer products appear in Admin and User App.| "TD_UI_Zlaata_Home_08"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1805,14 +4049,14 @@
               <c:numCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.0</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000000-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1866,7 +4110,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Home_08 |Verify all uploaded Special Timer products appear in Admin and User App.| "TD_UI_Zlaata_Home_08"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1879,7 +4123,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000002-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1933,7 +4177,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_New_01 |Verify New Label functionality in user app.| "TD_UI_Zlaata_New_01"</c:v>
+                  <c:v>TC_UI_Zlaata_Home_08 |Verify all uploaded Special Timer products appear in Admin and User App.| "TD_UI_Zlaata_Home_08"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1941,12 +4185,17 @@
           <c:val>
             <c:numRef>
               <c:f>Scenarios!$I$22</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BC15-411D-962D-5DCB501C11F3}"/>
+              <c16:uniqueId val="{00000001-2E13-4772-A58C-E37B2BA89DB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1960,11 +4209,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97185152"/>
-        <c:axId val="97201536"/>
+        <c:axId val="89325952"/>
+        <c:axId val="44310528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97185152"/>
+        <c:axId val="89325952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1974,7 +4223,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97201536"/>
+        <c:crossAx val="44310528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1982,7 +4231,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97201536"/>
+        <c:axId val="44310528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2014,7 +4263,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97185152"/>
+        <c:crossAx val="89325952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2043,7 +4292,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2109,7 +4358,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000001-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2134,7 +4383,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000003-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2159,7 +4408,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+                <c16:uniqueId val="{00000005-012F-4AE0-9B30-C14C76CB6C4B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2187,14 +4436,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-E9F3-48A9-919D-8B5D3C89A4DA}"/>
+              <c16:uniqueId val="{00000006-012F-4AE0-9B30-C14C76CB6C4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2215,931 +4470,6 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000122" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000122" header="0.30000000000000032" footer="0.30000000000000032"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:userShapes r:id="rId1"/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Tags</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$D$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>@New</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_New_01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$D$22:$D$24</c:f>
-              <c:numCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>@New</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_New_01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$F$22:$F$24</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Tags!$E$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Tags!$B$22:$B$24</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>@New</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>@TC_UI_Zlaata_New_01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>@Regression</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Tags!$E$22:$E$24</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3911-4866-9AC3-280C20776CB8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97122176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97123712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Features</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="3.3369832880226151E-2"/>
-          <c:y val="9.72480620155039E-2"/>
-          <c:w val="0.95324817070407986"/>
-          <c:h val="0.8601162790697674"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$F$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PASSED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="51FF21"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify New Label Feature</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$F$22</c:f>
-              <c:numCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$H$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SKIPPED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FFFF00"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify New Label Feature</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$H$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Features!$G$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FAILED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Features!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Verify New Label Feature</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Features!$G$22</c:f>
-              <c:numCache/>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3689-40C1-A405-579C7890F6E5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="97540352"/>
-        <c:axId val="97550336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="97540352"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97550336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="97550336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1100">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Scenarios</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="97540352"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
-        <c:minorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000056" l="0.70000000000000051" r="0.70000000000000051" t="0.75000000000000056" header="0.30000000000000027" footer="0.30000000000000027"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="126"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="26"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.3310417416097107E-2"/>
-          <c:y val="0.17399131020088515"/>
-          <c:w val="0.93298799578986624"/>
-          <c:h val="0.80271606659122552"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:doughnutChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d prstMaterial="matte"/>
-          </c:spPr>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="51FF21"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
-              </a:solidFill>
-              <a:ln w="6350">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="matte"/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1678-4457-8DD3-1C4694EC7DC1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'DB Data'!$C$2:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Features Passed</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Features Failed</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Features Skipped</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'DB Data'!$D$2:$D$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-1678-4457-8DD3-1C4694EC7DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="40"/>
-      </c:doughnutChart>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -3186,15 +4516,14 @@
             <a:r>
               <a:rPr lang="en-US" sz="1400" b="0" i="1">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Authors</a:t>
+              <a:t>Tags</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -3204,10 +4533,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.8329460366640847E-2"/>
-          <c:y val="0.10887593576392122"/>
-          <c:w val="0.96030983733539887"/>
-          <c:h val="0.84848841833351085"/>
+          <c:x val="2.8395445134575568E-2"/>
+          <c:y val="0.10887596899224808"/>
+          <c:w val="0.9602173913043478"/>
+          <c:h val="0.8484883720930233"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -3219,7 +4548,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$D$21</c:f>
+              <c:f>Tags!$D$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3254,37 +4583,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Regression</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Home_08</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$D$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$D$22:$D$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000000-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3293,7 +4618,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$F$21</c:f>
+              <c:f>Tags!$F$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3328,37 +4653,33 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Regression</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Home_08</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$F$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>Tags!$F$22:$F$23</c:f>
+              <c:numCache/>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000001-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3367,7 +4688,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Authors!$E$21</c:f>
+              <c:f>Tags!$E$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3402,37 +4723,41 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Authors!$B$22</c:f>
+              <c:f>Tags!$B$22:$B$23</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>author</c:v>
+                  <c:v>@Regression</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>@TC_UI_Zlaata_Home_08</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Authors!$E$22</c:f>
+              <c:f>Tags!$E$22:$E$23</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C43D-4700-9C1F-8935523D5E0B}"/>
+              <c16:uniqueId val="{00000002-2604-4208-BEA8-EA9F96270641}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3446,11 +4771,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97122176"/>
-        <c:axId val="97123712"/>
+        <c:axId val="46589440"/>
+        <c:axId val="46590976"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97122176"/>
+        <c:axId val="46589440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3460,7 +4785,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97123712"/>
+        <c:crossAx val="46590976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3468,7 +4793,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97123712"/>
+        <c:axId val="46590976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3486,7 +4811,7 @@
                 <a:r>
                   <a:rPr lang="en-US" sz="1100">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
                   <a:t>Scenarios</a:t>
@@ -3494,14 +4819,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
-        <c:crossAx val="97122176"/>
+        <c:crossAx val="46589440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3536,672 +4860,1681 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>43815</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>158115</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="190500" y="142875"/>
-          <a:ext cx="3749040" cy="777240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Duration</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828924</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472439</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>127635</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486774" y="142875"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Start Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2828925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>165735</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8486775" y="561975"/>
-          <a:ext cx="3749040" cy="365760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>End Time</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$6">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1019175" y="152401"/>
-          <a:ext cx="2933700" cy="771524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{ED1868E5-AE56-4ACA-8944-337939004EF9}" type="TxLink">
-            <a:rPr lang="en-US" sz="2400" b="1" i="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>0.252 s</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2400" b="1" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3790950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9448800" y="142875"/>
-          <a:ext cx="2800350" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:14 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3809999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>476249</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9467849" y="561975"/>
-          <a:ext cx="2771775" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" i="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:pPr algn="ctr"/>
-            <a:t>Jan 06, 2023 2:45:15 PM</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="1400" i="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
+      <xdr:colOff>57148</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66676</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7"/>
+        <xdr:cNvPr id="9" name="Group 8"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="190499" y="28576"/>
-          <a:ext cx="12045316" cy="3657600"/>
-          <a:chOff x="171449" y="36548"/>
-          <a:chExt cx="12045316" cy="3399182"/>
+          <a:off x="190498" y="0"/>
+          <a:ext cx="12068177" cy="3438525"/>
+          <a:chOff x="161923" y="0"/>
+          <a:chExt cx="12068177" cy="3438525"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="9" name="Group 8"/>
+          <xdr:cNvPr id="42" name="Group 41"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="171449" y="815528"/>
-            <a:ext cx="3749040" cy="2620202"/>
-            <a:chOff x="171449" y="815528"/>
-            <a:chExt cx="3749040" cy="2620202"/>
+            <a:off x="161923" y="0"/>
+            <a:ext cx="12068177" cy="3438525"/>
+            <a:chOff x="171448" y="19050"/>
+            <a:chExt cx="12068177" cy="3438525"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="13" name="Group 12"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="8477248" y="133350"/>
+              <a:ext cx="3762377" cy="685800"/>
+              <a:chOff x="8477248" y="133350"/>
+              <a:chExt cx="3762377" cy="685800"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="4" name="Rectangle 3"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477248" y="133350"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0" algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Start Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="5" name="Rectangle 4"/>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="8477249" y="495300"/>
+                <a:ext cx="3749040" cy="320040"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="l"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>End Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$4">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="TextBox 6"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9563100" y="133351"/>
+                <a:ext cx="2676525" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{07321330-A736-45CE-AAA5-68120F007E07}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink=" 'DB Data'!$B$5">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="8" name="TextBox 7"/>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="9572625" y="495300"/>
+                <a:ext cx="2667000" cy="323850"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:fld id="{C66D813D-5F81-41CE-8DAE-BBDD038F8F76}" type="TxLink">
+                  <a:rPr lang="en-US" sz="1400" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:pPr algn="ctr"/>
+                  <a:t>Jan 06, 2023 2:45:09 PM</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" sz="1400" i="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="2" name="Group 100"/>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="171448" y="19050"/>
+              <a:ext cx="12054842" cy="3438525"/>
+              <a:chOff x="171448" y="19050"/>
+              <a:chExt cx="12054842" cy="3438525"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="10" name="Group 9"/>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="171448" y="19050"/>
+                <a:ext cx="12054842" cy="3438525"/>
+                <a:chOff x="152398" y="27696"/>
+                <a:chExt cx="12054842" cy="3195586"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="16" name="Group 15"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="152398" y="656192"/>
+                  <a:ext cx="3749040" cy="2563550"/>
+                  <a:chOff x="152398" y="656192"/>
+                  <a:chExt cx="3749040" cy="2563550"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="31" name="Rectangle 30"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="152398" y="815526"/>
+                    <a:ext cx="3749040" cy="2381198"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:grpSp>
+                <xdr:nvGrpSpPr>
+                  <xdr:cNvPr id="32" name="Group 31"/>
+                  <xdr:cNvGrpSpPr/>
+                </xdr:nvGrpSpPr>
+                <xdr:grpSpPr>
+                  <a:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="3621406" cy="2563550"/>
+                    <a:chOff x="247650" y="656192"/>
+                    <a:chExt cx="3621406" cy="2563550"/>
+                  </a:xfrm>
+                </xdr:grpSpPr>
+                <xdr:grpSp>
+                  <xdr:nvGrpSpPr>
+                    <xdr:cNvPr id="33" name="Group 32"/>
+                    <xdr:cNvGrpSpPr/>
+                  </xdr:nvGrpSpPr>
+                  <xdr:grpSpPr>
+                    <a:xfrm>
+                      <a:off x="2771776" y="859785"/>
+                      <a:ext cx="1097280" cy="764816"/>
+                      <a:chOff x="2771776" y="859785"/>
+                      <a:chExt cx="1097280" cy="764816"/>
+                    </a:xfrm>
+                  </xdr:grpSpPr>
+                  <xdr:sp macro="" textlink="">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="35" name="Rounded Rectangle 34"/>
+                      <xdr:cNvSpPr/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="2771776" y="859785"/>
+                        <a:ext cx="1097280" cy="764816"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="roundRect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:ln w="3175"/>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="2">
+                        <a:schemeClr val="dk1"/>
+                      </a:lnRef>
+                      <a:fillRef idx="1">
+                        <a:schemeClr val="lt1"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:schemeClr val="dk1"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>PASSED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>FAILED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>SKIPPED</a:t>
+                        </a:r>
+                      </a:p>
+                      <a:p>
+                        <a:pPr algn="l"/>
+                        <a:r>
+                          <a:rPr lang="en-US" sz="1100">
+                            <a:ln>
+                              <a:noFill/>
+                            </a:ln>
+                            <a:solidFill>
+                              <a:schemeClr val="tx1"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:t>TOTAL</a:t>
+                        </a:r>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$2">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="36" name="TextBox 35"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="868694"/>
+                        <a:ext cx="485775" cy="247651"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{41487303-CB05-47E9-B96D-7F5847EFEAA3}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="27F959"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="27F959"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$3">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="37" name="TextBox 36"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3381375" y="1027977"/>
+                        <a:ext cx="485775" cy="251635"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{B77A6D75-C39D-49DE-828E-57821B240FA1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FF0000"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>2</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                  <xdr:sp macro="" textlink="'DB Data'!$D$4">
+                    <xdr:nvSpPr>
+                      <xdr:cNvPr id="38" name="TextBox 37"/>
+                      <xdr:cNvSpPr txBox="1"/>
+                    </xdr:nvSpPr>
+                    <xdr:spPr>
+                      <a:xfrm>
+                        <a:off x="3371850" y="1187314"/>
+                        <a:ext cx="495300" cy="239006"/>
+                      </a:xfrm>
+                      <a:prstGeom prst="rect">
+                        <a:avLst/>
+                      </a:prstGeom>
+                      <a:noFill/>
+                      <a:ln w="9525" cmpd="sng">
+                        <a:noFill/>
+                      </a:ln>
+                    </xdr:spPr>
+                    <xdr:style>
+                      <a:lnRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:lnRef>
+                      <a:fillRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:fillRef>
+                      <a:effectRef idx="0">
+                        <a:scrgbClr r="0" g="0" b="0"/>
+                      </a:effectRef>
+                      <a:fontRef idx="minor">
+                        <a:schemeClr val="dk1"/>
+                      </a:fontRef>
+                    </xdr:style>
+                    <xdr:txBody>
+                      <a:bodyPr wrap="square" rtlCol="0" anchor="t" anchorCtr="0"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr algn="ctr"/>
+                        <a:fld id="{7219BB06-5362-46C7-AE8B-8D4E64C9DED1}" type="TxLink">
+                          <a:rPr lang="en-US" sz="1100" b="0">
+                            <a:solidFill>
+                              <a:srgbClr val="FFFF00"/>
+                            </a:solidFill>
+                          </a:rPr>
+                          <a:pPr algn="ctr"/>
+                          <a:t>1</a:t>
+                        </a:fld>
+                        <a:endParaRPr lang="en-US" sz="1100" b="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FFFF00"/>
+                          </a:solidFill>
+                        </a:endParaRPr>
+                      </a:p>
+                    </xdr:txBody>
+                  </xdr:sp>
+                </xdr:grpSp>
+                <xdr:graphicFrame macro="">
+                  <xdr:nvGraphicFramePr>
+                    <xdr:cNvPr id="34" name="FeatureDough"/>
+                    <xdr:cNvGraphicFramePr>
+                      <a:graphicFrameLocks/>
+                    </xdr:cNvGraphicFramePr>
+                  </xdr:nvGraphicFramePr>
+                  <xdr:xfrm>
+                    <a:off x="247650" y="656192"/>
+                    <a:ext cx="2562225" cy="2563550"/>
+                  </xdr:xfrm>
+                  <a:graphic>
+                    <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+                      <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+                    </a:graphicData>
+                  </a:graphic>
+                </xdr:graphicFrame>
+              </xdr:grpSp>
+            </xdr:grpSp>
+            <xdr:grpSp>
+              <xdr:nvGrpSpPr>
+                <xdr:cNvPr id="17" name="Group 16"/>
+                <xdr:cNvGrpSpPr/>
+              </xdr:nvGrpSpPr>
+              <xdr:grpSpPr>
+                <a:xfrm>
+                  <a:off x="3981450" y="27696"/>
+                  <a:ext cx="4391026" cy="3177881"/>
+                  <a:chOff x="3981450" y="27696"/>
+                  <a:chExt cx="4391026" cy="3177881"/>
+                </a:xfrm>
+              </xdr:grpSpPr>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="25" name="Rectangle 24"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="3981450" y="133921"/>
+                    <a:ext cx="4391026" cy="3059265"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln w="6350"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:endParaRPr lang="en-US" sz="1100"/>
+                  </a:p>
+                </xdr:txBody>
+              </xdr:sp>
+              <xdr:sp macro="" textlink="">
+                <xdr:nvSpPr>
+                  <xdr:cNvPr id="26" name="Rounded Rectangle 25"/>
+                  <xdr:cNvSpPr/>
+                </xdr:nvSpPr>
+                <xdr:spPr>
+                  <a:xfrm>
+                    <a:off x="7143750" y="183252"/>
+                    <a:ext cx="1188720" cy="849796"/>
+                  </a:xfrm>
+                  <a:prstGeom prst="roundRect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:ln w="3175"/>
+                </xdr:spPr>
+                <xdr:style>
+                  <a:lnRef idx="2">
+                    <a:schemeClr val="dk1"/>
+                  </a:lnRef>
+                  <a:fillRef idx="1">
+                    <a:schemeClr val="lt1"/>
+                  </a:fillRef>
+                  <a:effectRef idx="0">
+                    <a:schemeClr val="dk1"/>
+                  </a:effectRef>
+                  <a:fontRef idx="minor">
+                    <a:schemeClr val="dk1"/>
+                  </a:fontRef>
+                </xdr:style>
+                <xdr:txBody>
+                  <a:bodyPr rtlCol="0" anchor="b" anchorCtr="0"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr algn="ctr"/>
+                    <a:endParaRPr lang="en-US" sz="1600" b="1" u="none">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>PASSED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>FAILED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>SKIPPED</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr algn="l"/>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>TOTAL</a:t>
+                    </a:r>
+                  </a: